--- a/GORRITI/Septiembre/GORRITI-Septiembre.xlsx
+++ b/GORRITI/Septiembre/GORRITI-Septiembre.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\GORRITI\Agosto\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\GORRITI\Septiembre\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7494E812-3AC3-4115-ACC2-3CB397427058}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05E5DAF3-9937-46B4-B9A9-30C20AF5ED6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="850" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,14 +21,14 @@
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">PRORRATEO!$A$1:$R$90</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'PRORRATEO DE PRUEBA  EMERGENCIA'!$A$1:$R$90</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$E$129</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$E$131</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="574" uniqueCount="246">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="581" uniqueCount="245">
   <si>
     <t>MAIL: consorciogorriti368@gmail.com</t>
   </si>
@@ -147,9 +147,6 @@
     <t>Fumigacion Viturro Alberto</t>
   </si>
   <si>
-    <t xml:space="preserve">Ascensores Lema mantenimiento </t>
-  </si>
-  <si>
     <t>TOTAL</t>
   </si>
   <si>
@@ -651,15 +648,9 @@
     <t>Articulos de limpieza</t>
   </si>
   <si>
-    <t>Transf 21/07</t>
-  </si>
-  <si>
     <t>EN MAY, JUNI, JULI NO SE DEBITA EL MANTENIMIENTO DE CUENTA</t>
   </si>
   <si>
-    <t>Debito 17/07</t>
-  </si>
-  <si>
     <t>Castellano Alejandro - Abono de servicio de mantenimiento de grupo electrogeno y porton</t>
   </si>
   <si>
@@ -672,90 +663,12 @@
     <t>Efectivo</t>
   </si>
   <si>
-    <t>Doartero Mano de obra y materiales recubrimiento de caño bajada</t>
-  </si>
-  <si>
-    <t>Transf 22/08</t>
-  </si>
-  <si>
-    <t>Transf 19/08</t>
-  </si>
-  <si>
-    <t>Matafuegos FIRE - Recarga</t>
-  </si>
-  <si>
-    <t>Transf 18/08</t>
-  </si>
-  <si>
-    <t>Transf 11/08</t>
-  </si>
-  <si>
-    <t>Doartero Mano de obra reparacion y cambio de luces piso 13</t>
-  </si>
-  <si>
-    <t>Transf 01/08</t>
-  </si>
-  <si>
-    <t>VTO 15/09</t>
-  </si>
-  <si>
-    <t>PERÍODO: AGOSTO</t>
-  </si>
-  <si>
-    <t>Sindicatos mes de AGOSTO</t>
-  </si>
-  <si>
-    <t>HONORARIOS ADMINISTRACION RC - SE ABONA EL MES JULIO - SE DEBE AGOSTO</t>
-  </si>
-  <si>
-    <t>Carta documento - Envio - 1A</t>
-  </si>
-  <si>
-    <t>Debito 13/08</t>
-  </si>
-  <si>
-    <t>PMC 11/08</t>
-  </si>
-  <si>
-    <t>Debito 12/08</t>
-  </si>
-  <si>
-    <t>Transf 14/08</t>
-  </si>
-  <si>
-    <t>Transf 07/08</t>
-  </si>
-  <si>
-    <t>Debito 11/08</t>
-  </si>
-  <si>
-    <t>Transf 12/08</t>
-  </si>
-  <si>
-    <t>Transf 21/08</t>
-  </si>
-  <si>
-    <t>No llego factura</t>
-  </si>
-  <si>
     <t>Sin consumo</t>
   </si>
   <si>
     <t>ANALIA AYELEN CAMERA</t>
   </si>
   <si>
-    <t>Retiro de piezas pagado por el propietario Carlos Srugo - Sin comprobante</t>
-  </si>
-  <si>
-    <t>Retiro de piezas pagado por el propietario Maria Couso - Sin comprobante</t>
-  </si>
-  <si>
-    <t>Retiro de piezas pagado por el propietario Sarubbi Adriana - Sin comprobante</t>
-  </si>
-  <si>
-    <t>Deposito sin identificar - 18/08</t>
-  </si>
-  <si>
     <t>LA CAJA NOS DA EN $1.510.113 PESOS, CUANDO EN EL BANCO TENEMOS 636.353,64 Y EN EFECTIVO 400.000 APROX, LA DIFERENCIA ES DE $473.759,95 ENTRE LA CAJA REAL QUE TENEMOS Y LA CAJA QUE NOS DA EL EXCEL DE $1.510.113</t>
   </si>
   <si>
@@ -766,6 +679,90 @@
   </si>
   <si>
     <t>Ascensor:</t>
+  </si>
+  <si>
+    <t>VTO 15/10</t>
+  </si>
+  <si>
+    <t>PERÍODO: SEPTIEMBRE</t>
+  </si>
+  <si>
+    <t>Sindicatos mes de SEPTIEMBRE</t>
+  </si>
+  <si>
+    <t>Debito 03/09</t>
+  </si>
+  <si>
+    <t>Transf 08/09</t>
+  </si>
+  <si>
+    <t>Doartero - Arreglo caño de agua terraza</t>
+  </si>
+  <si>
+    <t>PMC 08/09</t>
+  </si>
+  <si>
+    <t>HONORARIOS ADMINISTRACION RC - SE ABONA EL MES AGOSTO</t>
+  </si>
+  <si>
+    <t>HONORARIOS ADMINISTRACION RC - SE ABONA EL MES SEPTIEMBRE</t>
+  </si>
+  <si>
+    <t>Matias salvatierra - Desobstruccion columna cocina 4F</t>
+  </si>
+  <si>
+    <t>Debito 12/09</t>
+  </si>
+  <si>
+    <t>WF Ascensores - Anticipo 60% reparacion de la maquina de traccion según presupuesto aprobado 29/08</t>
+  </si>
+  <si>
+    <t>Transf 11/09</t>
+  </si>
+  <si>
+    <t>WF Ascensores - Servicio de mantenimiento ascensores</t>
+  </si>
+  <si>
+    <t>Ascensores Lema mantenimiento - Ultimo Mes</t>
+  </si>
+  <si>
+    <t>Transf 15/09</t>
+  </si>
+  <si>
+    <t>Transf 16/09</t>
+  </si>
+  <si>
+    <t>Debito 15/09</t>
+  </si>
+  <si>
+    <t>Debito 18/09</t>
+  </si>
+  <si>
+    <t>German Perez - Instalacion tablero de banco - Capacitor - Coseno Fit - Materiales y mano de obra</t>
+  </si>
+  <si>
+    <t>Transf 19/09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Doartero -Mano de obra y materiales reparacion caño cloacal zona bauleras </t>
+  </si>
+  <si>
+    <t>Transf 22/09</t>
+  </si>
+  <si>
+    <t>Debito 21/09</t>
+  </si>
+  <si>
+    <t>Destapaciones ItaloAmericana - Sector B destapacion de columna general cocina lavadero desde la terraza 30/05/2025</t>
+  </si>
+  <si>
+    <t>Transf 30/09</t>
+  </si>
+  <si>
+    <t>Destapaciones ItaloAmericana - Mantenimiento de cañerias repaso ramales de planta baja, columnas del primer piso y sus dos salidas cloacales - Abonos Mayo Junio Agosto y Septiembre</t>
+  </si>
+  <si>
+    <t>Depositos si identificar</t>
   </si>
 </sst>
 </file>
@@ -773,15 +770,15 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="9">
+    <numFmt numFmtId="8" formatCode="&quot;$&quot;\ #,##0.00;[Red]\-&quot;$&quot;\ #,##0.00"/>
+    <numFmt numFmtId="44" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="164" formatCode="&quot;$&quot;\ #,##0.00;[Red]\-&quot;$&quot;\ #,##0.00"/>
-    <numFmt numFmtId="165" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="166" formatCode="_ &quot;$&quot;\ * #,##0.00_ ;_ &quot;$&quot;\ * \-#,##0.00_ ;_ &quot;$&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="167" formatCode="_-&quot;$&quot;\ * #,##0_-;\-&quot;$&quot;\ * #,##0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="168" formatCode="_-&quot;$&quot;\ * #,##0.0_-;\-&quot;$&quot;\ * #,##0.0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="169" formatCode="_-&quot;$&quot;\ * #,##0.0_-;\-&quot;$&quot;\ * #,##0.0_-;_-&quot;$&quot;\ * &quot;-&quot;?_-;_-@_-"/>
-    <numFmt numFmtId="170" formatCode="_-[$$-2C0A]\ * #,##0.00_-;\-[$$-2C0A]\ * #,##0.00_-;_-[$$-2C0A]\ * &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="171" formatCode="#,##0.00_ ;[Red]\-#,##0.00\ "/>
+    <numFmt numFmtId="164" formatCode="_ &quot;$&quot;\ * #,##0.00_ ;_ &quot;$&quot;\ * \-#,##0.00_ ;_ &quot;$&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="165" formatCode="_-&quot;$&quot;\ * #,##0_-;\-&quot;$&quot;\ * #,##0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="166" formatCode="_-&quot;$&quot;\ * #,##0.0_-;\-&quot;$&quot;\ * #,##0.0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="167" formatCode="_-&quot;$&quot;\ * #,##0.0_-;\-&quot;$&quot;\ * #,##0.0_-;_-&quot;$&quot;\ * &quot;-&quot;?_-;_-@_-"/>
+    <numFmt numFmtId="168" formatCode="_-[$$-2C0A]\ * #,##0.00_-;\-[$$-2C0A]\ * #,##0.00_-;_-[$$-2C0A]\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="169" formatCode="#,##0.00_ ;[Red]\-#,##0.00\ "/>
   </numFmts>
   <fonts count="27" x14ac:knownFonts="1">
     <font>
@@ -1509,14 +1506,14 @@
   </borders>
   <cellStyleXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="166" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="242">
+  <cellXfs count="248">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1524,7 +1521,7 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="8" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="2" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1537,9 +1534,9 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="4" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -1553,7 +1550,7 @@
     <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -1563,40 +1560,40 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="44" fontId="3" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="165" fontId="9" fillId="6" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="9" fillId="6" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="14" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="14" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="15" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="15" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="16" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="3" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="0" fillId="3" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="0" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="44" fontId="7" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="15" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="15" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1611,24 +1608,24 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="6" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="20" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="20" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="20" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="15" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="15" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="15" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="20" fillId="0" borderId="27" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="20" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="20" fillId="0" borderId="31" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="21" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="21" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="20" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="20" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="20" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="15" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="15" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="15" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="20" fillId="0" borderId="27" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="20" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="20" fillId="0" borderId="31" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="21" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="21" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -1641,63 +1638,63 @@
     <xf numFmtId="2" fontId="15" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="20" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="20" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="20" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="15" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="15" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="15" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="20" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="20" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="20" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="15" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="15" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="15" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="20" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="20" fillId="0" borderId="30" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="20" fillId="0" borderId="32" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="20" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="20" fillId="0" borderId="30" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="20" fillId="0" borderId="32" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="10" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="4" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="15" fillId="4" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="15" fillId="4" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="6" fillId="7" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="15" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="13" fillId="8" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="6" fillId="7" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="15" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="13" fillId="8" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="10" fillId="4" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="10" fillId="4" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="4" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="22" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="7" fillId="4" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="22" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="7" fillId="4" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="10" fillId="8" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="10" fillId="8" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="20" fillId="2" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="20" fillId="2" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="9" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="9" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="44" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1712,27 +1709,27 @@
     <xf numFmtId="0" fontId="15" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="15" fillId="10" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="165" fontId="6" fillId="6" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="167" fontId="20" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="8" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="6" fillId="6" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="20" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="8" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="12" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="12" borderId="29" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="2" fillId="12" borderId="29" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1745,51 +1742,45 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="23" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="23" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="7" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="10" fillId="4" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="11" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="24" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="7" fillId="4" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="10" fillId="4" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="7" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="10" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="22" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="8" fontId="7" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="10" fillId="4" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="11" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="24" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="7" fillId="4" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="10" fillId="4" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="7" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="10" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="22" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="22" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="4" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="22" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="22" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="22" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="22" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="4" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="4" fillId="4" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="22" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="165" fontId="10" fillId="4" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="10" fillId="4" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="22" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="10" fillId="4" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="10" fillId="4" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="22" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="16" fontId="22" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="22" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="25" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="8" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="25" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="8" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="16" fontId="22" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="165" fontId="26" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="26" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="15" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
+    <xf numFmtId="165" fontId="15" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="43" fontId="0" fillId="3" borderId="12" xfId="3" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1803,27 +1794,52 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="10" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="10" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="19" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="171" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="170" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="165" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="8" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="169" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="168" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="44" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="168" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="20" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1836,41 +1852,15 @@
     <xf numFmtId="0" fontId="2" fillId="8" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="168" fontId="0" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="3" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1882,27 +1872,50 @@
     <xf numFmtId="0" fontId="16" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="1" xfId="4" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="8" fontId="8" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="8" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="8" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="8" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="170" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="44" fontId="8" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="20" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="16" fontId="22" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="25" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="7">
     <cellStyle name="Millares" xfId="3" builtinId="3"/>
@@ -2271,7 +2284,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M134"/>
+  <dimension ref="A1:M136"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="37.5703125" customWidth="1"/>
@@ -2286,37 +2299,37 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="190"/>
-      <c r="B1" s="191"/>
-      <c r="C1" s="192"/>
-      <c r="D1" s="192"/>
-      <c r="E1" s="193"/>
+      <c r="A1" s="188"/>
+      <c r="B1" s="189"/>
+      <c r="C1" s="190"/>
+      <c r="D1" s="190"/>
+      <c r="E1" s="191"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="15"/>
-      <c r="B2" s="189" t="s">
+      <c r="B2" s="187" t="s">
         <v>0</v>
       </c>
       <c r="C2" s="69"/>
-      <c r="D2" s="189"/>
+      <c r="D2" s="187"/>
       <c r="E2" s="70"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="15"/>
-      <c r="B3" s="189" t="s">
+      <c r="B3" s="187" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="189"/>
-      <c r="D3" s="189"/>
+      <c r="C3" s="187"/>
+      <c r="D3" s="187"/>
       <c r="E3" s="70"/>
     </row>
     <row r="4" spans="1:5" ht="32.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="15"/>
-      <c r="B4" s="194" t="s">
+      <c r="B4" s="192" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="189"/>
-      <c r="D4" s="195" t="s">
+      <c r="C4" s="187"/>
+      <c r="D4" s="193" t="s">
         <v>3</v>
       </c>
       <c r="E4" s="70"/>
@@ -2337,10 +2350,10 @@
         <v>6</v>
       </c>
       <c r="B6" s="18" t="s">
-        <v>223</v>
-      </c>
-      <c r="C6" s="196"/>
-      <c r="D6" s="189" t="s">
+        <v>218</v>
+      </c>
+      <c r="C6" s="194"/>
+      <c r="D6" s="187" t="s">
         <v>7</v>
       </c>
       <c r="E6" s="16"/>
@@ -2357,49 +2370,49 @@
       <c r="E7" s="19"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B9" s="215" t="s">
-        <v>222</v>
-      </c>
-      <c r="C9" s="206"/>
+      <c r="B9" s="209" t="s">
+        <v>217</v>
+      </c>
+      <c r="C9" s="210"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B10" s="206"/>
-      <c r="C10" s="206"/>
+      <c r="B10" s="210"/>
+      <c r="C10" s="210"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B11" s="206"/>
-      <c r="C11" s="206"/>
+      <c r="B11" s="210"/>
+      <c r="C11" s="210"/>
     </row>
     <row r="13" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="217" t="s">
+      <c r="A14" s="214" t="s">
         <v>10</v>
       </c>
-      <c r="B14" s="206"/>
-      <c r="C14" s="206"/>
-      <c r="D14" s="206"/>
-      <c r="E14" s="206"/>
+      <c r="B14" s="210"/>
+      <c r="C14" s="210"/>
+      <c r="D14" s="210"/>
+      <c r="E14" s="210"/>
     </row>
     <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="206"/>
-      <c r="B15" s="206"/>
-      <c r="C15" s="206"/>
-      <c r="D15" s="206"/>
-      <c r="E15" s="206"/>
+      <c r="A15" s="210"/>
+      <c r="B15" s="210"/>
+      <c r="C15" s="210"/>
+      <c r="D15" s="210"/>
+      <c r="E15" s="210"/>
     </row>
     <row r="16" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="206"/>
-      <c r="B16" s="206"/>
-      <c r="C16" s="206"/>
-      <c r="D16" s="206"/>
-      <c r="E16" s="206"/>
+      <c r="A16" s="210"/>
+      <c r="B16" s="210"/>
+      <c r="C16" s="210"/>
+      <c r="D16" s="210"/>
+      <c r="E16" s="210"/>
     </row>
     <row r="17" spans="1:8" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="206"/>
-      <c r="B17" s="206"/>
-      <c r="C17" s="206"/>
-      <c r="D17" s="206"/>
-      <c r="E17" s="206"/>
+      <c r="A17" s="210"/>
+      <c r="B17" s="210"/>
+      <c r="C17" s="210"/>
+      <c r="D17" s="210"/>
+      <c r="E17" s="210"/>
     </row>
     <row r="18" spans="1:8" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="19" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
@@ -2430,8 +2443,8 @@
       </c>
       <c r="B23" s="5"/>
       <c r="C23" s="5"/>
-      <c r="D23" s="156">
-        <v>1312219</v>
+      <c r="D23" s="239">
+        <v>1357288</v>
       </c>
       <c r="E23" s="152"/>
     </row>
@@ -2476,10 +2489,10 @@
       <c r="C28" s="56"/>
       <c r="D28" s="157">
         <f>SUM(D23:D27)</f>
-        <v>1312219</v>
+        <v>1357288</v>
       </c>
       <c r="E28" s="158"/>
-      <c r="G28" s="200"/>
+      <c r="G28" s="198"/>
     </row>
     <row r="29" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
@@ -2487,11 +2500,11 @@
       </c>
       <c r="B29" s="5"/>
       <c r="C29" s="5"/>
-      <c r="D29" s="156">
-        <v>1079569</v>
+      <c r="D29" s="239">
+        <v>1120450</v>
       </c>
       <c r="E29" s="152"/>
-      <c r="G29" s="202"/>
+      <c r="G29" s="200"/>
     </row>
     <row r="30" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="56" t="s">
@@ -2501,22 +2514,22 @@
       <c r="C30" s="56"/>
       <c r="D30" s="157">
         <f>SUM(D29:D29)</f>
-        <v>1079569</v>
+        <v>1120450</v>
       </c>
       <c r="E30" s="158"/>
-      <c r="G30" s="201"/>
+      <c r="G30" s="199"/>
     </row>
     <row r="31" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" s="5"/>
-      <c r="B31" s="199"/>
-      <c r="C31" s="199"/>
+      <c r="B31" s="197"/>
+      <c r="C31" s="197"/>
       <c r="D31" s="156"/>
-      <c r="E31" s="182"/>
-      <c r="G31" s="201">
+      <c r="E31" s="181"/>
+      <c r="G31" s="199">
         <v>-500000</v>
       </c>
       <c r="H31" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
     </row>
     <row r="32" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
@@ -2530,7 +2543,7 @@
         <v>0</v>
       </c>
       <c r="E32" s="158"/>
-      <c r="G32" s="201">
+      <c r="G32" s="199">
         <f>G30+G31</f>
         <v>-500000</v>
       </c>
@@ -2544,7 +2557,7 @@
       <c r="D33" s="119"/>
       <c r="E33" s="160">
         <f>D28+D30+D32</f>
-        <v>2391788</v>
+        <v>2477738</v>
       </c>
       <c r="F33" s="20"/>
     </row>
@@ -2558,942 +2571,981 @@
       <c r="E34" s="162"/>
     </row>
     <row r="35" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="216" t="s">
-        <v>202</v>
+      <c r="A35" s="213" t="s">
+        <v>201</v>
       </c>
       <c r="B35" s="208"/>
-      <c r="C35" s="182"/>
-      <c r="D35" s="156">
-        <v>90000</v>
-      </c>
-      <c r="E35" s="181" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="207" t="s">
+      <c r="C35" s="181"/>
+      <c r="D35" s="239">
+        <v>60000</v>
+      </c>
+      <c r="E35" s="180" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="215" t="s">
         <v>225</v>
       </c>
-      <c r="B36" s="210"/>
-      <c r="C36" s="51"/>
-      <c r="D36" s="156">
+      <c r="B36" s="216"/>
+      <c r="C36" s="181"/>
+      <c r="D36" s="239">
         <v>249000</v>
       </c>
-      <c r="E36" s="181" t="s">
-        <v>233</v>
-      </c>
-      <c r="H36" s="136"/>
-    </row>
-    <row r="37" spans="1:8" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="27" t="s">
+      <c r="E36" s="180" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="215" t="s">
+        <v>224</v>
+      </c>
+      <c r="B37" s="216"/>
+      <c r="C37" s="51"/>
+      <c r="D37" s="239">
+        <v>249000</v>
+      </c>
+      <c r="E37" s="180" t="s">
+        <v>221</v>
+      </c>
+      <c r="H37" s="136"/>
+    </row>
+    <row r="38" spans="1:8" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="27" t="s">
         <v>19</v>
-      </c>
-      <c r="B37" s="27"/>
-      <c r="C37" s="27"/>
-      <c r="D37" s="163"/>
-      <c r="E37" s="164">
-        <f>SUM(D35:D36)</f>
-        <v>339000</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A38" s="33" t="s">
-        <v>20</v>
       </c>
       <c r="B38" s="27"/>
       <c r="C38" s="27"/>
-      <c r="D38" s="165"/>
-      <c r="E38" s="166"/>
-    </row>
-    <row r="39" spans="1:8" s="36" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="209" t="s">
+      <c r="D38" s="163"/>
+      <c r="E38" s="164">
+        <f>SUM(D35:D37)</f>
+        <v>558000</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A39" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="B39" s="27"/>
+      <c r="C39" s="27"/>
+      <c r="D39" s="165"/>
+      <c r="E39" s="166"/>
+    </row>
+    <row r="40" spans="1:8" s="36" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="207" t="s">
         <v>21</v>
       </c>
-      <c r="B39" s="208"/>
-      <c r="C39" s="53"/>
-      <c r="D39" s="188">
-        <v>144149</v>
-      </c>
-      <c r="E39" s="167" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="209"/>
       <c r="B40" s="208"/>
       <c r="C40" s="53"/>
-      <c r="D40" s="168"/>
-      <c r="E40" s="167"/>
-    </row>
-    <row r="41" spans="1:8" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="27" t="s">
+      <c r="D40" s="240">
+        <v>144149</v>
+      </c>
+      <c r="E40" s="167" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="207"/>
+      <c r="B41" s="208"/>
+      <c r="C41" s="53"/>
+      <c r="D41" s="168"/>
+      <c r="E41" s="167"/>
+    </row>
+    <row r="42" spans="1:8" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="27" t="s">
         <v>22</v>
       </c>
-      <c r="B41" s="27"/>
-      <c r="C41" s="27"/>
-      <c r="D41" s="163"/>
-      <c r="E41" s="113">
-        <f>SUM(D39:D40)</f>
+      <c r="B42" s="27"/>
+      <c r="C42" s="27"/>
+      <c r="D42" s="163"/>
+      <c r="E42" s="113">
+        <f>SUM(D40:D41)</f>
         <v>144149</v>
       </c>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A42" s="33" t="s">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A43" s="33" t="s">
         <v>23</v>
       </c>
-      <c r="B42" s="153"/>
-      <c r="C42" s="153"/>
-      <c r="D42" s="169"/>
-      <c r="E42" s="170"/>
-    </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A43" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="B43" s="5"/>
-      <c r="C43" s="51"/>
-      <c r="D43" s="240">
-        <v>1843741.12</v>
-      </c>
-      <c r="E43" s="171" t="s">
-        <v>228</v>
-      </c>
-      <c r="G43" s="136"/>
+      <c r="B43" s="153"/>
+      <c r="C43" s="153"/>
+      <c r="D43" s="169"/>
+      <c r="E43" s="170"/>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" s="5" t="s">
-        <v>224</v>
-      </c>
-      <c r="B44" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B44" s="5"/>
+      <c r="C44" s="51"/>
+      <c r="D44" s="241">
+        <v>1753141.39</v>
+      </c>
+      <c r="E44" s="171" t="s">
+        <v>223</v>
+      </c>
+      <c r="G44" s="136"/>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A45" s="5" t="s">
+        <v>219</v>
+      </c>
+      <c r="B45" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="C44" s="5"/>
-      <c r="D44" s="168">
-        <v>133047.14000000001</v>
-      </c>
-      <c r="E44" s="172" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A45" s="5" t="str">
-        <f>A44</f>
-        <v>Sindicatos mes de AGOSTO</v>
-      </c>
-      <c r="B45" s="5" t="s">
-        <v>26</v>
-      </c>
       <c r="C45" s="5"/>
-      <c r="D45" s="168">
-        <v>241435.09</v>
-      </c>
-      <c r="E45" s="172" t="str">
-        <f>E44</f>
-        <v>Debito 12/08</v>
+      <c r="D45" s="183">
+        <v>137546.85999999999</v>
+      </c>
+      <c r="E45" s="172" t="s">
+        <v>227</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" s="5" t="str">
         <f>A45</f>
-        <v>Sindicatos mes de AGOSTO</v>
+        <v>Sindicatos mes de SEPTIEMBRE</v>
       </c>
       <c r="B46" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="C46" s="5"/>
+      <c r="D46" s="183">
+        <v>248622.81</v>
+      </c>
+      <c r="E46" s="172" t="str">
+        <f>E45</f>
+        <v>Debito 12/09</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A47" s="5" t="str">
+        <f>A46</f>
+        <v>Sindicatos mes de SEPTIEMBRE</v>
+      </c>
+      <c r="B47" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="C46" s="5"/>
-      <c r="D46" s="168">
-        <v>14783.02</v>
-      </c>
-      <c r="E46" s="173" t="str">
-        <f>E45</f>
-        <v>Debito 12/08</v>
-      </c>
-    </row>
-    <row r="47" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="27" t="s">
+      <c r="C47" s="5"/>
+      <c r="D47" s="183">
+        <v>15282.98</v>
+      </c>
+      <c r="E47" s="173" t="str">
+        <f>E46</f>
+        <v>Debito 12/09</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="27" t="s">
         <v>28</v>
-      </c>
-      <c r="B47" s="153"/>
-      <c r="C47" s="153"/>
-      <c r="D47" s="174"/>
-      <c r="E47" s="113">
-        <f>SUM(D43:D46)</f>
-        <v>2233006.37</v>
-      </c>
-    </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A48" s="33" t="s">
-        <v>29</v>
       </c>
       <c r="B48" s="153"/>
       <c r="C48" s="153"/>
-      <c r="D48" s="169"/>
-      <c r="E48" s="170"/>
-    </row>
-    <row r="49" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="B49" s="5"/>
-      <c r="C49" s="5"/>
-      <c r="D49" s="168">
-        <v>1002998.17</v>
-      </c>
-      <c r="E49" s="179" t="s">
-        <v>216</v>
-      </c>
+      <c r="D48" s="174"/>
+      <c r="E48" s="113">
+        <f>SUM(D44:D47)</f>
+        <v>2154594.04</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A49" s="33" t="s">
+        <v>29</v>
+      </c>
+      <c r="B49" s="153"/>
+      <c r="C49" s="153"/>
+      <c r="D49" s="169"/>
+      <c r="E49" s="170"/>
     </row>
     <row r="50" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="B50" s="5"/>
+      <c r="C50" s="5"/>
+      <c r="D50" s="183">
+        <v>824658.47</v>
+      </c>
+      <c r="E50" s="171" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="B50" s="184"/>
-      <c r="C50" s="5"/>
-      <c r="D50" s="168">
-        <v>23385.69</v>
-      </c>
-      <c r="E50" s="179" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A51" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="B51" s="5" t="s">
-        <v>236</v>
-      </c>
+      <c r="B51" s="183"/>
       <c r="C51" s="5"/>
-      <c r="D51" s="168">
-        <v>0</v>
-      </c>
-      <c r="E51" s="175"/>
+      <c r="D51" s="183">
+        <v>20038.91</v>
+      </c>
+      <c r="E51" s="171" t="s">
+        <v>223</v>
+      </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="B52" s="184"/>
+        <v>32</v>
+      </c>
+      <c r="B52" s="5" t="s">
+        <v>211</v>
+      </c>
       <c r="C52" s="5"/>
       <c r="D52" s="168">
-        <v>12432.23</v>
-      </c>
-      <c r="E52" s="179" t="str">
-        <f>E50</f>
-        <v>Transf 11/08</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E52" s="175"/>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" s="5" t="s">
-        <v>203</v>
-      </c>
-      <c r="B53" s="5"/>
+        <v>33</v>
+      </c>
+      <c r="B53" s="183"/>
       <c r="C53" s="5"/>
-      <c r="D53" s="168">
-        <v>5586.39</v>
-      </c>
-      <c r="E53" s="185" t="s">
-        <v>218</v>
+      <c r="D53" s="183">
+        <v>8423.4500000000007</v>
+      </c>
+      <c r="E53" s="179" t="str">
+        <f>E51</f>
+        <v>PMC 08/09</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" s="5" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B54" s="5"/>
       <c r="C54" s="5"/>
-      <c r="D54" s="168">
-        <v>2046270.6</v>
-      </c>
-      <c r="E54" s="185" t="s">
-        <v>209</v>
+      <c r="D54" s="183">
+        <v>5530.12</v>
+      </c>
+      <c r="E54" s="184" t="s">
+        <v>232</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" s="5" t="s">
-        <v>34</v>
+        <v>203</v>
       </c>
       <c r="B55" s="5"/>
       <c r="C55" s="5"/>
-      <c r="D55" s="168">
-        <v>24435</v>
-      </c>
-      <c r="E55" s="180" t="s">
+      <c r="D55" s="183">
+        <v>2086018.93</v>
+      </c>
+      <c r="E55" s="184" t="s">
         <v>234</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A56" s="209" t="s">
+      <c r="A56" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="B56" s="5"/>
+      <c r="C56" s="5"/>
+      <c r="D56" s="183">
+        <v>25159.5</v>
+      </c>
+      <c r="E56" s="184" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A57" s="207" t="s">
         <v>35</v>
       </c>
-      <c r="B56" s="208"/>
-      <c r="C56" s="5"/>
-      <c r="D56" s="168">
-        <v>2168902.4</v>
-      </c>
-      <c r="E56" s="185" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="209"/>
       <c r="B57" s="208"/>
-      <c r="C57" s="154"/>
-      <c r="D57" s="203"/>
-      <c r="E57" s="204"/>
-    </row>
-    <row r="58" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="27" t="s">
+      <c r="C57" s="5"/>
+      <c r="D57" s="183">
+        <v>2177347.2799999998</v>
+      </c>
+      <c r="E57" s="184" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="207"/>
+      <c r="B58" s="208"/>
+      <c r="C58" s="154"/>
+      <c r="D58" s="201"/>
+      <c r="E58" s="202"/>
+    </row>
+    <row r="59" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A59" s="27" t="s">
         <v>36</v>
-      </c>
-      <c r="B58" s="27"/>
-      <c r="C58" s="27"/>
-      <c r="D58" s="163"/>
-      <c r="E58" s="113">
-        <f>SUM(D49:D57)</f>
-        <v>5284010.4800000004</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="33" t="s">
-        <v>37</v>
       </c>
       <c r="B59" s="27"/>
       <c r="C59" s="27"/>
       <c r="D59" s="163"/>
-      <c r="E59" s="176"/>
-    </row>
-    <row r="60" spans="1:5" ht="29.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="207" t="s">
-        <v>210</v>
-      </c>
-      <c r="B60" s="208"/>
-      <c r="C60" s="54"/>
-      <c r="D60" s="236" t="s">
-        <v>235</v>
-      </c>
-      <c r="E60" s="179"/>
-    </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A61" s="5" t="s">
+      <c r="E59" s="113">
+        <f>SUM(D50:D58)</f>
+        <v>5147176.66</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A60" s="33" t="s">
+        <v>37</v>
+      </c>
+      <c r="B60" s="27"/>
+      <c r="C60" s="27"/>
+      <c r="D60" s="163"/>
+      <c r="E60" s="176"/>
+    </row>
+    <row r="61" spans="1:5" ht="29.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A61" s="215" t="s">
+        <v>207</v>
+      </c>
+      <c r="B61" s="208"/>
+      <c r="C61" s="54"/>
+      <c r="D61" s="242">
+        <v>70000</v>
+      </c>
+      <c r="E61" s="180" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" ht="29.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A62" s="243" t="s">
+        <v>231</v>
+      </c>
+      <c r="B62" s="244"/>
+      <c r="C62" s="243"/>
+      <c r="D62" s="245">
+        <v>175500</v>
+      </c>
+      <c r="E62" s="246" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A63" s="243" t="s">
+        <v>230</v>
+      </c>
+      <c r="B63" s="244"/>
+      <c r="C63" s="243"/>
+      <c r="D63" s="245">
+        <v>222600</v>
+      </c>
+      <c r="E63" s="246" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A64" s="243" t="s">
         <v>38</v>
       </c>
-      <c r="B61" s="155"/>
-      <c r="C61" s="5"/>
-      <c r="D61" s="168">
+      <c r="B64" s="155"/>
+      <c r="C64" s="5"/>
+      <c r="D64" s="183">
         <v>56800</v>
       </c>
-      <c r="E61" s="179" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A62" s="5" t="s">
+      <c r="E64" s="246" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="65" spans="1:10" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A65" s="215" t="s">
+        <v>238</v>
+      </c>
+      <c r="B65" s="216"/>
+      <c r="C65" s="5"/>
+      <c r="D65" s="141">
+        <v>250000</v>
+      </c>
+      <c r="E65" s="246" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="66" spans="1:10" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A66" s="215" t="s">
+        <v>222</v>
+      </c>
+      <c r="B66" s="216"/>
+      <c r="C66" s="195"/>
+      <c r="D66" s="141">
+        <v>350000</v>
+      </c>
+      <c r="E66" s="180" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="67" spans="1:10" ht="39" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A67" s="211" t="s">
+        <v>226</v>
+      </c>
+      <c r="B67" s="212"/>
+      <c r="C67" s="51"/>
+      <c r="D67" s="141">
+        <v>24100</v>
+      </c>
+      <c r="E67" s="180"/>
+    </row>
+    <row r="68" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A68" s="203" t="s">
+        <v>205</v>
+      </c>
+      <c r="B68" s="204"/>
+      <c r="C68" s="51"/>
+      <c r="D68" s="141">
+        <v>276800</v>
+      </c>
+      <c r="E68" s="180" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="69" spans="1:10" ht="39" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A69" s="211" t="s">
+        <v>228</v>
+      </c>
+      <c r="B69" s="212"/>
+      <c r="C69" s="51"/>
+      <c r="D69" s="141">
+        <v>2468400</v>
+      </c>
+      <c r="E69" s="180" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="70" spans="1:10" ht="39" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A70" s="211" t="s">
+        <v>236</v>
+      </c>
+      <c r="B70" s="212"/>
+      <c r="C70" s="51"/>
+      <c r="D70" s="141">
+        <v>550000</v>
+      </c>
+      <c r="E70" s="180" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="71" spans="1:10" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A71" s="215" t="s">
+        <v>241</v>
+      </c>
+      <c r="B71" s="216"/>
+      <c r="C71" s="5"/>
+      <c r="D71" s="141">
+        <v>190000</v>
+      </c>
+      <c r="E71" s="180" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="72" spans="1:10" ht="61.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A72" s="215" t="s">
+        <v>243</v>
+      </c>
+      <c r="B72" s="216"/>
+      <c r="C72" s="5"/>
+      <c r="D72" s="141">
+        <v>450000</v>
+      </c>
+      <c r="E72" s="180" t="s">
+        <v>242</v>
+      </c>
+      <c r="I72" s="207"/>
+      <c r="J72" s="208"/>
+    </row>
+    <row r="73" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A73" s="27" t="s">
         <v>39</v>
       </c>
-      <c r="B62" s="155"/>
-      <c r="C62" s="5"/>
-      <c r="D62" s="168">
-        <v>155700</v>
-      </c>
-      <c r="E62" s="181" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="207" t="s">
-        <v>214</v>
-      </c>
-      <c r="B63" s="210"/>
-      <c r="C63" s="197"/>
-      <c r="D63" s="116">
-        <v>300000</v>
-      </c>
-      <c r="E63" s="180" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="207" t="s">
-        <v>220</v>
-      </c>
-      <c r="B64" s="210"/>
-      <c r="C64" s="51"/>
-      <c r="D64" s="116">
-        <v>150000</v>
-      </c>
-      <c r="E64" s="180" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="65" spans="1:10" ht="39" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="237" t="s">
-        <v>238</v>
-      </c>
-      <c r="B65" s="238"/>
-      <c r="C65" s="51"/>
-      <c r="D65" s="116">
-        <v>300000</v>
-      </c>
-      <c r="E65" s="180"/>
-    </row>
-    <row r="66" spans="1:10" ht="39" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="237" t="s">
-        <v>239</v>
-      </c>
-      <c r="B66" s="238"/>
-      <c r="C66" s="51"/>
-      <c r="D66" s="116">
-        <v>300000</v>
-      </c>
-      <c r="E66" s="180"/>
-    </row>
-    <row r="67" spans="1:10" ht="39" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="237" t="s">
-        <v>240</v>
-      </c>
-      <c r="B67" s="238"/>
-      <c r="C67" s="51"/>
-      <c r="D67" s="116">
-        <v>300000</v>
-      </c>
-      <c r="E67" s="180"/>
-    </row>
-    <row r="68" spans="1:10" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="207" t="s">
-        <v>206</v>
-      </c>
-      <c r="B68" s="210"/>
-      <c r="C68" s="5"/>
-      <c r="D68" s="116">
-        <v>0</v>
-      </c>
-      <c r="E68" s="180" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="69" spans="1:10" ht="22.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="209" t="s">
-        <v>217</v>
-      </c>
-      <c r="B69" s="208"/>
-      <c r="C69" s="5"/>
-      <c r="D69" s="116">
-        <v>481849.77</v>
-      </c>
-      <c r="E69" s="180" t="s">
-        <v>230</v>
-      </c>
-      <c r="I69" s="209"/>
-      <c r="J69" s="208"/>
-    </row>
-    <row r="70" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A70" s="27" t="s">
+      <c r="B73" s="33"/>
+      <c r="C73" s="33"/>
+      <c r="D73" s="32"/>
+      <c r="E73" s="177">
+        <f>SUM(D61:D72)</f>
+        <v>5084200</v>
+      </c>
+    </row>
+    <row r="74" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A74" s="33" t="s">
         <v>40</v>
       </c>
-      <c r="B70" s="33"/>
-      <c r="C70" s="33"/>
-      <c r="D70" s="32"/>
-      <c r="E70" s="177">
-        <f>SUM(D60:D69)</f>
-        <v>2044349.77</v>
-      </c>
-    </row>
-    <row r="71" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A71" s="33" t="s">
-        <v>41</v>
-      </c>
-      <c r="B71" s="67"/>
-      <c r="C71" s="27"/>
-      <c r="D71" s="159"/>
-      <c r="E71" s="176"/>
-    </row>
-    <row r="72" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A72" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B72" s="5"/>
-      <c r="C72" s="5"/>
-      <c r="D72" s="168">
-        <v>187224.98</v>
-      </c>
-      <c r="E72" s="178"/>
-    </row>
-    <row r="73" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A73" s="5" t="s">
-        <v>205</v>
-      </c>
-      <c r="B73" s="5"/>
-      <c r="C73" s="5"/>
-      <c r="D73" s="168"/>
-      <c r="E73" s="118"/>
-      <c r="G73" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="74" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A74" s="50" t="s">
-        <v>19</v>
-      </c>
-      <c r="B74" s="50"/>
-      <c r="C74" s="50"/>
-      <c r="D74" s="119"/>
-      <c r="E74" s="113">
-        <f>SUM(D72:D73)</f>
-        <v>187224.98</v>
-      </c>
-    </row>
-    <row r="75" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A75" s="5"/>
+      <c r="B74" s="67"/>
+      <c r="C74" s="27"/>
+      <c r="D74" s="159"/>
+      <c r="E74" s="176"/>
+    </row>
+    <row r="75" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A75" s="5" t="s">
+        <v>40</v>
+      </c>
       <c r="B75" s="5"/>
       <c r="C75" s="5"/>
-      <c r="D75" s="112"/>
-      <c r="E75" s="120"/>
-    </row>
-    <row r="76" spans="1:10" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A76" s="212" t="s">
-        <v>243</v>
-      </c>
-      <c r="B76" s="213"/>
-      <c r="C76" s="213"/>
-      <c r="D76" s="214"/>
-      <c r="E76" s="121">
+      <c r="D75" s="183">
+        <v>228026.21</v>
+      </c>
+      <c r="E75" s="178"/>
+    </row>
+    <row r="76" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A76" s="5" t="s">
+        <v>204</v>
+      </c>
+      <c r="B76" s="5"/>
+      <c r="C76" s="5"/>
+      <c r="D76" s="168"/>
+      <c r="E76" s="118"/>
+      <c r="G76" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="77" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A77" s="50" t="s">
+        <v>19</v>
+      </c>
+      <c r="B77" s="50"/>
+      <c r="C77" s="50"/>
+      <c r="D77" s="119"/>
+      <c r="E77" s="113">
+        <f>SUM(D75:D76)</f>
+        <v>228026.21</v>
+      </c>
+    </row>
+    <row r="78" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A78" s="5"/>
+      <c r="B78" s="5"/>
+      <c r="C78" s="5"/>
+      <c r="D78" s="112"/>
+      <c r="E78" s="120"/>
+    </row>
+    <row r="79" spans="1:10" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A79" s="219" t="s">
+        <v>214</v>
+      </c>
+      <c r="B79" s="220"/>
+      <c r="C79" s="220"/>
+      <c r="D79" s="221"/>
+      <c r="E79" s="121">
         <v>3500000</v>
       </c>
     </row>
-    <row r="77" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A77" s="1"/>
-      <c r="D77" s="122"/>
-      <c r="E77" s="123"/>
-      <c r="F77" s="42"/>
-    </row>
-    <row r="78" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A78" s="3" t="s">
+    <row r="80" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A80" s="1"/>
+      <c r="D80" s="122"/>
+      <c r="E80" s="123"/>
+      <c r="F80" s="42"/>
+    </row>
+    <row r="81" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A81" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B81" s="10"/>
+      <c r="C81" s="4"/>
+      <c r="D81" s="124"/>
+      <c r="E81" s="196">
+        <f>(SUM(E30:E79))</f>
+        <v>19293883.91</v>
+      </c>
+      <c r="F81" s="151"/>
+      <c r="G81" s="42"/>
+    </row>
+    <row r="82" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D82" s="122"/>
+      <c r="E82" s="122"/>
+      <c r="G82" s="151"/>
+    </row>
+    <row r="83" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D83" s="122"/>
+      <c r="E83" s="122"/>
+    </row>
+    <row r="84" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A84" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="B78" s="10"/>
-      <c r="C78" s="4"/>
-      <c r="D78" s="124"/>
-      <c r="E78" s="198">
-        <f>(SUM(E30:E76))</f>
-        <v>16123528.600000001</v>
-      </c>
-      <c r="F78" s="151"/>
-      <c r="G78" s="42"/>
-    </row>
-    <row r="79" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="D79" s="122"/>
-      <c r="E79" s="122"/>
-      <c r="G79" s="151"/>
-    </row>
-    <row r="80" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D80" s="122"/>
-      <c r="E80" s="122"/>
-    </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A81" s="11" t="s">
+      <c r="B84" s="12"/>
+      <c r="C84" s="13"/>
+      <c r="D84" s="125"/>
+      <c r="E84" s="126"/>
+    </row>
+    <row r="85" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A85" s="207"/>
+      <c r="B85" s="208"/>
+      <c r="C85" s="5"/>
+      <c r="D85" s="141"/>
+      <c r="E85" s="114"/>
+    </row>
+    <row r="86" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A86" s="207"/>
+      <c r="B86" s="208"/>
+      <c r="C86" s="5"/>
+      <c r="D86" s="116"/>
+      <c r="E86" s="114"/>
+    </row>
+    <row r="87" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A87" s="215"/>
+      <c r="B87" s="208"/>
+      <c r="C87" s="5"/>
+      <c r="D87" s="116"/>
+      <c r="E87" s="114"/>
+    </row>
+    <row r="88" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A88" s="115"/>
+      <c r="B88" s="117"/>
+      <c r="C88" s="5"/>
+      <c r="D88" s="116"/>
+      <c r="E88" s="114"/>
+    </row>
+    <row r="89" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A89" s="48"/>
+      <c r="B89" s="47"/>
+      <c r="C89" s="47"/>
+      <c r="D89" s="57"/>
+      <c r="E89" s="57">
+        <f>SUM(D85:D88)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="91" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="92" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A92" s="28" t="s">
         <v>43</v>
       </c>
-      <c r="B81" s="12"/>
-      <c r="C81" s="13"/>
-      <c r="D81" s="125"/>
-      <c r="E81" s="126"/>
-    </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A82" s="209"/>
-      <c r="B82" s="208"/>
-      <c r="C82" s="5"/>
-      <c r="D82" s="141"/>
-      <c r="E82" s="114"/>
-    </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A83" s="209"/>
-      <c r="B83" s="208"/>
-      <c r="C83" s="5"/>
-      <c r="D83" s="116"/>
-      <c r="E83" s="114"/>
-    </row>
-    <row r="84" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A84" s="207"/>
-      <c r="B84" s="208"/>
-      <c r="C84" s="5"/>
-      <c r="D84" s="116"/>
-      <c r="E84" s="114"/>
-    </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A85" s="115"/>
-      <c r="B85" s="117"/>
-      <c r="C85" s="5"/>
-      <c r="D85" s="116"/>
-      <c r="E85" s="114"/>
-    </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A86" s="48"/>
-      <c r="B86" s="47"/>
-      <c r="C86" s="47"/>
-      <c r="D86" s="57"/>
-      <c r="E86" s="57">
-        <f>SUM(D82:D85)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="87" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="88" spans="1:5" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="89" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A89" s="28" t="s">
+      <c r="B92" s="28"/>
+      <c r="C92" s="28"/>
+      <c r="D92" s="29"/>
+      <c r="E92" s="111"/>
+    </row>
+    <row r="93" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="94" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A94" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="B89" s="28"/>
-      <c r="C89" s="28"/>
-      <c r="D89" s="29"/>
-      <c r="E89" s="111"/>
-    </row>
-    <row r="90" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="91" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A91" s="3" t="s">
+      <c r="B94" s="10"/>
+      <c r="C94" s="4"/>
+      <c r="D94" s="4"/>
+      <c r="E94" s="68">
+        <f>E89+E92</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="96" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A96" s="108" t="s">
         <v>45</v>
       </c>
-      <c r="B91" s="10"/>
-      <c r="C91" s="4"/>
-      <c r="D91" s="4"/>
-      <c r="E91" s="68">
-        <f>E86+E89</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="92" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="93" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A93" s="108" t="s">
+      <c r="B96" s="109">
+        <f>E81</f>
+        <v>19293883.91</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A97" s="108" t="s">
         <v>46</v>
       </c>
-      <c r="B93" s="109">
-        <f>E78</f>
-        <v>16123528.600000001</v>
-      </c>
-    </row>
-    <row r="94" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A94" s="108" t="s">
+      <c r="B97" s="109">
+        <f>E81-E79</f>
+        <v>15793883.91</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A98" s="108" t="s">
         <v>47</v>
       </c>
-      <c r="B94" s="109">
-        <f>E78-E76</f>
-        <v>12623528.600000001</v>
-      </c>
-    </row>
-    <row r="95" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A95" s="108" t="s">
+      <c r="B98" s="109">
+        <f>E94-E92</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A99" s="108" t="s">
         <v>48</v>
       </c>
-      <c r="B95" s="109">
-        <f>E91-E89</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="96" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A96" s="108" t="s">
+      <c r="B99" s="109">
+        <f>E94</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" ht="34.5" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="101" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A101" s="217"/>
+      <c r="B101" s="210"/>
+      <c r="C101" s="210"/>
+      <c r="D101" s="210"/>
+      <c r="E101" s="210"/>
+    </row>
+    <row r="102" spans="1:5" ht="106.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A102" s="210"/>
+      <c r="B102" s="210"/>
+      <c r="C102" s="210"/>
+      <c r="D102" s="210"/>
+      <c r="E102" s="210"/>
+    </row>
+    <row r="103" spans="1:5" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A103" s="210"/>
+      <c r="B103" s="210"/>
+      <c r="C103" s="210"/>
+      <c r="D103" s="210"/>
+      <c r="E103" s="210"/>
+    </row>
+    <row r="105" spans="1:5" ht="0.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A105" s="21" t="s">
         <v>49</v>
       </c>
-      <c r="B96" s="109">
-        <f>E91</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97" spans="1:6" ht="34.5" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="98" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A98" s="205"/>
-      <c r="B98" s="206"/>
-      <c r="C98" s="206"/>
-      <c r="D98" s="206"/>
-      <c r="E98" s="206"/>
-    </row>
-    <row r="99" spans="1:6" ht="106.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A99" s="206"/>
-      <c r="B99" s="206"/>
-      <c r="C99" s="206"/>
-      <c r="D99" s="206"/>
-      <c r="E99" s="206"/>
-    </row>
-    <row r="100" spans="1:6" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A100" s="206"/>
-      <c r="B100" s="206"/>
-      <c r="C100" s="206"/>
-      <c r="D100" s="206"/>
-      <c r="E100" s="206"/>
-    </row>
-    <row r="102" spans="1:6" ht="0.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A102" s="21" t="s">
+      <c r="B105" s="137"/>
+      <c r="C105" s="22"/>
+    </row>
+    <row r="106" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A106" s="31"/>
+      <c r="B106" s="58">
+        <v>0</v>
+      </c>
+      <c r="C106" s="24"/>
+    </row>
+    <row r="107" spans="1:5" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A107" s="23" t="s">
         <v>50</v>
       </c>
-      <c r="B102" s="137"/>
-      <c r="C102" s="22"/>
-    </row>
-    <row r="103" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A103" s="31"/>
-      <c r="B103" s="58">
-        <v>0</v>
-      </c>
-      <c r="C103" s="24"/>
-    </row>
-    <row r="104" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A104" s="23" t="s">
+      <c r="B107" s="38">
+        <f>PRORRATEO!I81</f>
+        <v>14136349.759999996</v>
+      </c>
+      <c r="C107" s="22"/>
+    </row>
+    <row r="108" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A108" s="23"/>
+      <c r="B108" s="38">
+        <v>0</v>
+      </c>
+      <c r="C108" s="22"/>
+    </row>
+    <row r="109" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A109" s="23" t="s">
         <v>51</v>
       </c>
-      <c r="B104" s="38">
-        <f>PRORRATEO!I81</f>
-        <v>14195644.699999997</v>
-      </c>
-      <c r="C104" s="22"/>
-    </row>
-    <row r="105" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A105" s="23"/>
-      <c r="B105" s="38">
-        <v>0</v>
-      </c>
-      <c r="C105" s="22"/>
-    </row>
-    <row r="106" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A106" s="23" t="s">
+      <c r="B109" s="118">
+        <f>B131</f>
+        <v>453000</v>
+      </c>
+      <c r="C109" s="22"/>
+    </row>
+    <row r="110" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A110" s="26"/>
+      <c r="B110" s="46"/>
+      <c r="C110" s="22"/>
+    </row>
+    <row r="111" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A111" s="131" t="s">
         <v>52</v>
       </c>
-      <c r="B106" s="118">
-        <f>B129</f>
-        <v>190000</v>
-      </c>
-      <c r="C106" s="22"/>
-    </row>
-    <row r="107" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A107" s="26"/>
-      <c r="B107" s="46"/>
-      <c r="C107" s="22"/>
-    </row>
-    <row r="108" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A108" s="131" t="s">
+      <c r="B111" s="46"/>
+      <c r="C111" s="22"/>
+    </row>
+    <row r="112" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A112" s="37" t="s">
         <v>53</v>
       </c>
-      <c r="B108" s="46"/>
-      <c r="C108" s="22"/>
-    </row>
-    <row r="109" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A109" s="37" t="s">
+      <c r="B112" s="46">
+        <f>-B97</f>
+        <v>-15793883.91</v>
+      </c>
+      <c r="C112" s="22"/>
+    </row>
+    <row r="113" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A113" s="26" t="s">
         <v>54</v>
       </c>
-      <c r="B109" s="46">
-        <f>-B94</f>
-        <v>-12623528.600000001</v>
-      </c>
-      <c r="C109" s="22"/>
-    </row>
-    <row r="110" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A110" s="26" t="s">
+      <c r="B113" s="46">
+        <f>-(B98)</f>
+        <v>0</v>
+      </c>
+      <c r="C113" s="22"/>
+    </row>
+    <row r="114" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A114" s="30" t="s">
+        <v>39</v>
+      </c>
+      <c r="B114" s="58">
+        <f>SUM(B106:B113)</f>
+        <v>-1204534.1500000041</v>
+      </c>
+      <c r="C114" s="25"/>
+      <c r="D114" s="42"/>
+    </row>
+    <row r="115" spans="1:7" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B115" s="39"/>
+      <c r="C115" s="25"/>
+      <c r="D115" s="42"/>
+      <c r="E115" s="138"/>
+      <c r="F115" s="139"/>
+    </row>
+    <row r="116" spans="1:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B116" s="40"/>
+      <c r="C116" s="25"/>
+    </row>
+    <row r="117" spans="1:7" s="36" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B117" s="39"/>
+      <c r="C117" s="35"/>
+    </row>
+    <row r="118" spans="1:7" s="36" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A118" s="143" t="s">
         <v>55</v>
       </c>
-      <c r="B110" s="46">
-        <f>-(B95)</f>
-        <v>0</v>
-      </c>
-      <c r="C110" s="22"/>
-    </row>
-    <row r="111" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A111" s="30" t="s">
-        <v>40</v>
-      </c>
-      <c r="B111" s="58">
-        <f>SUM(B103:B110)</f>
-        <v>1762116.0999999959</v>
-      </c>
-      <c r="C111" s="25"/>
-      <c r="D111" s="42"/>
-    </row>
-    <row r="112" spans="1:6" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B112" s="39"/>
-      <c r="C112" s="25"/>
-      <c r="D112" s="42"/>
-      <c r="E112" s="138"/>
-      <c r="F112" s="139"/>
-    </row>
-    <row r="113" spans="1:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B113" s="40"/>
-      <c r="C113" s="25"/>
-    </row>
-    <row r="114" spans="1:7" s="36" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B114" s="39"/>
-      <c r="C114" s="35"/>
-    </row>
-    <row r="115" spans="1:7" s="36" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A115" s="143" t="s">
-        <v>56</v>
-      </c>
-      <c r="B115" s="144">
-        <v>-160998.50937697478</v>
-      </c>
-      <c r="C115" s="35"/>
-      <c r="D115" s="45"/>
-    </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A116" s="53" t="s">
-        <v>57</v>
-      </c>
-      <c r="B116" s="148">
-        <f>-B94</f>
-        <v>-12623528.600000001</v>
-      </c>
-    </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A117" s="53" t="s">
-        <v>58</v>
-      </c>
-      <c r="B117" s="148">
-        <f>-B95</f>
-        <v>0</v>
-      </c>
-      <c r="G117" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A118" s="53" t="s">
-        <v>59</v>
-      </c>
-      <c r="B118" s="148">
-        <f>B129</f>
-        <v>190000</v>
-      </c>
+      <c r="B118" s="144">
+        <v>1510113.5906230211</v>
+      </c>
+      <c r="C118" s="35"/>
+      <c r="D118" s="45"/>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A119" s="53" t="s">
-        <v>226</v>
-      </c>
-      <c r="B119" s="235">
-        <v>-91004</v>
+        <v>56</v>
+      </c>
+      <c r="B119" s="148">
+        <f>-B97</f>
+        <v>-15793883.91</v>
       </c>
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A120" s="53" t="s">
+        <v>57</v>
+      </c>
+      <c r="B120" s="148">
+        <f>-B98</f>
+        <v>0</v>
+      </c>
+      <c r="G120" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="121" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A121" s="53" t="s">
+        <v>58</v>
+      </c>
+      <c r="B121" s="148">
+        <f>B131</f>
+        <v>453000</v>
+      </c>
+    </row>
+    <row r="122" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A122" s="53" t="s">
+        <v>59</v>
+      </c>
+      <c r="B122" s="149">
+        <f>PRORRATEO!I81</f>
+        <v>14136349.759999996</v>
+      </c>
+    </row>
+    <row r="123" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A123" s="150" t="s">
         <v>60</v>
       </c>
-      <c r="B120" s="149">
-        <f>PRORRATEO!I81</f>
-        <v>14195644.699999997</v>
-      </c>
-    </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A121" s="150" t="s">
+      <c r="B123" s="185"/>
+    </row>
+    <row r="124" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A124" s="146" t="s">
         <v>61</v>
       </c>
-      <c r="B121" s="186"/>
-    </row>
-    <row r="122" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A122" s="146" t="s">
+      <c r="B124" s="147">
+        <f>SUM(B118:C123)</f>
+        <v>305579.44062301703</v>
+      </c>
+      <c r="D124" s="24"/>
+      <c r="F124" s="24"/>
+    </row>
+    <row r="125" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A125" s="145"/>
+      <c r="B125" s="145"/>
+      <c r="F125" s="151"/>
+    </row>
+    <row r="126" spans="1:7" ht="34.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="127" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A127" s="218" t="s">
         <v>62</v>
       </c>
-      <c r="B122" s="147">
-        <f>SUM(B115:C121)</f>
-        <v>1510113.5906230211</v>
-      </c>
-      <c r="D122" s="24"/>
-      <c r="F122" s="24"/>
-    </row>
-    <row r="123" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A123" s="145"/>
-      <c r="B123" s="145"/>
-      <c r="F123" s="151"/>
-    </row>
-    <row r="124" spans="1:7" ht="34.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A125" s="211" t="s">
-        <v>63</v>
-      </c>
-      <c r="B125" s="206"/>
-      <c r="C125" s="206"/>
-    </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A126" s="206"/>
-      <c r="B126" s="206"/>
-      <c r="C126" s="206"/>
-    </row>
-    <row r="127" spans="1:7" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A127" s="128" t="s">
-        <v>241</v>
-      </c>
-      <c r="B127" s="239">
-        <v>190000</v>
-      </c>
-      <c r="C127" s="34">
+      <c r="B127" s="210"/>
+      <c r="C127" s="210"/>
+    </row>
+    <row r="128" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A128" s="210"/>
+      <c r="B128" s="210"/>
+      <c r="C128" s="210"/>
+    </row>
+    <row r="129" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A129" s="128" t="s">
+        <v>244</v>
+      </c>
+      <c r="B129" s="205">
+        <f>246000+107000+100000</f>
+        <v>453000</v>
+      </c>
+      <c r="C129" s="34">
         <v>40000</v>
       </c>
     </row>
-    <row r="128" spans="1:7" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A128" s="128"/>
-      <c r="B128" s="130"/>
-      <c r="C128" s="39"/>
-    </row>
-    <row r="129" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A129" s="43" t="s">
-        <v>40</v>
-      </c>
-      <c r="B129" s="129">
-        <f>SUM(B127:B128)</f>
-        <v>190000</v>
-      </c>
-      <c r="C129" s="44"/>
-    </row>
-    <row r="130" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="M130" s="8"/>
-    </row>
-    <row r="131" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A131" s="205"/>
-      <c r="B131" s="206"/>
-      <c r="C131" s="206"/>
-      <c r="D131" s="206"/>
-      <c r="E131" s="206"/>
+    <row r="130" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A130" s="128"/>
+      <c r="B130" s="130"/>
+      <c r="C130" s="39"/>
+    </row>
+    <row r="131" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A131" s="43" t="s">
+        <v>39</v>
+      </c>
+      <c r="B131" s="129">
+        <f>SUM(B129:B130)</f>
+        <v>453000</v>
+      </c>
+      <c r="C131" s="44"/>
     </row>
     <row r="132" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A132" s="206"/>
-      <c r="B132" s="206"/>
-      <c r="C132" s="206"/>
-      <c r="D132" s="206"/>
-      <c r="E132" s="206"/>
-    </row>
-    <row r="133" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A133" s="206"/>
-      <c r="B133" s="206"/>
-      <c r="C133" s="206"/>
-      <c r="D133" s="206"/>
-      <c r="E133" s="206"/>
+      <c r="M132" s="8"/>
+    </row>
+    <row r="133" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A133" s="217"/>
+      <c r="B133" s="210"/>
+      <c r="C133" s="210"/>
+      <c r="D133" s="210"/>
+      <c r="E133" s="210"/>
     </row>
     <row r="134" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A134" s="206"/>
-      <c r="B134" s="206"/>
-      <c r="C134" s="206"/>
-      <c r="D134" s="206"/>
-      <c r="E134" s="206"/>
+      <c r="A134" s="210"/>
+      <c r="B134" s="210"/>
+      <c r="C134" s="210"/>
+      <c r="D134" s="210"/>
+      <c r="E134" s="210"/>
+    </row>
+    <row r="135" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A135" s="210"/>
+      <c r="B135" s="210"/>
+      <c r="C135" s="210"/>
+      <c r="D135" s="210"/>
+      <c r="E135" s="210"/>
+    </row>
+    <row r="136" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A136" s="210"/>
+      <c r="B136" s="210"/>
+      <c r="C136" s="210"/>
+      <c r="D136" s="210"/>
+      <c r="E136" s="210"/>
     </row>
   </sheetData>
-  <mergeCells count="24">
-    <mergeCell ref="I69:J69"/>
+  <mergeCells count="25">
+    <mergeCell ref="A133:E136"/>
+    <mergeCell ref="A101:E103"/>
+    <mergeCell ref="A87:B87"/>
+    <mergeCell ref="A58:B58"/>
+    <mergeCell ref="A61:B61"/>
+    <mergeCell ref="A86:B86"/>
+    <mergeCell ref="A85:B85"/>
+    <mergeCell ref="A127:C128"/>
+    <mergeCell ref="A79:D79"/>
+    <mergeCell ref="A65:B65"/>
+    <mergeCell ref="I72:J72"/>
     <mergeCell ref="B9:C11"/>
+    <mergeCell ref="A70:B70"/>
+    <mergeCell ref="A72:B72"/>
+    <mergeCell ref="A40:B40"/>
+    <mergeCell ref="A35:B35"/>
+    <mergeCell ref="A14:E17"/>
+    <mergeCell ref="A37:B37"/>
+    <mergeCell ref="A66:B66"/>
+    <mergeCell ref="A71:B71"/>
+    <mergeCell ref="A41:B41"/>
+    <mergeCell ref="A57:B57"/>
     <mergeCell ref="A67:B67"/>
     <mergeCell ref="A69:B69"/>
-    <mergeCell ref="A39:B39"/>
-    <mergeCell ref="A35:B35"/>
-    <mergeCell ref="A14:E17"/>
     <mergeCell ref="A36:B36"/>
-    <mergeCell ref="A63:B63"/>
-    <mergeCell ref="A68:B68"/>
-    <mergeCell ref="A40:B40"/>
-    <mergeCell ref="A56:B56"/>
-    <mergeCell ref="A64:B64"/>
-    <mergeCell ref="A65:B65"/>
-    <mergeCell ref="A66:B66"/>
-    <mergeCell ref="A131:E134"/>
-    <mergeCell ref="A98:E100"/>
-    <mergeCell ref="A84:B84"/>
-    <mergeCell ref="A57:B57"/>
-    <mergeCell ref="A60:B60"/>
-    <mergeCell ref="A83:B83"/>
-    <mergeCell ref="A82:B82"/>
-    <mergeCell ref="A125:C126"/>
-    <mergeCell ref="A76:D76"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -3536,16 +3588,16 @@
       <c r="D1" s="6"/>
       <c r="E1" s="6"/>
       <c r="F1" s="6"/>
-      <c r="G1" s="231"/>
-      <c r="H1" s="206"/>
-      <c r="I1" s="206"/>
-      <c r="J1" s="206"/>
-      <c r="K1" s="206"/>
-      <c r="L1" s="206"/>
-      <c r="M1" s="206"/>
-      <c r="N1" s="206"/>
-      <c r="O1" s="206"/>
-      <c r="P1" s="206"/>
+      <c r="G1" s="228"/>
+      <c r="H1" s="210"/>
+      <c r="I1" s="210"/>
+      <c r="J1" s="210"/>
+      <c r="K1" s="210"/>
+      <c r="L1" s="210"/>
+      <c r="M1" s="210"/>
+      <c r="N1" s="210"/>
+      <c r="O1" s="210"/>
+      <c r="P1" s="210"/>
       <c r="Q1" s="6"/>
       <c r="R1" s="6"/>
     </row>
@@ -3565,17 +3617,17 @@
       <c r="J2" s="6"/>
       <c r="K2" s="6"/>
       <c r="L2" s="6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="M2" s="7"/>
       <c r="N2" s="6"/>
       <c r="O2" s="6"/>
-      <c r="P2" s="228">
+      <c r="P2" s="224">
         <f>U2-P3</f>
         <v>12623528.600000001</v>
       </c>
-      <c r="Q2" s="206"/>
-      <c r="R2" s="206"/>
+      <c r="Q2" s="210"/>
+      <c r="R2" s="210"/>
       <c r="S2" s="20"/>
       <c r="U2">
         <v>16123528.600000001</v>
@@ -3594,128 +3646,128 @@
       <c r="J3" s="6"/>
       <c r="K3" s="6"/>
       <c r="L3" s="6" t="s">
-        <v>245</v>
+        <v>216</v>
       </c>
       <c r="M3" s="6"/>
       <c r="N3" s="6"/>
       <c r="O3" s="6"/>
-      <c r="P3" s="228">
+      <c r="P3" s="224">
         <v>3500000</v>
       </c>
-      <c r="Q3" s="206"/>
-      <c r="R3" s="206"/>
+      <c r="Q3" s="210"/>
+      <c r="R3" s="210"/>
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A4" s="223" t="s">
+      <c r="A4" s="235" t="s">
+        <v>64</v>
+      </c>
+      <c r="B4" s="237" t="s">
         <v>65</v>
       </c>
-      <c r="B4" s="225" t="s">
+      <c r="C4" s="132"/>
+      <c r="D4" s="225" t="s">
         <v>66</v>
       </c>
-      <c r="C4" s="132"/>
-      <c r="D4" s="218" t="s">
+      <c r="E4" s="225" t="s">
         <v>67</v>
       </c>
-      <c r="E4" s="218" t="s">
+      <c r="F4" s="234" t="s">
         <v>68</v>
       </c>
-      <c r="F4" s="220" t="s">
+      <c r="G4" s="225" t="s">
         <v>69</v>
       </c>
-      <c r="G4" s="218" t="s">
+      <c r="H4" s="232" t="s">
         <v>70</v>
       </c>
-      <c r="H4" s="222" t="s">
+      <c r="I4" s="225" t="s">
+        <v>50</v>
+      </c>
+      <c r="J4" s="234" t="s">
         <v>71</v>
       </c>
-      <c r="I4" s="218" t="s">
-        <v>51</v>
-      </c>
-      <c r="J4" s="220" t="s">
+      <c r="K4" s="236" t="s">
         <v>72</v>
       </c>
-      <c r="K4" s="224" t="s">
+      <c r="L4" s="232" t="s">
         <v>73</v>
       </c>
-      <c r="L4" s="222" t="s">
-        <v>74</v>
-      </c>
-      <c r="M4" s="233" t="s">
-        <v>244</v>
-      </c>
-      <c r="N4" s="222" t="s">
+      <c r="M4" s="231" t="s">
+        <v>215</v>
+      </c>
+      <c r="N4" s="232" t="s">
+        <v>75</v>
+      </c>
+      <c r="O4" s="226" t="s">
         <v>76</v>
       </c>
-      <c r="O4" s="229" t="s">
+      <c r="P4" s="62" t="s">
         <v>77</v>
       </c>
-      <c r="P4" s="62" t="s">
+      <c r="Q4" s="229" t="s">
         <v>78</v>
       </c>
-      <c r="Q4" s="232" t="s">
+      <c r="R4" s="222" t="s">
         <v>79</v>
       </c>
-      <c r="R4" s="227" t="s">
-        <v>80</v>
-      </c>
       <c r="U4" s="42"/>
     </row>
     <row r="5" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="219"/>
-      <c r="B5" s="226"/>
+      <c r="A5" s="223"/>
+      <c r="B5" s="230"/>
       <c r="C5" s="133"/>
-      <c r="D5" s="219"/>
-      <c r="E5" s="219"/>
-      <c r="F5" s="221"/>
-      <c r="G5" s="219"/>
-      <c r="H5" s="221"/>
-      <c r="I5" s="219"/>
-      <c r="J5" s="221"/>
-      <c r="K5" s="221"/>
-      <c r="L5" s="221"/>
-      <c r="M5" s="219"/>
-      <c r="N5" s="221"/>
-      <c r="O5" s="230"/>
+      <c r="D5" s="223"/>
+      <c r="E5" s="223"/>
+      <c r="F5" s="233"/>
+      <c r="G5" s="223"/>
+      <c r="H5" s="233"/>
+      <c r="I5" s="223"/>
+      <c r="J5" s="233"/>
+      <c r="K5" s="233"/>
+      <c r="L5" s="233"/>
+      <c r="M5" s="223"/>
+      <c r="N5" s="233"/>
+      <c r="O5" s="227"/>
       <c r="P5" s="60" t="str">
         <f>RESUMEN!B9</f>
-        <v>VTO 15/09</v>
-      </c>
-      <c r="Q5" s="226"/>
-      <c r="R5" s="219"/>
+        <v>VTO 15/10</v>
+      </c>
+      <c r="Q5" s="230"/>
+      <c r="R5" s="223"/>
     </row>
     <row r="6" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B6" s="64"/>
       <c r="C6" s="64" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D6" s="64">
         <v>1</v>
       </c>
       <c r="E6" s="64" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F6" s="64"/>
       <c r="G6" s="71">
         <v>0.5131</v>
       </c>
       <c r="H6" s="72">
-        <v>74326.009999999995</v>
-      </c>
-      <c r="I6" s="73">
-        <f>920334-I13-I7-I47-I48-I59-I69-I73</f>
-        <v>74375.19</v>
+        <v>82681.009999999995</v>
+      </c>
+      <c r="I6" s="247">
+        <f>1024281-I13-I7-I47-I48-I59-I69-I73</f>
+        <v>82680.190000000061</v>
       </c>
       <c r="J6" s="74"/>
       <c r="K6" s="75">
         <f t="shared" ref="K6:K37" si="0">H6-I6</f>
-        <v>-49.180000000007567</v>
+        <v>0.81999999993422534</v>
       </c>
       <c r="L6" s="75">
         <f t="shared" ref="L6:L37" si="1">IF(K6&gt;0,K6*3%,0)</f>
-        <v>0</v>
+        <v>2.4599999998026759E-2</v>
       </c>
       <c r="M6" s="76">
         <f>P$3*G6%</f>
@@ -3730,48 +3782,48 @@
       </c>
       <c r="P6" s="79">
         <f t="shared" ref="P6:P37" si="2">ROUND(SUM(K6:O6),0) + S6</f>
-        <v>82681.009999999995</v>
+        <v>82731.009999999995</v>
       </c>
       <c r="Q6" s="80">
         <f t="shared" ref="Q6:Q37" si="3">ROUND(P6*6% + P6,0) + S6</f>
-        <v>87642.01</v>
+        <v>87695.01</v>
       </c>
       <c r="R6" s="81">
         <f t="shared" ref="R6:R37" si="4">ROUND(P6*3%,0) + P6</f>
-        <v>85161.01</v>
+        <v>85213.01</v>
       </c>
       <c r="S6" s="42">
         <v>0.01</v>
       </c>
       <c r="U6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="7" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B7" s="64"/>
       <c r="C7" s="64" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D7" s="64">
         <f t="shared" ref="D7:D38" si="5">D6+1</f>
         <v>2</v>
       </c>
       <c r="E7" s="64" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F7" s="65"/>
       <c r="G7" s="71">
         <v>0.6119</v>
       </c>
       <c r="H7" s="72">
-        <v>88639.02</v>
-      </c>
-      <c r="I7" s="73">
+        <v>98660.02</v>
+      </c>
+      <c r="I7" s="247">
         <f>H7</f>
-        <v>88639.02</v>
+        <v>98660.02</v>
       </c>
       <c r="J7" s="74"/>
       <c r="K7" s="75">
@@ -3787,7 +3839,7 @@
         <v>21416.5</v>
       </c>
       <c r="N7" s="77">
-        <f t="shared" ref="N6:N37" si="7">P$2*G7%</f>
+        <f t="shared" ref="N7:N37" si="7">P$2*G7%</f>
         <v>77243.37150340002</v>
       </c>
       <c r="O7" s="78">
@@ -3813,7 +3865,7 @@
     </row>
     <row r="8" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B8" s="64">
         <v>1</v>
@@ -3824,18 +3876,18 @@
         <v>3</v>
       </c>
       <c r="E8" s="64" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F8" s="65"/>
       <c r="G8" s="71">
         <v>0.61150000000000004</v>
       </c>
       <c r="H8" s="72">
-        <v>91238.03</v>
-      </c>
-      <c r="I8" s="73">
-        <f t="shared" ref="I7:I13" si="9">H8</f>
-        <v>91238.03</v>
+        <v>101553.03</v>
+      </c>
+      <c r="I8" s="247">
+        <f t="shared" ref="I8:I13" si="9">H8</f>
+        <v>101553.03</v>
       </c>
       <c r="J8" s="74"/>
       <c r="K8" s="75">
@@ -3876,7 +3928,7 @@
     </row>
     <row r="9" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B9" s="64">
         <v>2</v>
@@ -3887,18 +3939,18 @@
         <v>4</v>
       </c>
       <c r="E9" s="64" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F9" s="65"/>
       <c r="G9" s="71">
         <v>0.50329999999999997</v>
       </c>
       <c r="H9" s="72">
-        <v>75094.039999999994</v>
-      </c>
-      <c r="I9" s="73">
+        <v>83585.039999999994</v>
+      </c>
+      <c r="I9" s="247">
         <f t="shared" si="9"/>
-        <v>75094.039999999994</v>
+        <v>83585.039999999994</v>
       </c>
       <c r="J9" s="74"/>
       <c r="K9" s="75">
@@ -3940,7 +3992,7 @@
     </row>
     <row r="10" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B10" s="64">
         <v>3</v>
@@ -3951,18 +4003,18 @@
         <v>5</v>
       </c>
       <c r="E10" s="64" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F10" s="65"/>
       <c r="G10" s="71">
         <v>0.50329999999999997</v>
       </c>
       <c r="H10" s="72">
-        <v>75094.05</v>
-      </c>
-      <c r="I10" s="73">
+        <v>83585.05</v>
+      </c>
+      <c r="I10" s="247">
         <f t="shared" si="9"/>
-        <v>75094.05</v>
+        <v>83585.05</v>
       </c>
       <c r="J10" s="74"/>
       <c r="K10" s="75">
@@ -4004,7 +4056,7 @@
     </row>
     <row r="11" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B11" s="64">
         <v>4</v>
@@ -4015,20 +4067,20 @@
         <v>6</v>
       </c>
       <c r="E11" s="64" t="s">
+        <v>89</v>
+      </c>
+      <c r="F11" s="64" t="s">
         <v>90</v>
-      </c>
-      <c r="F11" s="64" t="s">
-        <v>91</v>
       </c>
       <c r="G11" s="71">
         <v>0.74990000000000001</v>
       </c>
       <c r="H11" s="72">
-        <v>108629.06</v>
-      </c>
-      <c r="I11" s="73">
+        <v>120910.06</v>
+      </c>
+      <c r="I11" s="247">
         <f t="shared" si="9"/>
-        <v>108629.06</v>
+        <v>120910.06</v>
       </c>
       <c r="J11" s="74"/>
       <c r="K11" s="75">
@@ -4069,7 +4121,7 @@
     </row>
     <row r="12" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B12" s="64">
         <v>5</v>
@@ -4080,20 +4132,20 @@
         <v>7</v>
       </c>
       <c r="E12" s="64" t="s">
+        <v>91</v>
+      </c>
+      <c r="F12" s="64" t="s">
         <v>92</v>
-      </c>
-      <c r="F12" s="64" t="s">
-        <v>93</v>
       </c>
       <c r="G12" s="71">
         <v>0.54249999999999998</v>
       </c>
       <c r="H12" s="72">
-        <v>78585.070000000007</v>
-      </c>
-      <c r="I12" s="73">
+        <v>87470.07</v>
+      </c>
+      <c r="I12" s="247">
         <f t="shared" si="9"/>
-        <v>78585.070000000007</v>
+        <v>87470.07</v>
       </c>
       <c r="J12" s="74"/>
       <c r="K12" s="75">
@@ -4134,7 +4186,7 @@
     </row>
     <row r="13" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B13" s="64">
         <v>6</v>
@@ -4145,18 +4197,18 @@
         <v>8</v>
       </c>
       <c r="E13" s="64" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F13" s="65"/>
       <c r="G13" s="71">
         <v>0.45369999999999999</v>
       </c>
       <c r="H13" s="72">
-        <v>65722.080000000002</v>
-      </c>
-      <c r="I13" s="73">
+        <v>73152.08</v>
+      </c>
+      <c r="I13" s="247">
         <f t="shared" si="9"/>
-        <v>65722.080000000002</v>
+        <v>73152.08</v>
       </c>
       <c r="J13" s="74"/>
       <c r="K13" s="75">
@@ -4197,7 +4249,7 @@
     </row>
     <row r="14" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B14" s="64">
         <v>7</v>
@@ -4208,29 +4260,26 @@
         <v>9</v>
       </c>
       <c r="E14" s="64" t="s">
+        <v>95</v>
+      </c>
+      <c r="F14" s="84" t="s">
         <v>96</v>
-      </c>
-      <c r="F14" s="84" t="s">
-        <v>97</v>
       </c>
       <c r="G14" s="71">
         <v>0.52439999999999998</v>
       </c>
       <c r="H14" s="72">
-        <v>7718.09</v>
-      </c>
-      <c r="I14" s="73">
-        <f>H14</f>
-        <v>7718.09</v>
-      </c>
+        <v>84552.09</v>
+      </c>
+      <c r="I14" s="73"/>
       <c r="J14" s="74"/>
       <c r="K14" s="75">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>84552.09</v>
       </c>
       <c r="L14" s="75">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2536.5626999999999</v>
       </c>
       <c r="M14" s="76">
         <f t="shared" si="6"/>
@@ -4245,27 +4294,27 @@
       </c>
       <c r="P14" s="79">
         <f t="shared" si="2"/>
-        <v>84552.09</v>
+        <v>171640.09</v>
       </c>
       <c r="Q14" s="80">
         <f t="shared" si="3"/>
-        <v>89625.09</v>
+        <v>181938.09</v>
       </c>
       <c r="R14" s="81">
         <f t="shared" si="4"/>
-        <v>87089.09</v>
+        <v>176789.09</v>
       </c>
       <c r="S14" s="42">
         <f t="shared" si="8"/>
         <v>0.09</v>
       </c>
       <c r="U14" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="15" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B15" s="64">
         <v>8</v>
@@ -4276,28 +4325,26 @@
         <v>10</v>
       </c>
       <c r="E15" s="64" t="s">
+        <v>95</v>
+      </c>
+      <c r="F15" s="84" t="s">
         <v>96</v>
-      </c>
-      <c r="F15" s="84" t="s">
-        <v>97</v>
       </c>
       <c r="G15" s="71">
         <v>0.42399999999999999</v>
       </c>
       <c r="H15" s="72">
-        <v>-32049.9</v>
-      </c>
-      <c r="I15" s="73">
-        <v>32049.1</v>
-      </c>
+        <v>4265.1000000000004</v>
+      </c>
+      <c r="I15" s="73"/>
       <c r="J15" s="74"/>
       <c r="K15" s="75">
         <f t="shared" si="0"/>
-        <v>-64099</v>
+        <v>4265.1000000000004</v>
       </c>
       <c r="L15" s="75">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>127.953</v>
       </c>
       <c r="M15" s="76">
         <f t="shared" si="6"/>
@@ -4312,57 +4359,57 @@
       </c>
       <c r="P15" s="79">
         <f t="shared" si="2"/>
-        <v>4265.1000000000004</v>
+        <v>72757.100000000006</v>
       </c>
       <c r="Q15" s="80">
         <f t="shared" si="3"/>
-        <v>4521.1000000000004</v>
+        <v>77123.100000000006</v>
       </c>
       <c r="R15" s="81">
         <f t="shared" si="4"/>
-        <v>4393.1000000000004</v>
+        <v>74940.100000000006</v>
       </c>
       <c r="S15" s="42">
         <f t="shared" si="8"/>
         <v>9.9999999999999992E-2</v>
       </c>
       <c r="U15" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="16" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B16" s="64">
         <v>1</v>
       </c>
       <c r="C16" s="64" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D16" s="64">
         <f t="shared" si="5"/>
         <v>11</v>
       </c>
       <c r="E16" s="64" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F16" s="65"/>
       <c r="G16" s="71">
         <v>2.3033000000000001</v>
       </c>
       <c r="H16" s="72">
-        <v>4082280.11</v>
+        <v>4667126.1100000003</v>
       </c>
       <c r="I16" s="73"/>
       <c r="J16" s="74"/>
       <c r="K16" s="75">
         <f t="shared" si="0"/>
-        <v>4082280.11</v>
+        <v>4667126.1100000003</v>
       </c>
       <c r="L16" s="75">
         <f t="shared" si="1"/>
-        <v>122468.40329999999</v>
+        <v>140013.78330000001</v>
       </c>
       <c r="M16" s="76">
         <f t="shared" si="6"/>
@@ -4372,20 +4419,20 @@
         <f t="shared" si="7"/>
         <v>290757.73424380005</v>
       </c>
-      <c r="O16" s="241">
-        <v>91004</v>
+      <c r="O16" s="206">
+        <v>0</v>
       </c>
       <c r="P16" s="79">
         <f t="shared" si="2"/>
-        <v>4667126.1100000003</v>
+        <v>5178513.1100000003</v>
       </c>
       <c r="Q16" s="80">
         <f t="shared" si="3"/>
-        <v>4947154.1100000003</v>
+        <v>5489224.1100000003</v>
       </c>
       <c r="R16" s="81">
         <f t="shared" si="4"/>
-        <v>4807140.1100000003</v>
+        <v>5333868.1100000003</v>
       </c>
       <c r="S16" s="42">
         <f t="shared" si="8"/>
@@ -4394,42 +4441,39 @@
     </row>
     <row r="17" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B17" s="64">
         <v>1</v>
       </c>
       <c r="C17" s="64" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D17" s="64">
         <f t="shared" si="5"/>
         <v>12</v>
       </c>
       <c r="E17" s="64" t="s">
+        <v>103</v>
+      </c>
+      <c r="F17" s="65" t="s">
         <v>104</v>
-      </c>
-      <c r="F17" s="65" t="s">
-        <v>105</v>
       </c>
       <c r="G17" s="71">
         <v>2.7492999999999999</v>
       </c>
       <c r="H17" s="72">
-        <v>398258.12</v>
-      </c>
-      <c r="I17" s="73">
-        <f>H17</f>
-        <v>398258.12</v>
-      </c>
+        <v>443284.12</v>
+      </c>
+      <c r="I17" s="73"/>
       <c r="J17" s="74"/>
       <c r="K17" s="75">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>443284.12</v>
       </c>
       <c r="L17" s="75">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>13298.523599999999</v>
       </c>
       <c r="M17" s="76">
         <f t="shared" si="6"/>
@@ -4444,15 +4488,15 @@
       </c>
       <c r="P17" s="79">
         <f t="shared" si="2"/>
-        <v>443284.12</v>
+        <v>899867.12</v>
       </c>
       <c r="Q17" s="80">
         <f t="shared" si="3"/>
-        <v>469881.12</v>
+        <v>953859.12</v>
       </c>
       <c r="R17" s="81">
         <f t="shared" si="4"/>
-        <v>456583.12</v>
+        <v>926863.12</v>
       </c>
       <c r="S17" s="42">
         <f t="shared" si="8"/>
@@ -4461,33 +4505,33 @@
     </row>
     <row r="18" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B18" s="64">
         <v>2</v>
       </c>
       <c r="C18" s="64" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D18" s="64">
         <f t="shared" si="5"/>
         <v>13</v>
       </c>
       <c r="E18" s="64" t="s">
+        <v>105</v>
+      </c>
+      <c r="F18" s="65" t="s">
         <v>106</v>
-      </c>
-      <c r="F18" s="65" t="s">
-        <v>107</v>
       </c>
       <c r="G18" s="71">
         <v>2.3033000000000001</v>
       </c>
       <c r="H18" s="72">
-        <v>333651.13</v>
-      </c>
-      <c r="I18" s="73">
+        <v>371373.13</v>
+      </c>
+      <c r="I18" s="247">
         <f>H18</f>
-        <v>333651.13</v>
+        <v>371373.13</v>
       </c>
       <c r="J18" s="74"/>
       <c r="K18" s="75">
@@ -4528,42 +4572,41 @@
     </row>
     <row r="19" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B19" s="64">
         <v>2</v>
       </c>
       <c r="C19" s="64" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D19" s="64">
         <f t="shared" si="5"/>
         <v>14</v>
       </c>
       <c r="E19" s="64" t="s">
+        <v>108</v>
+      </c>
+      <c r="F19" s="65" t="s">
         <v>109</v>
-      </c>
-      <c r="F19" s="65" t="s">
-        <v>110</v>
       </c>
       <c r="G19" s="71">
         <v>2.6368</v>
       </c>
       <c r="H19" s="72">
-        <v>980449.14</v>
-      </c>
-      <c r="I19" s="73">
-        <f>40000+200000+350000+40000</f>
-        <v>630000</v>
+        <v>786108.14</v>
+      </c>
+      <c r="I19" s="247">
+        <v>47000.14</v>
       </c>
       <c r="J19" s="74"/>
       <c r="K19" s="75">
         <f t="shared" si="0"/>
-        <v>350449.14</v>
+        <v>739108</v>
       </c>
       <c r="L19" s="75">
         <f t="shared" si="1"/>
-        <v>10513.474200000001</v>
+        <v>22173.239999999998</v>
       </c>
       <c r="M19" s="76">
         <f t="shared" si="6"/>
@@ -4578,51 +4621,51 @@
       </c>
       <c r="P19" s="79">
         <f t="shared" si="2"/>
-        <v>786108.14</v>
+        <v>1186426.1399999999</v>
       </c>
       <c r="Q19" s="80">
         <f t="shared" si="3"/>
-        <v>833275.14</v>
+        <v>1257612.1399999999</v>
       </c>
       <c r="R19" s="81">
         <f t="shared" si="4"/>
-        <v>809691.14</v>
+        <v>1222019.1399999999</v>
       </c>
       <c r="S19" s="42">
         <f t="shared" si="8"/>
         <v>0.13999999999999999</v>
       </c>
       <c r="U19" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="20" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B20" s="64">
         <v>3</v>
       </c>
       <c r="C20" s="64" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D20" s="64">
         <f t="shared" si="5"/>
         <v>15</v>
       </c>
       <c r="E20" s="64" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F20" s="65"/>
       <c r="G20" s="71">
         <v>2.3536999999999999</v>
       </c>
       <c r="H20" s="72">
-        <v>340952.15</v>
-      </c>
-      <c r="I20" s="73">
+        <v>379499.15</v>
+      </c>
+      <c r="I20" s="247">
         <f>H20</f>
-        <v>340952.15</v>
+        <v>379499.15</v>
       </c>
       <c r="J20" s="74"/>
       <c r="K20" s="75">
@@ -4663,33 +4706,33 @@
     </row>
     <row r="21" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B21" s="64">
         <v>3</v>
       </c>
       <c r="C21" s="64" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D21" s="64">
         <f t="shared" si="5"/>
         <v>16</v>
       </c>
       <c r="E21" s="64" t="s">
+        <v>113</v>
+      </c>
+      <c r="F21" s="64" t="s">
         <v>114</v>
-      </c>
-      <c r="F21" s="64" t="s">
-        <v>115</v>
       </c>
       <c r="G21" s="71">
         <v>2.6476999999999999</v>
       </c>
       <c r="H21" s="72">
-        <v>383540.16</v>
-      </c>
-      <c r="I21" s="73">
-        <f>83540.16+300000</f>
-        <v>383540.16000000003</v>
+        <v>426903.16</v>
+      </c>
+      <c r="I21" s="247">
+        <f>H21</f>
+        <v>426903.16</v>
       </c>
       <c r="J21" s="74"/>
       <c r="K21" s="75">
@@ -4731,33 +4774,33 @@
     </row>
     <row r="22" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B22" s="64">
         <v>4</v>
       </c>
       <c r="C22" s="64" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D22" s="64">
         <f t="shared" si="5"/>
         <v>17</v>
       </c>
       <c r="E22" s="64" t="s">
+        <v>115</v>
+      </c>
+      <c r="F22" s="65" t="s">
         <v>116</v>
-      </c>
-      <c r="F22" s="65" t="s">
-        <v>117</v>
       </c>
       <c r="G22" s="71">
         <v>2.3235000000000001</v>
       </c>
       <c r="H22" s="73">
-        <v>336577.17</v>
-      </c>
-      <c r="I22" s="73">
+        <v>374630.17</v>
+      </c>
+      <c r="I22" s="247">
         <f>H22</f>
-        <v>336577.17</v>
+        <v>374630.17</v>
       </c>
       <c r="J22" s="74"/>
       <c r="K22" s="75">
@@ -4798,41 +4841,41 @@
     </row>
     <row r="23" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B23" s="64">
         <v>4</v>
       </c>
       <c r="C23" s="64" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D23" s="64">
         <f t="shared" si="5"/>
         <v>18</v>
       </c>
       <c r="E23" s="64" t="s">
+        <v>118</v>
+      </c>
+      <c r="F23" s="142" t="s">
         <v>119</v>
-      </c>
-      <c r="F23" s="142" t="s">
-        <v>120</v>
       </c>
       <c r="G23" s="71">
         <v>2.6880000000000002</v>
       </c>
       <c r="H23" s="72">
-        <v>401059.18</v>
-      </c>
-      <c r="I23" s="73">
-        <v>389378</v>
+        <v>458795.18</v>
+      </c>
+      <c r="I23" s="247">
+        <v>420000</v>
       </c>
       <c r="J23" s="74"/>
       <c r="K23" s="75">
         <f t="shared" si="0"/>
-        <v>11681.179999999993</v>
+        <v>38795.179999999993</v>
       </c>
       <c r="L23" s="75">
         <f t="shared" si="1"/>
-        <v>350.43539999999979</v>
+        <v>1163.8553999999997</v>
       </c>
       <c r="M23" s="76">
         <f t="shared" si="6"/>
@@ -4847,51 +4890,51 @@
       </c>
       <c r="P23" s="79">
         <f t="shared" si="2"/>
-        <v>445432.18</v>
+        <v>473359.18</v>
       </c>
       <c r="Q23" s="80">
         <f t="shared" si="3"/>
-        <v>472158.18</v>
+        <v>501761.18</v>
       </c>
       <c r="R23" s="81">
         <f t="shared" si="4"/>
-        <v>458795.18</v>
+        <v>487560.18</v>
       </c>
       <c r="S23" s="42">
         <f t="shared" si="8"/>
         <v>0.18000000000000002</v>
       </c>
       <c r="U23" s="152" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="24" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B24" s="64">
         <v>5</v>
       </c>
       <c r="C24" s="64" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D24" s="64">
         <f t="shared" si="5"/>
         <v>19</v>
       </c>
       <c r="E24" s="64" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F24" s="65"/>
       <c r="G24" s="71">
         <v>2.36</v>
       </c>
       <c r="H24" s="72">
-        <v>241865.19</v>
-      </c>
-      <c r="I24" s="73">
+        <v>380515.19</v>
+      </c>
+      <c r="I24" s="247">
         <f>H24</f>
-        <v>241865.19</v>
+        <v>380515.19</v>
       </c>
       <c r="J24" s="74"/>
       <c r="K24" s="75">
@@ -4932,35 +4975,35 @@
     </row>
     <row r="25" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B25" s="64">
         <v>5</v>
       </c>
       <c r="C25" s="64" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D25" s="64">
         <f t="shared" si="5"/>
         <v>20</v>
       </c>
       <c r="E25" s="64" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="F25" s="64"/>
       <c r="G25" s="71">
         <v>2.7183000000000002</v>
       </c>
       <c r="H25" s="72">
-        <v>393382.2</v>
-      </c>
-      <c r="I25" s="73">
-        <v>400000</v>
+        <v>431668.2</v>
+      </c>
+      <c r="I25" s="247">
+        <v>445000</v>
       </c>
       <c r="J25" s="74"/>
       <c r="K25" s="110">
         <f t="shared" si="0"/>
-        <v>-6617.7999999999884</v>
+        <v>-13331.799999999988</v>
       </c>
       <c r="L25" s="75">
         <f t="shared" si="1"/>
@@ -4979,15 +5022,15 @@
       </c>
       <c r="P25" s="79">
         <f t="shared" si="2"/>
-        <v>431668.2</v>
+        <v>424954.2</v>
       </c>
       <c r="Q25" s="80">
         <f t="shared" si="3"/>
-        <v>457568.2</v>
+        <v>450451.20000000001</v>
       </c>
       <c r="R25" s="81">
         <f t="shared" si="4"/>
-        <v>444618.2</v>
+        <v>437703.2</v>
       </c>
       <c r="S25" s="42">
         <f t="shared" si="8"/>
@@ -4996,31 +5039,31 @@
     </row>
     <row r="26" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B26" s="64">
         <v>6</v>
       </c>
       <c r="C26" s="64" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D26" s="64">
         <f t="shared" si="5"/>
         <v>21</v>
       </c>
       <c r="E26" s="64" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F26" s="65"/>
       <c r="G26" s="71">
         <v>2.3033000000000001</v>
       </c>
       <c r="H26" s="72">
-        <v>333651.21000000002</v>
-      </c>
-      <c r="I26" s="73">
+        <v>371373.21</v>
+      </c>
+      <c r="I26" s="247">
         <f>H26</f>
-        <v>333651.21000000002</v>
+        <v>371373.21</v>
       </c>
       <c r="J26" s="74"/>
       <c r="K26" s="75">
@@ -5061,42 +5104,39 @@
     </row>
     <row r="27" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B27" s="64">
         <v>6</v>
       </c>
       <c r="C27" s="64" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D27" s="64">
         <f t="shared" si="5"/>
         <v>22</v>
       </c>
       <c r="E27" s="64" t="s">
+        <v>126</v>
+      </c>
+      <c r="F27" s="84" t="s">
         <v>127</v>
-      </c>
-      <c r="F27" s="84" t="s">
-        <v>128</v>
       </c>
       <c r="G27" s="71">
         <v>2.6360000000000001</v>
       </c>
       <c r="H27" s="72">
-        <v>149378.22</v>
-      </c>
-      <c r="I27" s="73">
-        <f>H27</f>
-        <v>149378.22</v>
-      </c>
+        <v>425016.22</v>
+      </c>
+      <c r="I27" s="73"/>
       <c r="J27" s="74"/>
       <c r="K27" s="75">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>425016.22</v>
       </c>
       <c r="L27" s="75">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>12750.486599999998</v>
       </c>
       <c r="M27" s="76">
         <f t="shared" si="6"/>
@@ -5106,59 +5146,59 @@
         <f t="shared" si="7"/>
         <v>332756.21389600006</v>
       </c>
-      <c r="O27" s="183">
+      <c r="O27" s="182">
         <v>0</v>
       </c>
       <c r="P27" s="79">
         <f t="shared" si="2"/>
-        <v>425016.22</v>
+        <v>862783.22</v>
       </c>
       <c r="Q27" s="80">
         <f t="shared" si="3"/>
-        <v>450517.22</v>
+        <v>914550.22</v>
       </c>
       <c r="R27" s="81">
         <f t="shared" si="4"/>
-        <v>437766.22</v>
+        <v>888666.22</v>
       </c>
       <c r="S27" s="42">
         <f t="shared" si="8"/>
         <v>0.22000000000000006</v>
       </c>
       <c r="T27" s="65" t="s">
+        <v>96</v>
+      </c>
+      <c r="U27" t="s">
         <v>97</v>
-      </c>
-      <c r="U27" t="s">
-        <v>98</v>
       </c>
     </row>
     <row r="28" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B28" s="64">
         <v>7</v>
       </c>
       <c r="C28" s="64" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D28" s="64">
         <f t="shared" si="5"/>
         <v>23</v>
       </c>
       <c r="E28" s="64" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F28" s="65"/>
       <c r="G28" s="71">
         <v>2.3033000000000001</v>
       </c>
       <c r="H28" s="72">
-        <v>328727.23</v>
-      </c>
-      <c r="I28" s="73">
-        <f>300000+28727.23</f>
-        <v>328727.23</v>
+        <v>371373.23</v>
+      </c>
+      <c r="I28" s="247">
+        <f>H28</f>
+        <v>371373.23</v>
       </c>
       <c r="J28" s="74"/>
       <c r="K28" s="75">
@@ -5199,31 +5239,31 @@
     </row>
     <row r="29" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B29" s="64">
         <v>7</v>
       </c>
       <c r="C29" s="64" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D29" s="64">
         <f t="shared" si="5"/>
         <v>24</v>
       </c>
       <c r="E29" s="64" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F29" s="65"/>
       <c r="G29" s="71">
         <v>2.6158999999999999</v>
       </c>
       <c r="H29" s="72">
-        <v>378934.24</v>
-      </c>
-      <c r="I29" s="73">
-        <f t="shared" ref="I29:I34" si="10">H29</f>
-        <v>378934.24</v>
+        <v>421775.24</v>
+      </c>
+      <c r="I29" s="247">
+        <f t="shared" ref="I29:I33" si="10">H29</f>
+        <v>421775.24</v>
       </c>
       <c r="J29" s="74"/>
       <c r="K29" s="75">
@@ -5264,31 +5304,31 @@
     </row>
     <row r="30" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B30" s="64">
         <v>8</v>
       </c>
       <c r="C30" s="64" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D30" s="64">
         <f t="shared" si="5"/>
         <v>25</v>
       </c>
       <c r="E30" s="64" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="F30" s="64"/>
       <c r="G30" s="71">
         <v>2.3536999999999999</v>
       </c>
       <c r="H30" s="72">
-        <v>340952.25</v>
-      </c>
-      <c r="I30" s="73">
+        <v>379499.25</v>
+      </c>
+      <c r="I30" s="247">
         <f t="shared" si="10"/>
-        <v>340952.25</v>
+        <v>379499.25</v>
       </c>
       <c r="J30" s="74"/>
       <c r="K30" s="75">
@@ -5329,33 +5369,33 @@
     </row>
     <row r="31" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B31" s="64">
         <v>8</v>
       </c>
       <c r="C31" s="64" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D31" s="64">
         <f t="shared" si="5"/>
         <v>26</v>
       </c>
       <c r="E31" s="64" t="s">
+        <v>133</v>
+      </c>
+      <c r="F31" s="64" t="s">
         <v>134</v>
-      </c>
-      <c r="F31" s="64" t="s">
-        <v>135</v>
       </c>
       <c r="G31" s="71">
         <v>2.6469</v>
       </c>
       <c r="H31" s="72">
-        <v>383424.26</v>
-      </c>
-      <c r="I31" s="73">
+        <v>426774.26</v>
+      </c>
+      <c r="I31" s="247">
         <f t="shared" si="10"/>
-        <v>383424.26</v>
+        <v>426774.26</v>
       </c>
       <c r="J31" s="74"/>
       <c r="K31" s="75">
@@ -5396,31 +5436,31 @@
     </row>
     <row r="32" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="5" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B32" s="64">
         <v>9</v>
       </c>
       <c r="C32" s="64" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D32" s="64">
         <f t="shared" si="5"/>
         <v>27</v>
       </c>
       <c r="E32" s="64" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F32" s="65"/>
       <c r="G32" s="71">
         <v>2.3536999999999999</v>
       </c>
       <c r="H32" s="72">
-        <v>332213.27</v>
-      </c>
-      <c r="I32" s="73">
+        <v>379499.27</v>
+      </c>
+      <c r="I32" s="247">
         <f>H32</f>
-        <v>332213.27</v>
+        <v>379499.27</v>
       </c>
       <c r="J32" s="74"/>
       <c r="K32" s="75">
@@ -5461,31 +5501,31 @@
     </row>
     <row r="33" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="5" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B33" s="64">
         <v>9</v>
       </c>
       <c r="C33" s="64" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D33" s="64">
         <f t="shared" si="5"/>
         <v>28</v>
       </c>
       <c r="E33" s="64" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F33" s="64"/>
       <c r="G33" s="71">
         <v>2.6663000000000001</v>
       </c>
       <c r="H33" s="72">
-        <v>386235.28</v>
-      </c>
-      <c r="I33" s="73">
+        <v>429902.28</v>
+      </c>
+      <c r="I33" s="247">
         <f t="shared" si="10"/>
-        <v>386235.28</v>
+        <v>429902.28</v>
       </c>
       <c r="J33" s="74"/>
       <c r="K33" s="75">
@@ -5526,33 +5566,33 @@
     </row>
     <row r="34" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="5" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B34" s="64">
         <v>10</v>
       </c>
       <c r="C34" s="64" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D34" s="64">
         <f t="shared" si="5"/>
         <v>29</v>
       </c>
       <c r="E34" s="64" t="s">
+        <v>137</v>
+      </c>
+      <c r="F34" s="64" t="s">
         <v>138</v>
-      </c>
-      <c r="F34" s="64" t="s">
-        <v>139</v>
       </c>
       <c r="G34" s="71">
         <v>2.4476</v>
       </c>
       <c r="H34" s="72">
-        <v>373054.29</v>
-      </c>
-      <c r="I34" s="73">
+        <v>413139.29</v>
+      </c>
+      <c r="I34" s="247">
         <f>H34</f>
-        <v>373054.29</v>
+        <v>413139.29</v>
       </c>
       <c r="J34" s="74"/>
       <c r="K34" s="75">
@@ -5571,7 +5611,7 @@
         <f t="shared" si="7"/>
         <v>308973.48601360008</v>
       </c>
-      <c r="O34" s="187">
+      <c r="O34" s="186">
         <v>18500</v>
       </c>
       <c r="P34" s="79">
@@ -5593,40 +5633,39 @@
     </row>
     <row r="35" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="5" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B35" s="64">
         <v>10</v>
       </c>
       <c r="C35" s="64" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D35" s="64">
         <f t="shared" si="5"/>
         <v>30</v>
       </c>
       <c r="E35" s="64" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F35" s="65"/>
       <c r="G35" s="71">
         <v>2.7183000000000002</v>
       </c>
       <c r="H35" s="72">
-        <v>393767.3</v>
-      </c>
-      <c r="I35" s="73">
-        <f>H35</f>
-        <v>393767.3</v>
+        <v>438286.3</v>
+      </c>
+      <c r="I35" s="247">
+        <v>371260</v>
       </c>
       <c r="J35" s="74"/>
       <c r="K35" s="75">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>67026.299999999988</v>
       </c>
       <c r="L35" s="75">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2010.7889999999995</v>
       </c>
       <c r="M35" s="76">
         <f t="shared" si="6"/>
@@ -5641,15 +5680,15 @@
       </c>
       <c r="P35" s="79">
         <f t="shared" si="2"/>
-        <v>438286.3</v>
+        <v>507323.3</v>
       </c>
       <c r="Q35" s="80">
         <f t="shared" si="3"/>
-        <v>464583.3</v>
+        <v>537763.30000000005</v>
       </c>
       <c r="R35" s="81">
         <f t="shared" si="4"/>
-        <v>451435.3</v>
+        <v>522543.3</v>
       </c>
       <c r="S35" s="42">
         <f t="shared" si="8"/>
@@ -5658,33 +5697,33 @@
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="5" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B36" s="64">
         <v>11</v>
       </c>
       <c r="C36" s="64" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D36" s="64">
         <f t="shared" si="5"/>
         <v>31</v>
       </c>
       <c r="E36" s="64" t="s">
+        <v>140</v>
+      </c>
+      <c r="F36" s="64" t="s">
         <v>141</v>
-      </c>
-      <c r="F36" s="64" t="s">
-        <v>142</v>
       </c>
       <c r="G36" s="71">
         <v>2.3026</v>
       </c>
       <c r="H36" s="73">
-        <v>333550.31</v>
-      </c>
-      <c r="I36" s="73">
+        <v>371260.31</v>
+      </c>
+      <c r="I36" s="247">
         <f>H36</f>
-        <v>333550.31</v>
+        <v>371260.31</v>
       </c>
       <c r="J36" s="82"/>
       <c r="K36" s="75">
@@ -5725,39 +5764,39 @@
     </row>
     <row r="37" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="5" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B37" s="64">
         <v>11</v>
       </c>
       <c r="C37" s="64" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D37" s="64">
         <f t="shared" si="5"/>
         <v>32</v>
       </c>
       <c r="E37" s="64" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F37" s="65"/>
       <c r="G37" s="71">
         <v>2.6562000000000001</v>
       </c>
       <c r="H37" s="72">
-        <v>515847.32</v>
-      </c>
-      <c r="I37" s="73">
-        <v>384772.32</v>
+        <v>563280.31999999995</v>
+      </c>
+      <c r="I37" s="247">
+        <v>428273.23</v>
       </c>
       <c r="J37" s="74"/>
       <c r="K37" s="75">
         <f t="shared" si="0"/>
-        <v>131075</v>
+        <v>135007.08999999997</v>
       </c>
       <c r="L37" s="75">
         <f t="shared" si="1"/>
-        <v>3932.25</v>
+        <v>4050.2126999999987</v>
       </c>
       <c r="M37" s="76">
         <f t="shared" si="6"/>
@@ -5772,15 +5811,15 @@
       </c>
       <c r="P37" s="79">
         <f t="shared" si="2"/>
-        <v>563280.31999999995</v>
+        <v>567330.31999999995</v>
       </c>
       <c r="Q37" s="80">
         <f t="shared" si="3"/>
-        <v>597077.31999999995</v>
+        <v>601370.31999999995</v>
       </c>
       <c r="R37" s="81">
         <f t="shared" si="4"/>
-        <v>580178.31999999995</v>
+        <v>584350.31999999995</v>
       </c>
       <c r="S37" s="42">
         <f t="shared" si="8"/>
@@ -5789,31 +5828,31 @@
     </row>
     <row r="38" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="5" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B38" s="64">
         <v>12</v>
       </c>
       <c r="C38" s="64" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D38" s="64">
         <f t="shared" si="5"/>
         <v>33</v>
       </c>
       <c r="E38" s="64" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F38" s="65"/>
       <c r="G38" s="71">
         <v>2.3342999999999998</v>
       </c>
       <c r="H38" s="72">
-        <v>338142.33</v>
-      </c>
-      <c r="I38" s="73">
-        <f t="shared" ref="I38:I41" si="11">H38</f>
-        <v>338142.33</v>
+        <v>376372.33</v>
+      </c>
+      <c r="I38" s="247">
+        <f t="shared" ref="I38:I40" si="11">H38</f>
+        <v>376372.33</v>
       </c>
       <c r="J38" s="74"/>
       <c r="K38" s="75">
@@ -5854,31 +5893,31 @@
     </row>
     <row r="39" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="5" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B39" s="64">
         <v>12</v>
       </c>
       <c r="C39" s="64" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D39" s="64">
         <f t="shared" ref="D39:D75" si="18">D38+1</f>
         <v>34</v>
       </c>
       <c r="E39" s="64" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F39" s="64"/>
       <c r="G39" s="71">
         <v>2.6259000000000001</v>
       </c>
       <c r="H39" s="72">
-        <v>380382.34</v>
-      </c>
-      <c r="I39" s="73">
+        <v>423388.34</v>
+      </c>
+      <c r="I39" s="247">
         <f t="shared" si="11"/>
-        <v>380382.34</v>
+        <v>423388.34</v>
       </c>
       <c r="J39" s="74"/>
       <c r="K39" s="75">
@@ -5919,33 +5958,33 @@
     </row>
     <row r="40" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="5" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B40" s="64">
         <v>1</v>
       </c>
       <c r="C40" s="64" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D40" s="64">
         <f t="shared" si="18"/>
         <v>35</v>
       </c>
       <c r="E40" s="64" t="s">
+        <v>146</v>
+      </c>
+      <c r="F40" s="65" t="s">
         <v>147</v>
-      </c>
-      <c r="F40" s="65" t="s">
-        <v>148</v>
       </c>
       <c r="G40" s="71">
         <v>1.0069999999999999</v>
       </c>
       <c r="H40" s="72">
-        <v>145872.35</v>
-      </c>
-      <c r="I40" s="73">
+        <v>167235.35</v>
+      </c>
+      <c r="I40" s="247">
         <f t="shared" si="11"/>
-        <v>145872.35</v>
+        <v>167235.35</v>
       </c>
       <c r="J40" s="74"/>
       <c r="K40" s="75">
@@ -5986,41 +6025,42 @@
     </row>
     <row r="41" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="5" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B41" s="64">
         <v>1</v>
       </c>
       <c r="C41" s="64" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D41" s="64">
         <f t="shared" si="18"/>
         <v>36</v>
       </c>
       <c r="E41" s="64" t="s">
+        <v>149</v>
+      </c>
+      <c r="F41" s="65" t="s">
         <v>150</v>
-      </c>
-      <c r="F41" s="65" t="s">
-        <v>151</v>
       </c>
       <c r="G41" s="71">
         <v>0.78120000000000001</v>
       </c>
       <c r="H41" s="73">
-        <v>116558.36</v>
-      </c>
-      <c r="I41" s="73">
-        <v>113163.36</v>
+        <v>133338.35999999999</v>
+      </c>
+      <c r="I41" s="247">
+        <f>H41</f>
+        <v>133338.35999999999</v>
       </c>
       <c r="J41" s="74"/>
       <c r="K41" s="75">
         <f t="shared" si="12"/>
-        <v>3395</v>
+        <v>0</v>
       </c>
       <c r="L41" s="75">
         <f t="shared" si="13"/>
-        <v>101.85</v>
+        <v>0</v>
       </c>
       <c r="M41" s="76">
         <f t="shared" si="6"/>
@@ -6035,22 +6075,22 @@
       </c>
       <c r="P41" s="79">
         <f t="shared" si="15"/>
-        <v>129454.36</v>
+        <v>125957.36</v>
       </c>
       <c r="Q41" s="80">
         <f t="shared" si="16"/>
-        <v>137222.35999999999</v>
+        <v>133515.35999999999</v>
       </c>
       <c r="R41" s="81">
         <f t="shared" si="17"/>
-        <v>133338.35999999999</v>
+        <v>129736.36</v>
       </c>
       <c r="S41" s="42">
         <f t="shared" si="19"/>
         <v>0.36000000000000015</v>
       </c>
       <c r="U41" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="42" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -6059,35 +6099,36 @@
         <v>1</v>
       </c>
       <c r="C42" s="63" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D42" s="64">
         <f t="shared" si="18"/>
         <v>37</v>
       </c>
       <c r="E42" s="63" t="s">
+        <v>149</v>
+      </c>
+      <c r="F42" s="65" t="s">
         <v>150</v>
-      </c>
-      <c r="F42" s="65" t="s">
-        <v>151</v>
       </c>
       <c r="G42" s="85">
         <v>1.2153</v>
       </c>
       <c r="H42" s="72">
-        <v>181327.37</v>
-      </c>
-      <c r="I42" s="73">
-        <v>176047.37</v>
+        <v>207430.37</v>
+      </c>
+      <c r="I42" s="247">
+        <f>H42</f>
+        <v>207430.37</v>
       </c>
       <c r="J42" s="74"/>
       <c r="K42" s="75">
         <f t="shared" si="12"/>
-        <v>5280</v>
+        <v>0</v>
       </c>
       <c r="L42" s="75">
         <f t="shared" si="13"/>
-        <v>158.4</v>
+        <v>0</v>
       </c>
       <c r="M42" s="76">
         <f t="shared" si="6"/>
@@ -6102,22 +6143,22 @@
       </c>
       <c r="P42" s="79">
         <f t="shared" si="15"/>
-        <v>201388.37</v>
+        <v>195949.37</v>
       </c>
       <c r="Q42" s="80">
         <f t="shared" si="16"/>
-        <v>213472.37</v>
+        <v>207706.37</v>
       </c>
       <c r="R42" s="81">
         <f t="shared" si="17"/>
-        <v>207430.37</v>
+        <v>201827.37</v>
       </c>
       <c r="S42" s="42">
         <f t="shared" si="19"/>
         <v>0.37000000000000016</v>
       </c>
       <c r="U42" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="43" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -6125,35 +6166,36 @@
         <v>2</v>
       </c>
       <c r="C43" s="86" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D43" s="64">
         <f t="shared" si="18"/>
         <v>38</v>
       </c>
       <c r="E43" s="63" t="s">
+        <v>153</v>
+      </c>
+      <c r="F43" s="63" t="s">
         <v>154</v>
-      </c>
-      <c r="F43" s="63" t="s">
-        <v>155</v>
       </c>
       <c r="G43" s="85">
         <v>0.95489999999999997</v>
       </c>
       <c r="H43" s="72">
-        <v>142475.38</v>
-      </c>
-      <c r="I43" s="73">
-        <v>138325.38</v>
+        <v>162985.38</v>
+      </c>
+      <c r="I43" s="247">
+        <f>H43</f>
+        <v>162985.38</v>
       </c>
       <c r="J43" s="74"/>
       <c r="K43" s="75">
         <f t="shared" si="12"/>
-        <v>4150</v>
+        <v>0</v>
       </c>
       <c r="L43" s="75">
         <f t="shared" si="13"/>
-        <v>124.5</v>
+        <v>0</v>
       </c>
       <c r="M43" s="76">
         <f t="shared" si="6"/>
@@ -6168,15 +6210,15 @@
       </c>
       <c r="P43" s="79">
         <f t="shared" si="15"/>
-        <v>158238.38</v>
+        <v>153964.38</v>
       </c>
       <c r="Q43" s="80">
         <f t="shared" si="16"/>
-        <v>167733.38</v>
+        <v>163202.38</v>
       </c>
       <c r="R43" s="81">
         <f t="shared" si="17"/>
-        <v>162985.38</v>
+        <v>158583.38</v>
       </c>
       <c r="S43" s="42">
         <f t="shared" si="19"/>
@@ -6188,31 +6230,31 @@
         <v>2</v>
       </c>
       <c r="C44" s="86" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D44" s="64">
         <f t="shared" si="18"/>
         <v>39</v>
       </c>
       <c r="E44" s="63" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F44" s="84"/>
       <c r="G44" s="85">
         <v>0.75519999999999998</v>
       </c>
       <c r="H44" s="72">
-        <v>774365.39</v>
+        <v>919361.39</v>
       </c>
       <c r="I44" s="73"/>
       <c r="J44" s="74"/>
       <c r="K44" s="75">
         <f t="shared" si="12"/>
-        <v>774365.39</v>
+        <v>919361.39</v>
       </c>
       <c r="L44" s="75">
         <f t="shared" si="13"/>
-        <v>23230.9617</v>
+        <v>27580.841700000001</v>
       </c>
       <c r="M44" s="76">
         <f t="shared" si="6"/>
@@ -6227,15 +6269,15 @@
       </c>
       <c r="P44" s="79">
         <f t="shared" si="15"/>
-        <v>919361.39</v>
+        <v>1068707.3899999999</v>
       </c>
       <c r="Q44" s="80">
         <f t="shared" si="16"/>
-        <v>974523.39</v>
+        <v>1132830.3899999999</v>
       </c>
       <c r="R44" s="81">
         <f t="shared" si="17"/>
-        <v>946942.39</v>
+        <v>1100768.3899999999</v>
       </c>
       <c r="S44" s="42">
         <f t="shared" si="19"/>
@@ -6247,27 +6289,27 @@
         <v>2</v>
       </c>
       <c r="C45" s="86" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D45" s="64">
         <f t="shared" si="18"/>
         <v>40</v>
       </c>
       <c r="E45" s="63" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F45" s="63" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="G45" s="85">
         <v>1.1545000000000001</v>
       </c>
       <c r="H45" s="72">
-        <v>162981.4</v>
-      </c>
-      <c r="I45" s="73">
-        <f>H45</f>
-        <v>162981.4</v>
+        <v>186146.4</v>
+      </c>
+      <c r="I45" s="247">
+        <f t="shared" ref="I45:I51" si="20">H45</f>
+        <v>186146.4</v>
       </c>
       <c r="J45" s="74"/>
       <c r="K45" s="75">
@@ -6311,32 +6353,31 @@
         <v>3</v>
       </c>
       <c r="C46" s="86" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D46" s="64">
         <f t="shared" si="18"/>
         <v>41</v>
       </c>
       <c r="E46" s="63" t="s">
+        <v>157</v>
+      </c>
+      <c r="F46" s="63" t="s">
         <v>158</v>
-      </c>
-      <c r="F46" s="63" t="s">
-        <v>159</v>
       </c>
       <c r="G46" s="85">
         <v>0.95489999999999997</v>
       </c>
       <c r="H46" s="72">
-        <v>138930.41</v>
-      </c>
-      <c r="I46" s="73">
-        <f>H46</f>
-        <v>138930.41</v>
+        <v>153964.41</v>
+      </c>
+      <c r="I46" s="247">
+        <v>158583.41</v>
       </c>
       <c r="J46" s="74"/>
       <c r="K46" s="75">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>-4619</v>
       </c>
       <c r="L46" s="75">
         <f t="shared" si="13"/>
@@ -6355,15 +6396,15 @@
       </c>
       <c r="P46" s="79">
         <f t="shared" si="15"/>
-        <v>153964.41</v>
+        <v>149345.41</v>
       </c>
       <c r="Q46" s="80">
         <f t="shared" si="16"/>
-        <v>163202.41</v>
+        <v>158306.41</v>
       </c>
       <c r="R46" s="81">
         <f t="shared" si="17"/>
-        <v>158583.41</v>
+        <v>153825.41</v>
       </c>
       <c r="S46" s="42">
         <f t="shared" si="19"/>
@@ -6375,25 +6416,25 @@
         <v>3</v>
       </c>
       <c r="C47" s="86" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D47" s="64">
         <f t="shared" si="18"/>
         <v>42</v>
       </c>
       <c r="E47" s="63" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F47" s="84"/>
       <c r="G47" s="85">
         <v>0.75519999999999998</v>
       </c>
       <c r="H47" s="72">
-        <v>109397.42</v>
-      </c>
-      <c r="I47" s="73">
-        <f>H47</f>
-        <v>109397.42</v>
+        <v>121765.42</v>
+      </c>
+      <c r="I47" s="247">
+        <f t="shared" si="20"/>
+        <v>121765.42</v>
       </c>
       <c r="J47" s="74"/>
       <c r="K47" s="75">
@@ -6437,25 +6478,25 @@
         <v>3</v>
       </c>
       <c r="C48" s="86" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D48" s="64">
         <f t="shared" si="18"/>
         <v>43</v>
       </c>
       <c r="E48" s="63" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="F48" s="84"/>
       <c r="G48" s="85">
         <v>1.1545000000000001</v>
       </c>
       <c r="H48" s="72">
-        <v>167238.43</v>
-      </c>
-      <c r="I48" s="73">
-        <f>H48</f>
-        <v>167238.43</v>
+        <v>186146.43</v>
+      </c>
+      <c r="I48" s="247">
+        <f t="shared" si="20"/>
+        <v>186146.43</v>
       </c>
       <c r="J48" s="74"/>
       <c r="K48" s="75">
@@ -6499,27 +6540,27 @@
         <v>4</v>
       </c>
       <c r="C49" s="86" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D49" s="64">
         <f t="shared" si="18"/>
         <v>44</v>
       </c>
       <c r="E49" s="63" t="s">
+        <v>161</v>
+      </c>
+      <c r="F49" s="84" t="s">
         <v>162</v>
-      </c>
-      <c r="F49" s="84" t="s">
-        <v>163</v>
       </c>
       <c r="G49" s="85">
         <v>0.95489999999999997</v>
       </c>
       <c r="H49" s="72">
-        <v>138325.44</v>
-      </c>
-      <c r="I49" s="73">
-        <f>H49</f>
-        <v>138325.44</v>
+        <v>153964.44</v>
+      </c>
+      <c r="I49" s="247">
+        <f t="shared" si="20"/>
+        <v>153964.44</v>
       </c>
       <c r="J49" s="74"/>
       <c r="K49" s="75">
@@ -6563,25 +6604,25 @@
         <v>4</v>
       </c>
       <c r="C50" s="86" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D50" s="64">
         <f t="shared" si="18"/>
         <v>45</v>
       </c>
       <c r="E50" s="63" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="F50" s="63"/>
       <c r="G50" s="85">
         <v>0.75519999999999998</v>
       </c>
       <c r="H50" s="72">
-        <v>109395.45</v>
-      </c>
-      <c r="I50" s="73">
-        <f>H50</f>
-        <v>109395.45</v>
+        <v>121765.45</v>
+      </c>
+      <c r="I50" s="247">
+        <f t="shared" si="20"/>
+        <v>121765.45</v>
       </c>
       <c r="J50" s="74"/>
       <c r="K50" s="75">
@@ -6620,7 +6661,7 @@
         <v>0.45000000000000023</v>
       </c>
       <c r="U50" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="51" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -6628,27 +6669,27 @@
         <v>4</v>
       </c>
       <c r="C51" s="86" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D51" s="64">
         <f t="shared" si="18"/>
         <v>46</v>
       </c>
       <c r="E51" s="63" t="s">
+        <v>165</v>
+      </c>
+      <c r="F51" s="63" t="s">
         <v>166</v>
-      </c>
-      <c r="F51" s="63" t="s">
-        <v>167</v>
       </c>
       <c r="G51" s="85">
         <v>1.1545000000000001</v>
       </c>
       <c r="H51" s="72">
-        <v>314417.46000000002</v>
-      </c>
-      <c r="I51" s="73">
-        <f>H51</f>
-        <v>314417.46000000002</v>
+        <v>186146.46</v>
+      </c>
+      <c r="I51" s="247">
+        <f t="shared" si="20"/>
+        <v>186146.46</v>
       </c>
       <c r="J51" s="74"/>
       <c r="K51" s="75">
@@ -6692,35 +6733,35 @@
         <v>5</v>
       </c>
       <c r="C52" s="86" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D52" s="64">
         <f t="shared" si="18"/>
         <v>47</v>
       </c>
       <c r="E52" s="63" t="s">
+        <v>167</v>
+      </c>
+      <c r="F52" s="84" t="s">
         <v>168</v>
-      </c>
-      <c r="F52" s="84" t="s">
-        <v>169</v>
       </c>
       <c r="G52" s="85">
         <v>0.95489999999999997</v>
       </c>
       <c r="H52" s="72">
-        <v>142475.47</v>
-      </c>
-      <c r="I52" s="73">
-        <v>138325.47</v>
+        <v>158238.47</v>
+      </c>
+      <c r="I52" s="247">
+        <v>162945.47</v>
       </c>
       <c r="J52" s="74"/>
       <c r="K52" s="75">
         <f t="shared" si="12"/>
-        <v>4150</v>
+        <v>-4707</v>
       </c>
       <c r="L52" s="75">
         <f t="shared" si="13"/>
-        <v>124.5</v>
+        <v>0</v>
       </c>
       <c r="M52" s="76">
         <f t="shared" si="6"/>
@@ -6735,15 +6776,15 @@
       </c>
       <c r="P52" s="79">
         <f t="shared" si="15"/>
-        <v>158238.47</v>
+        <v>149257.47</v>
       </c>
       <c r="Q52" s="80">
         <f t="shared" si="16"/>
-        <v>167733.47</v>
+        <v>158213.47</v>
       </c>
       <c r="R52" s="81">
         <f t="shared" si="17"/>
-        <v>162985.47</v>
+        <v>153735.47</v>
       </c>
       <c r="S52" s="42">
         <f t="shared" si="19"/>
@@ -6755,31 +6796,32 @@
         <v>5</v>
       </c>
       <c r="C53" s="86" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D53" s="64">
         <f t="shared" si="18"/>
         <v>48</v>
       </c>
       <c r="E53" s="63" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F53" s="63" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="G53" s="85">
         <v>0.75519999999999998</v>
       </c>
       <c r="H53" s="72">
-        <v>109397.48</v>
-      </c>
-      <c r="I53" s="73">
-        <v>109400</v>
+        <v>121762.48</v>
+      </c>
+      <c r="I53" s="247">
+        <f>H53</f>
+        <v>121762.48</v>
       </c>
       <c r="J53" s="74"/>
       <c r="K53" s="75">
         <f t="shared" si="12"/>
-        <v>-2.5200000000040745</v>
+        <v>0</v>
       </c>
       <c r="L53" s="75">
         <f t="shared" si="13"/>
@@ -6798,15 +6840,15 @@
       </c>
       <c r="P53" s="79">
         <f t="shared" si="15"/>
-        <v>121762.48</v>
+        <v>121765.48</v>
       </c>
       <c r="Q53" s="80">
         <f t="shared" si="16"/>
-        <v>129068.48</v>
+        <v>129071.48</v>
       </c>
       <c r="R53" s="81">
         <f t="shared" si="17"/>
-        <v>125415.48</v>
+        <v>125418.48</v>
       </c>
       <c r="S53" s="42">
         <f t="shared" si="19"/>
@@ -6818,27 +6860,27 @@
         <v>5</v>
       </c>
       <c r="C54" s="86" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D54" s="64">
         <f t="shared" si="18"/>
         <v>49</v>
       </c>
       <c r="E54" s="63" t="s">
+        <v>170</v>
+      </c>
+      <c r="F54" s="63" t="s">
         <v>171</v>
-      </c>
-      <c r="F54" s="63" t="s">
-        <v>172</v>
       </c>
       <c r="G54" s="85">
         <v>1.1545000000000001</v>
       </c>
       <c r="H54" s="72">
-        <v>167238.49</v>
-      </c>
-      <c r="I54" s="73">
-        <f t="shared" ref="I52:I59" si="20">H54</f>
-        <v>167238.49</v>
+        <v>186146.49</v>
+      </c>
+      <c r="I54" s="247">
+        <f t="shared" ref="I54:I59" si="21">H54</f>
+        <v>186146.49</v>
       </c>
       <c r="J54" s="74"/>
       <c r="K54" s="75">
@@ -6882,25 +6924,25 @@
         <v>6</v>
       </c>
       <c r="C55" s="86" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D55" s="64">
         <f t="shared" si="18"/>
         <v>50</v>
       </c>
       <c r="E55" s="63" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="F55" s="63"/>
       <c r="G55" s="85">
         <v>0.95489999999999997</v>
       </c>
       <c r="H55" s="72">
-        <v>142475.5</v>
-      </c>
-      <c r="I55" s="73">
+        <v>153964.5</v>
+      </c>
+      <c r="I55" s="247">
         <f>H55</f>
-        <v>142475.5</v>
+        <v>153964.5</v>
       </c>
       <c r="J55" s="74"/>
       <c r="K55" s="75">
@@ -6944,33 +6986,33 @@
         <v>6</v>
       </c>
       <c r="C56" s="86" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D56" s="64">
         <f t="shared" si="18"/>
         <v>51</v>
       </c>
       <c r="E56" s="63" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="F56" s="63"/>
       <c r="G56" s="85">
         <v>0.75519999999999998</v>
       </c>
       <c r="H56" s="72">
-        <v>112375.51</v>
-      </c>
-      <c r="I56" s="73">
-        <v>109397</v>
+        <v>125418.45</v>
+      </c>
+      <c r="I56" s="247">
+        <v>124933</v>
       </c>
       <c r="J56" s="74"/>
       <c r="K56" s="75">
         <f t="shared" si="12"/>
-        <v>2978.5099999999948</v>
+        <v>485.44999999999709</v>
       </c>
       <c r="L56" s="75">
         <f t="shared" si="13"/>
-        <v>89.355299999999843</v>
+        <v>14.563499999999912</v>
       </c>
       <c r="M56" s="76">
         <f t="shared" si="6"/>
@@ -6985,22 +7027,22 @@
       </c>
       <c r="P56" s="79">
         <f t="shared" si="15"/>
-        <v>124833.51</v>
+        <v>122265.51</v>
       </c>
       <c r="Q56" s="80">
         <f t="shared" si="16"/>
-        <v>132324.51</v>
+        <v>129601.51</v>
       </c>
       <c r="R56" s="81">
         <f t="shared" si="17"/>
-        <v>128578.51</v>
+        <v>125933.51</v>
       </c>
       <c r="S56" s="42">
         <f t="shared" si="19"/>
         <v>0.51000000000000023</v>
       </c>
       <c r="U56" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="57" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -7008,29 +7050,30 @@
         <v>6</v>
       </c>
       <c r="C57" s="86" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D57" s="64">
         <f t="shared" si="18"/>
         <v>52</v>
       </c>
       <c r="E57" s="63" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="F57" s="84"/>
       <c r="G57" s="85">
         <v>1.1545000000000001</v>
       </c>
       <c r="H57" s="72">
-        <v>167238.51999999999</v>
-      </c>
-      <c r="I57" s="73">
-        <v>283506</v>
+        <v>69879.520000000004</v>
+      </c>
+      <c r="I57" s="247">
+        <f>H57</f>
+        <v>69879.520000000004</v>
       </c>
       <c r="J57" s="74"/>
       <c r="K57" s="75">
         <f t="shared" si="12"/>
-        <v>-116267.48000000001</v>
+        <v>0</v>
       </c>
       <c r="L57" s="75">
         <f t="shared" si="13"/>
@@ -7049,15 +7092,15 @@
       </c>
       <c r="P57" s="79">
         <f t="shared" si="15"/>
-        <v>69879.520000000004</v>
+        <v>186146.52</v>
       </c>
       <c r="Q57" s="80">
         <f t="shared" si="16"/>
-        <v>74072.52</v>
+        <v>197315.52</v>
       </c>
       <c r="R57" s="81">
         <f t="shared" si="17"/>
-        <v>71975.520000000004</v>
+        <v>191730.52</v>
       </c>
       <c r="S57" s="42">
         <f t="shared" si="19"/>
@@ -7069,25 +7112,25 @@
         <v>7</v>
       </c>
       <c r="C58" s="86" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D58" s="64">
         <f t="shared" si="18"/>
         <v>53</v>
       </c>
       <c r="E58" s="63" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="F58" s="84"/>
       <c r="G58" s="85">
         <v>0.95489999999999997</v>
       </c>
       <c r="H58" s="72">
-        <v>138325.53</v>
-      </c>
-      <c r="I58" s="73">
-        <f t="shared" si="20"/>
-        <v>138325.53</v>
+        <v>153964.53</v>
+      </c>
+      <c r="I58" s="247">
+        <f t="shared" si="21"/>
+        <v>153964.53</v>
       </c>
       <c r="J58" s="74"/>
       <c r="K58" s="75">
@@ -7131,25 +7174,25 @@
         <v>7</v>
       </c>
       <c r="C59" s="86" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D59" s="64">
         <f t="shared" si="18"/>
         <v>54</v>
       </c>
       <c r="E59" s="63" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F59" s="63"/>
       <c r="G59" s="85">
         <v>0.75519999999999998</v>
       </c>
       <c r="H59" s="72">
-        <v>109397.54</v>
-      </c>
-      <c r="I59" s="73">
-        <f t="shared" si="20"/>
-        <v>109397.54</v>
+        <v>121765.54</v>
+      </c>
+      <c r="I59" s="247">
+        <f t="shared" si="21"/>
+        <v>121765.54</v>
       </c>
       <c r="J59" s="74"/>
       <c r="K59" s="75">
@@ -7193,33 +7236,31 @@
         <v>7</v>
       </c>
       <c r="C60" s="86" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D60" s="64">
         <f t="shared" si="18"/>
         <v>55</v>
       </c>
       <c r="E60" s="63" t="s">
-        <v>237</v>
+        <v>212</v>
       </c>
       <c r="F60" s="63"/>
       <c r="G60" s="85">
         <v>1.1545000000000001</v>
       </c>
       <c r="H60" s="72">
-        <v>919383.55</v>
-      </c>
-      <c r="I60" s="73">
-        <v>300000</v>
-      </c>
+        <v>824111.55</v>
+      </c>
+      <c r="I60" s="73"/>
       <c r="J60" s="74"/>
       <c r="K60" s="75">
         <f t="shared" si="12"/>
-        <v>619383.55000000005</v>
+        <v>824111.55</v>
       </c>
       <c r="L60" s="75">
         <f t="shared" si="13"/>
-        <v>18581.5065</v>
+        <v>24723.3465</v>
       </c>
       <c r="M60" s="76">
         <f t="shared" si="6"/>
@@ -7234,15 +7275,15 @@
       </c>
       <c r="P60" s="79">
         <f t="shared" si="15"/>
-        <v>824111.55</v>
+        <v>1034981.55</v>
       </c>
       <c r="Q60" s="80">
         <f t="shared" si="16"/>
-        <v>873558.55</v>
+        <v>1097080.55</v>
       </c>
       <c r="R60" s="81">
         <f t="shared" si="17"/>
-        <v>848834.55</v>
+        <v>1066030.55</v>
       </c>
       <c r="S60" s="42">
         <f t="shared" si="19"/>
@@ -7254,35 +7295,36 @@
         <v>8</v>
       </c>
       <c r="C61" s="86" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D61" s="64">
         <f t="shared" si="18"/>
         <v>56</v>
       </c>
       <c r="E61" s="63" t="s">
+        <v>180</v>
+      </c>
+      <c r="F61" s="84" t="s">
         <v>181</v>
-      </c>
-      <c r="F61" s="84" t="s">
-        <v>182</v>
       </c>
       <c r="G61" s="85">
         <v>0.95489999999999997</v>
       </c>
       <c r="H61" s="72">
-        <v>138325.56</v>
-      </c>
-      <c r="I61" s="73">
-        <v>118186.56</v>
+        <v>174707.56</v>
+      </c>
+      <c r="I61" s="247">
+        <f>H61</f>
+        <v>174707.56</v>
       </c>
       <c r="J61" s="74"/>
       <c r="K61" s="75">
         <f t="shared" si="12"/>
-        <v>20139</v>
+        <v>0</v>
       </c>
       <c r="L61" s="75">
         <f t="shared" si="13"/>
-        <v>604.16999999999996</v>
+        <v>0</v>
       </c>
       <c r="M61" s="76">
         <f t="shared" si="6"/>
@@ -7295,15 +7337,15 @@
       <c r="O61" s="78"/>
       <c r="P61" s="79">
         <f t="shared" si="15"/>
-        <v>174707.56</v>
+        <v>153964.56</v>
       </c>
       <c r="Q61" s="80">
         <f t="shared" si="16"/>
-        <v>185190.56</v>
+        <v>163202.56</v>
       </c>
       <c r="R61" s="81">
         <f t="shared" si="17"/>
-        <v>179948.56</v>
+        <v>158583.56</v>
       </c>
       <c r="S61" s="42">
         <f t="shared" si="19"/>
@@ -7315,35 +7357,35 @@
         <v>8</v>
       </c>
       <c r="C62" s="86" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D62" s="64">
         <f t="shared" si="18"/>
         <v>57</v>
       </c>
       <c r="E62" s="63" t="s">
+        <v>182</v>
+      </c>
+      <c r="F62" s="84" t="s">
         <v>183</v>
-      </c>
-      <c r="F62" s="84" t="s">
-        <v>184</v>
       </c>
       <c r="G62" s="85">
         <v>0.75519999999999998</v>
       </c>
       <c r="H62" s="72">
-        <v>103329.57</v>
-      </c>
-      <c r="I62" s="73">
+        <v>121765.57</v>
+      </c>
+      <c r="I62" s="247">
         <v>103329.57</v>
       </c>
       <c r="J62" s="74"/>
       <c r="K62" s="75">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>18436</v>
       </c>
       <c r="L62" s="75">
         <f t="shared" si="13"/>
-        <v>0</v>
+        <v>553.07999999999993</v>
       </c>
       <c r="M62" s="76">
         <f t="shared" si="6"/>
@@ -7358,15 +7400,15 @@
       </c>
       <c r="P62" s="79">
         <f t="shared" si="15"/>
-        <v>121765.57</v>
+        <v>140754.57</v>
       </c>
       <c r="Q62" s="80">
         <f t="shared" si="16"/>
-        <v>129072.57</v>
+        <v>149200.57</v>
       </c>
       <c r="R62" s="81">
         <f t="shared" si="17"/>
-        <v>125418.57</v>
+        <v>144977.57</v>
       </c>
       <c r="S62" s="42">
         <f t="shared" si="19"/>
@@ -7378,33 +7420,34 @@
         <v>8</v>
       </c>
       <c r="C63" s="86" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D63" s="64">
         <f t="shared" si="18"/>
         <v>58</v>
       </c>
       <c r="E63" s="63" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="F63" s="84"/>
       <c r="G63" s="85">
         <v>1.1545000000000001</v>
       </c>
       <c r="H63" s="72">
-        <v>172255.58</v>
-      </c>
-      <c r="I63" s="73">
-        <v>167238.57999999999</v>
+        <v>191314.58</v>
+      </c>
+      <c r="I63" s="247">
+        <f>H63</f>
+        <v>191314.58</v>
       </c>
       <c r="J63" s="74"/>
       <c r="K63" s="75">
         <f t="shared" si="12"/>
-        <v>5017</v>
+        <v>0</v>
       </c>
       <c r="L63" s="75">
         <f t="shared" si="13"/>
-        <v>150.51</v>
+        <v>0</v>
       </c>
       <c r="M63" s="76">
         <f t="shared" si="6"/>
@@ -7419,15 +7462,15 @@
       </c>
       <c r="P63" s="79">
         <f t="shared" si="15"/>
-        <v>191314.58</v>
+        <v>186146.58</v>
       </c>
       <c r="Q63" s="80">
         <f t="shared" si="16"/>
-        <v>202793.58</v>
+        <v>197315.58</v>
       </c>
       <c r="R63" s="81">
         <f t="shared" si="17"/>
-        <v>197053.58</v>
+        <v>191730.58</v>
       </c>
       <c r="S63" s="42">
         <f t="shared" si="19"/>
@@ -7439,27 +7482,30 @@
         <v>9</v>
       </c>
       <c r="C64" s="86" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D64" s="64">
         <f t="shared" si="18"/>
         <v>59</v>
       </c>
       <c r="E64" s="63" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="F64" s="63"/>
       <c r="G64" s="85">
         <v>0.95489999999999997</v>
       </c>
       <c r="H64" s="72">
-        <v>-133488.41</v>
-      </c>
-      <c r="I64" s="73"/>
+        <v>20475.59</v>
+      </c>
+      <c r="I64" s="247">
+        <f>H64*2</f>
+        <v>40951.18</v>
+      </c>
       <c r="J64" s="74"/>
       <c r="K64" s="75">
         <f t="shared" si="12"/>
-        <v>-133488.41</v>
+        <v>-20475.59</v>
       </c>
       <c r="L64" s="75">
         <f t="shared" si="13"/>
@@ -7478,15 +7524,15 @@
       </c>
       <c r="P64" s="79">
         <f t="shared" si="15"/>
-        <v>20475.59</v>
+        <v>133488.59</v>
       </c>
       <c r="Q64" s="80">
         <f t="shared" si="16"/>
-        <v>21704.59</v>
+        <v>141498.59</v>
       </c>
       <c r="R64" s="81">
         <f t="shared" si="17"/>
-        <v>21089.59</v>
+        <v>137493.59</v>
       </c>
       <c r="S64" s="42">
         <f t="shared" si="19"/>
@@ -7498,25 +7544,25 @@
         <v>9</v>
       </c>
       <c r="C65" s="86" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D65" s="64">
         <f t="shared" si="18"/>
         <v>60</v>
       </c>
       <c r="E65" s="63" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="F65" s="84"/>
       <c r="G65" s="85">
         <v>0.75519999999999998</v>
       </c>
       <c r="H65" s="72">
-        <v>307651.59999999998</v>
-      </c>
-      <c r="I65" s="73">
-        <f>H65</f>
-        <v>307651.59999999998</v>
+        <v>121765.6</v>
+      </c>
+      <c r="I65" s="247">
+        <f t="shared" ref="I65:I70" si="22">H65</f>
+        <v>121765.6</v>
       </c>
       <c r="J65" s="74"/>
       <c r="K65" s="75">
@@ -7555,7 +7601,7 @@
         <v>0.60000000000000031</v>
       </c>
       <c r="U65" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="66" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -7563,25 +7609,25 @@
         <v>9</v>
       </c>
       <c r="C66" s="86" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D66" s="64">
         <f t="shared" si="18"/>
         <v>61</v>
       </c>
       <c r="E66" s="63" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F66" s="63"/>
       <c r="G66" s="85">
         <v>1.1545000000000001</v>
       </c>
       <c r="H66" s="72">
-        <v>167238.60999999999</v>
-      </c>
-      <c r="I66" s="73">
-        <f>H66</f>
-        <v>167238.60999999999</v>
+        <v>186146.61</v>
+      </c>
+      <c r="I66" s="247">
+        <f t="shared" si="22"/>
+        <v>186146.61</v>
       </c>
       <c r="J66" s="74"/>
       <c r="K66" s="75">
@@ -7620,7 +7666,7 @@
         <v>0.61000000000000032</v>
       </c>
       <c r="U66" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="67" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -7628,27 +7674,27 @@
         <v>10</v>
       </c>
       <c r="C67" s="86" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D67" s="64">
         <f t="shared" si="18"/>
         <v>62</v>
       </c>
       <c r="E67" s="63" t="s">
+        <v>191</v>
+      </c>
+      <c r="F67" s="84" t="s">
         <v>192</v>
-      </c>
-      <c r="F67" s="84" t="s">
-        <v>193</v>
       </c>
       <c r="G67" s="85">
         <v>0.95489999999999997</v>
       </c>
       <c r="H67" s="72">
-        <v>138325.62</v>
-      </c>
-      <c r="I67" s="73">
-        <f>H67</f>
-        <v>138325.62</v>
+        <v>153964.62</v>
+      </c>
+      <c r="I67" s="247">
+        <f t="shared" si="22"/>
+        <v>153964.62</v>
       </c>
       <c r="J67" s="74"/>
       <c r="K67" s="75">
@@ -7687,7 +7733,7 @@
         <v>0.62000000000000033</v>
       </c>
       <c r="U67" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="68" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -7695,27 +7741,27 @@
         <v>10</v>
       </c>
       <c r="C68" s="86" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D68" s="64">
         <f t="shared" si="18"/>
         <v>63</v>
       </c>
       <c r="E68" s="63" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F68" s="63" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G68" s="85">
         <v>0.75519999999999998</v>
       </c>
       <c r="H68" s="72">
-        <v>109397.63</v>
-      </c>
-      <c r="I68" s="73">
-        <f>H68</f>
-        <v>109397.63</v>
+        <v>121765.63</v>
+      </c>
+      <c r="I68" s="247">
+        <f t="shared" si="22"/>
+        <v>121765.63</v>
       </c>
       <c r="J68" s="74"/>
       <c r="K68" s="75">
@@ -7759,25 +7805,25 @@
         <v>10</v>
       </c>
       <c r="C69" s="86" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D69" s="64">
         <f t="shared" si="18"/>
         <v>64</v>
       </c>
       <c r="E69" s="63" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F69" s="63"/>
       <c r="G69" s="85">
         <v>1.1545000000000001</v>
       </c>
       <c r="H69" s="72">
-        <v>167238.64000000001</v>
-      </c>
-      <c r="I69" s="73">
-        <f>H69</f>
-        <v>167238.64000000001</v>
+        <v>186146.64</v>
+      </c>
+      <c r="I69" s="247">
+        <f t="shared" si="22"/>
+        <v>186146.64</v>
       </c>
       <c r="J69" s="74"/>
       <c r="K69" s="75">
@@ -7821,33 +7867,33 @@
         <v>11</v>
       </c>
       <c r="C70" s="86" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D70" s="64">
         <f t="shared" si="18"/>
         <v>65</v>
       </c>
       <c r="E70" s="63" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="F70" s="84"/>
       <c r="G70" s="85">
         <v>0.95489999999999997</v>
       </c>
       <c r="H70" s="72">
-        <v>138325.65</v>
-      </c>
-      <c r="I70" s="73">
-        <f>H70</f>
-        <v>138325.65</v>
+        <v>153964.65</v>
+      </c>
+      <c r="I70" s="247">
+        <f t="shared" si="22"/>
+        <v>153964.65</v>
       </c>
       <c r="J70" s="74"/>
       <c r="K70" s="75">
-        <f t="shared" ref="K70:K75" si="21">H70-I70</f>
+        <f t="shared" ref="K70:K75" si="23">H70-I70</f>
         <v>0</v>
       </c>
       <c r="L70" s="75">
-        <f t="shared" ref="L70:L75" si="22">IF(K70&gt;0,K70*3%,0)</f>
+        <f t="shared" ref="L70:L75" si="24">IF(K70&gt;0,K70*3%,0)</f>
         <v>0</v>
       </c>
       <c r="M70" s="76">
@@ -7855,22 +7901,22 @@
         <v>33421.5</v>
       </c>
       <c r="N70" s="77">
-        <f t="shared" ref="N70:N75" si="23">P$2*G70%</f>
+        <f t="shared" ref="N70:N75" si="25">P$2*G70%</f>
         <v>120542.07460140002</v>
       </c>
       <c r="O70" s="78">
         <v>0</v>
       </c>
       <c r="P70" s="79">
-        <f t="shared" ref="P70:P75" si="24">ROUND(SUM(K70:O70),0) + S70</f>
+        <f t="shared" ref="P70:P75" si="26">ROUND(SUM(K70:O70),0) + S70</f>
         <v>153964.65</v>
       </c>
       <c r="Q70" s="80">
-        <f t="shared" ref="Q70:Q75" si="25">ROUND(P70*6% + P70,0) + S70</f>
+        <f t="shared" ref="Q70:Q75" si="27">ROUND(P70*6% + P70,0) + S70</f>
         <v>163203.65</v>
       </c>
       <c r="R70" s="81">
-        <f t="shared" ref="R70:R75" si="26">ROUND(P70*3%,0) + P70</f>
+        <f t="shared" ref="R70:R75" si="28">ROUND(P70*3%,0) + P70</f>
         <v>158583.65</v>
       </c>
       <c r="S70" s="42">
@@ -7883,56 +7929,59 @@
         <v>11</v>
       </c>
       <c r="C71" s="86" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D71" s="64">
         <f t="shared" si="18"/>
         <v>66</v>
       </c>
       <c r="E71" s="63" t="s">
+        <v>196</v>
+      </c>
+      <c r="F71" s="84" t="s">
         <v>197</v>
-      </c>
-      <c r="F71" s="84" t="s">
-        <v>198</v>
       </c>
       <c r="G71" s="85">
         <v>0.75519999999999998</v>
       </c>
       <c r="H71" s="72">
-        <v>302099.65999999997</v>
-      </c>
-      <c r="I71" s="73"/>
+        <v>432928.66</v>
+      </c>
+      <c r="I71" s="247">
+        <f>240226+192702.66</f>
+        <v>432928.66000000003</v>
+      </c>
       <c r="J71" s="74"/>
       <c r="K71" s="75">
-        <f t="shared" si="21"/>
-        <v>302099.65999999997</v>
+        <f t="shared" si="23"/>
+        <v>0</v>
       </c>
       <c r="L71" s="75">
-        <f t="shared" si="22"/>
-        <v>9062.9897999999994</v>
+        <f t="shared" si="24"/>
+        <v>0</v>
       </c>
       <c r="M71" s="76">
-        <f t="shared" ref="M71:M75" si="27">P$3*G71%</f>
+        <f t="shared" ref="M71:M75" si="29">P$3*G71%</f>
         <v>26432</v>
       </c>
       <c r="N71" s="77">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>95332.887987200011</v>
       </c>
       <c r="O71" s="78">
         <v>0</v>
       </c>
       <c r="P71" s="79">
-        <f t="shared" si="24"/>
-        <v>432928.66</v>
+        <f t="shared" si="26"/>
+        <v>121765.66</v>
       </c>
       <c r="Q71" s="80">
-        <f t="shared" si="25"/>
-        <v>458904.66</v>
+        <f t="shared" si="27"/>
+        <v>129072.66</v>
       </c>
       <c r="R71" s="81">
-        <f t="shared" si="26"/>
-        <v>445916.66</v>
+        <f t="shared" si="28"/>
+        <v>125418.66</v>
       </c>
       <c r="S71" s="42">
         <f t="shared" si="19"/>
@@ -7944,56 +7993,56 @@
         <v>11</v>
       </c>
       <c r="C72" s="86" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D72" s="64">
         <f t="shared" si="18"/>
         <v>67</v>
       </c>
       <c r="E72" s="63" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F72" s="63"/>
       <c r="G72" s="85">
         <v>1.1545000000000001</v>
       </c>
       <c r="H72" s="72">
-        <v>162981.67000000001</v>
-      </c>
-      <c r="I72" s="73">
+        <v>186146.67</v>
+      </c>
+      <c r="I72" s="247">
         <f>H72</f>
-        <v>162981.67000000001</v>
+        <v>186146.67</v>
       </c>
       <c r="J72" s="74"/>
       <c r="K72" s="75">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="L72" s="75">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="M72" s="76">
+        <f t="shared" si="29"/>
+        <v>40407.500000000007</v>
+      </c>
+      <c r="N72" s="77">
+        <f t="shared" si="25"/>
+        <v>145738.63768700004</v>
+      </c>
+      <c r="O72" s="78">
+        <v>0</v>
+      </c>
+      <c r="P72" s="79">
+        <f t="shared" si="26"/>
+        <v>186146.67</v>
+      </c>
+      <c r="Q72" s="80">
         <f t="shared" si="27"/>
-        <v>40407.500000000007</v>
-      </c>
-      <c r="N72" s="77">
-        <f t="shared" si="23"/>
-        <v>145738.63768700004</v>
-      </c>
-      <c r="O72" s="78">
-        <v>0</v>
-      </c>
-      <c r="P72" s="79">
-        <f t="shared" si="24"/>
-        <v>186146.67</v>
-      </c>
-      <c r="Q72" s="80">
-        <f t="shared" si="25"/>
         <v>197315.67</v>
       </c>
       <c r="R72" s="81">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>191730.67</v>
       </c>
       <c r="S72" s="42">
@@ -8006,56 +8055,56 @@
         <v>12</v>
       </c>
       <c r="C73" s="87" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D73" s="64">
         <f t="shared" si="18"/>
         <v>68</v>
       </c>
       <c r="E73" s="88" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F73" s="88"/>
       <c r="G73" s="89">
         <v>0.95489999999999997</v>
       </c>
       <c r="H73" s="90">
-        <v>138325.68</v>
-      </c>
-      <c r="I73" s="73">
+        <v>153964.68</v>
+      </c>
+      <c r="I73" s="247">
         <f>H73</f>
-        <v>138325.68</v>
+        <v>153964.68</v>
       </c>
       <c r="J73" s="92"/>
       <c r="K73" s="93">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="L73" s="75">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="M73" s="76">
+        <f t="shared" si="29"/>
+        <v>33421.5</v>
+      </c>
+      <c r="N73" s="94">
+        <f t="shared" si="25"/>
+        <v>120542.07460140002</v>
+      </c>
+      <c r="O73" s="95">
+        <v>0</v>
+      </c>
+      <c r="P73" s="79">
+        <f t="shared" si="26"/>
+        <v>153964.68</v>
+      </c>
+      <c r="Q73" s="80">
         <f t="shared" si="27"/>
-        <v>33421.5</v>
-      </c>
-      <c r="N73" s="94">
-        <f t="shared" si="23"/>
-        <v>120542.07460140002</v>
-      </c>
-      <c r="O73" s="95">
-        <v>0</v>
-      </c>
-      <c r="P73" s="79">
-        <f t="shared" si="24"/>
-        <v>153964.68</v>
-      </c>
-      <c r="Q73" s="80">
-        <f t="shared" si="25"/>
         <v>163203.68</v>
       </c>
       <c r="R73" s="81">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>158583.67999999999</v>
       </c>
       <c r="S73" s="42">
@@ -8068,56 +8117,56 @@
         <v>12</v>
       </c>
       <c r="C74" s="86" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D74" s="64">
         <f t="shared" si="18"/>
         <v>69</v>
       </c>
       <c r="E74" s="64" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F74" s="96"/>
       <c r="G74" s="89">
         <v>0.75519999999999998</v>
       </c>
       <c r="H74" s="90">
-        <v>109397.69</v>
-      </c>
-      <c r="I74" s="73">
+        <v>121765.69</v>
+      </c>
+      <c r="I74" s="247">
         <f>H74</f>
-        <v>109397.69</v>
+        <v>121765.69</v>
       </c>
       <c r="J74" s="92"/>
       <c r="K74" s="93">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="L74" s="75">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="M74" s="76">
+        <f t="shared" si="29"/>
+        <v>26432</v>
+      </c>
+      <c r="N74" s="94">
+        <f t="shared" si="25"/>
+        <v>95332.887987200011</v>
+      </c>
+      <c r="O74" s="95">
+        <v>0</v>
+      </c>
+      <c r="P74" s="79">
+        <f t="shared" si="26"/>
+        <v>121765.69</v>
+      </c>
+      <c r="Q74" s="80">
         <f t="shared" si="27"/>
-        <v>26432</v>
-      </c>
-      <c r="N74" s="94">
-        <f t="shared" si="23"/>
-        <v>95332.887987200011</v>
-      </c>
-      <c r="O74" s="95">
-        <v>0</v>
-      </c>
-      <c r="P74" s="79">
-        <f t="shared" si="24"/>
-        <v>121765.69</v>
-      </c>
-      <c r="Q74" s="80">
-        <f t="shared" si="25"/>
         <v>129072.69</v>
       </c>
       <c r="R74" s="81">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>125418.69</v>
       </c>
       <c r="S74" s="42">
@@ -8130,56 +8179,56 @@
         <v>12</v>
       </c>
       <c r="C75" s="86" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D75" s="64">
         <f t="shared" si="18"/>
         <v>70</v>
       </c>
       <c r="E75" s="64" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="F75" s="96"/>
       <c r="G75" s="89">
         <v>1.1549</v>
       </c>
       <c r="H75" s="90">
-        <v>167296.70000000001</v>
-      </c>
-      <c r="I75" s="73">
+        <v>186211.7</v>
+      </c>
+      <c r="I75" s="247">
         <f>H75</f>
-        <v>167296.70000000001</v>
+        <v>186211.7</v>
       </c>
       <c r="J75" s="92"/>
       <c r="K75" s="93">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="L75" s="75">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="M75" s="76">
+        <f t="shared" si="29"/>
+        <v>40421.5</v>
+      </c>
+      <c r="N75" s="94">
+        <f t="shared" si="25"/>
+        <v>145789.13180140001</v>
+      </c>
+      <c r="O75" s="95">
+        <v>0</v>
+      </c>
+      <c r="P75" s="79">
+        <f t="shared" si="26"/>
+        <v>186211.7</v>
+      </c>
+      <c r="Q75" s="80">
         <f t="shared" si="27"/>
-        <v>40421.5</v>
-      </c>
-      <c r="N75" s="94">
-        <f t="shared" si="23"/>
-        <v>145789.13180140001</v>
-      </c>
-      <c r="O75" s="95">
-        <v>0</v>
-      </c>
-      <c r="P75" s="79">
-        <f t="shared" si="24"/>
-        <v>186211.7</v>
-      </c>
-      <c r="Q75" s="80">
-        <f t="shared" si="25"/>
         <v>197384.7</v>
       </c>
       <c r="R75" s="81">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>191797.7</v>
       </c>
       <c r="S75" s="42">
@@ -8299,11 +8348,11 @@
       </c>
       <c r="H81" s="52">
         <f>SUM(H6:H80)</f>
-        <v>20191563.850000001</v>
+        <v>22459791.789999999</v>
       </c>
       <c r="I81" s="61">
         <f>SUM(I6:I80)</f>
-        <v>14195644.699999997</v>
+        <v>14136349.759999996</v>
       </c>
       <c r="J81" s="52">
         <f>SUM(J6:J80)</f>
@@ -8311,7 +8360,7 @@
       </c>
       <c r="K81" s="61">
         <f>SUM(K6:K80)</f>
-        <v>5995919.1499999985</v>
+        <v>8323442.0299999993</v>
       </c>
       <c r="L81" s="61"/>
       <c r="M81" s="61">
@@ -8324,15 +8373,15 @@
       </c>
       <c r="O81" s="61">
         <f>SUM(O6:O80)</f>
-        <v>109504</v>
+        <v>18500</v>
       </c>
       <c r="P81" s="106">
         <f>SUM(P6:P80)</f>
-        <v>22418471.850000001</v>
+        <v>24716492.850000001</v>
       </c>
       <c r="Q81" s="106">
         <f>SUM(Q6:Q80)</f>
-        <v>23763602.850000001</v>
+        <v>26199503.850000001</v>
       </c>
       <c r="R81" s="106"/>
     </row>
@@ -8342,103 +8391,94 @@
     </row>
     <row r="83" spans="2:18" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="84" spans="2:18" ht="9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E84" s="205" t="str">
+      <c r="E84" s="217" t="str">
         <f>RESUMEN!A14</f>
         <v>ESTIMADOS PROPIETARIOS E INQUILINOS: POR FAVOR LOS QUE ABONAN EN PRIMER VENCIMIENTO ABONEN EL MONTO DE PRIMER VENCIMIENTO, ASI AGILIZAN LA LIQUIDACION, RESPETEN LOS CENTAVOS CORRESPONDIENTES A LA UNIDAD FUNCIONAL. ES DE CARÁCTER OBLIGATORIO INFORMAR VIA MAIL LAS EXPENSAS. CASO CONTRARIO SE INFORMARA VIA CARTA DOCUMENTO A LA UNIDAD FUNCIONAL QUE CREEMOS QUE CORRESPONDE, CUYO COSTO SERA IMPUTADO A LA UNIDAD FUNCIONAL SOSPECHADA.</v>
       </c>
-      <c r="F84" s="206"/>
-      <c r="G84" s="206"/>
-      <c r="H84" s="206"/>
-      <c r="I84" s="206"/>
-      <c r="J84" s="206"/>
-      <c r="K84" s="206"/>
-      <c r="L84" s="206"/>
-      <c r="M84" s="206"/>
-      <c r="N84" s="206"/>
-      <c r="O84" s="206"/>
-      <c r="P84" s="206"/>
+      <c r="F84" s="210"/>
+      <c r="G84" s="210"/>
+      <c r="H84" s="210"/>
+      <c r="I84" s="210"/>
+      <c r="J84" s="210"/>
+      <c r="K84" s="210"/>
+      <c r="L84" s="210"/>
+      <c r="M84" s="210"/>
+      <c r="N84" s="210"/>
+      <c r="O84" s="210"/>
+      <c r="P84" s="210"/>
     </row>
     <row r="85" spans="2:18" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E85" s="206"/>
-      <c r="F85" s="206"/>
-      <c r="G85" s="206"/>
-      <c r="H85" s="206"/>
-      <c r="I85" s="206"/>
-      <c r="J85" s="206"/>
-      <c r="K85" s="206"/>
-      <c r="L85" s="206"/>
-      <c r="M85" s="206"/>
-      <c r="N85" s="206"/>
-      <c r="O85" s="206"/>
-      <c r="P85" s="206"/>
+      <c r="E85" s="210"/>
+      <c r="F85" s="210"/>
+      <c r="G85" s="210"/>
+      <c r="H85" s="210"/>
+      <c r="I85" s="210"/>
+      <c r="J85" s="210"/>
+      <c r="K85" s="210"/>
+      <c r="L85" s="210"/>
+      <c r="M85" s="210"/>
+      <c r="N85" s="210"/>
+      <c r="O85" s="210"/>
+      <c r="P85" s="210"/>
     </row>
     <row r="86" spans="2:18" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E86" s="206"/>
-      <c r="F86" s="206"/>
-      <c r="G86" s="206"/>
-      <c r="H86" s="206"/>
-      <c r="I86" s="206"/>
-      <c r="J86" s="206"/>
-      <c r="K86" s="206"/>
-      <c r="L86" s="206"/>
-      <c r="M86" s="206"/>
-      <c r="N86" s="206"/>
-      <c r="O86" s="206"/>
-      <c r="P86" s="206"/>
+      <c r="E86" s="210"/>
+      <c r="F86" s="210"/>
+      <c r="G86" s="210"/>
+      <c r="H86" s="210"/>
+      <c r="I86" s="210"/>
+      <c r="J86" s="210"/>
+      <c r="K86" s="210"/>
+      <c r="L86" s="210"/>
+      <c r="M86" s="210"/>
+      <c r="N86" s="210"/>
+      <c r="O86" s="210"/>
+      <c r="P86" s="210"/>
     </row>
     <row r="87" spans="2:18" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E87" s="206"/>
-      <c r="F87" s="206"/>
-      <c r="G87" s="206"/>
-      <c r="H87" s="206"/>
-      <c r="I87" s="206"/>
-      <c r="J87" s="206"/>
-      <c r="K87" s="206"/>
-      <c r="L87" s="206"/>
-      <c r="M87" s="206"/>
-      <c r="N87" s="206"/>
-      <c r="O87" s="206"/>
-      <c r="P87" s="206"/>
+      <c r="E87" s="210"/>
+      <c r="F87" s="210"/>
+      <c r="G87" s="210"/>
+      <c r="H87" s="210"/>
+      <c r="I87" s="210"/>
+      <c r="J87" s="210"/>
+      <c r="K87" s="210"/>
+      <c r="L87" s="210"/>
+      <c r="M87" s="210"/>
+      <c r="N87" s="210"/>
+      <c r="O87" s="210"/>
+      <c r="P87" s="210"/>
     </row>
     <row r="88" spans="2:18" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E88" s="206"/>
-      <c r="F88" s="206"/>
-      <c r="G88" s="206"/>
-      <c r="H88" s="206"/>
-      <c r="I88" s="206"/>
-      <c r="J88" s="206"/>
-      <c r="K88" s="206"/>
-      <c r="L88" s="206"/>
-      <c r="M88" s="206"/>
-      <c r="N88" s="206"/>
-      <c r="O88" s="206"/>
-      <c r="P88" s="206"/>
+      <c r="E88" s="210"/>
+      <c r="F88" s="210"/>
+      <c r="G88" s="210"/>
+      <c r="H88" s="210"/>
+      <c r="I88" s="210"/>
+      <c r="J88" s="210"/>
+      <c r="K88" s="210"/>
+      <c r="L88" s="210"/>
+      <c r="M88" s="210"/>
+      <c r="N88" s="210"/>
+      <c r="O88" s="210"/>
+      <c r="P88" s="210"/>
     </row>
     <row r="89" spans="2:18" ht="67.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E89" s="206"/>
-      <c r="F89" s="206"/>
-      <c r="G89" s="206"/>
-      <c r="H89" s="206"/>
-      <c r="I89" s="206"/>
-      <c r="J89" s="206"/>
-      <c r="K89" s="206"/>
-      <c r="L89" s="206"/>
-      <c r="M89" s="206"/>
-      <c r="N89" s="206"/>
-      <c r="O89" s="206"/>
-      <c r="P89" s="206"/>
+      <c r="E89" s="210"/>
+      <c r="F89" s="210"/>
+      <c r="G89" s="210"/>
+      <c r="H89" s="210"/>
+      <c r="I89" s="210"/>
+      <c r="J89" s="210"/>
+      <c r="K89" s="210"/>
+      <c r="L89" s="210"/>
+      <c r="M89" s="210"/>
+      <c r="N89" s="210"/>
+      <c r="O89" s="210"/>
+      <c r="P89" s="210"/>
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="R4:R5"/>
-    <mergeCell ref="P2:R2"/>
-    <mergeCell ref="E4:E5"/>
-    <mergeCell ref="O4:O5"/>
-    <mergeCell ref="G1:P1"/>
-    <mergeCell ref="Q4:Q5"/>
-    <mergeCell ref="M4:M5"/>
-    <mergeCell ref="N4:N5"/>
-    <mergeCell ref="P3:R3"/>
     <mergeCell ref="E84:P89"/>
     <mergeCell ref="D4:D5"/>
     <mergeCell ref="J4:J5"/>
@@ -8450,6 +8490,15 @@
     <mergeCell ref="B4:B5"/>
     <mergeCell ref="F4:F5"/>
     <mergeCell ref="H4:H5"/>
+    <mergeCell ref="R4:R5"/>
+    <mergeCell ref="P2:R2"/>
+    <mergeCell ref="E4:E5"/>
+    <mergeCell ref="O4:O5"/>
+    <mergeCell ref="G1:P1"/>
+    <mergeCell ref="Q4:Q5"/>
+    <mergeCell ref="M4:M5"/>
+    <mergeCell ref="N4:N5"/>
+    <mergeCell ref="P3:R3"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="3" orientation="landscape" r:id="rId1"/>
@@ -8504,16 +8553,16 @@
       <c r="D1" s="6"/>
       <c r="E1" s="6"/>
       <c r="F1" s="6"/>
-      <c r="G1" s="231"/>
-      <c r="H1" s="206"/>
-      <c r="I1" s="206"/>
-      <c r="J1" s="206"/>
-      <c r="K1" s="206"/>
-      <c r="L1" s="206"/>
-      <c r="M1" s="206"/>
-      <c r="N1" s="206"/>
-      <c r="O1" s="206"/>
-      <c r="P1" s="206"/>
+      <c r="G1" s="228"/>
+      <c r="H1" s="210"/>
+      <c r="I1" s="210"/>
+      <c r="J1" s="210"/>
+      <c r="K1" s="210"/>
+      <c r="L1" s="210"/>
+      <c r="M1" s="210"/>
+      <c r="N1" s="210"/>
+      <c r="O1" s="210"/>
+      <c r="P1" s="210"/>
       <c r="Q1" s="6"/>
       <c r="R1" s="6"/>
     </row>
@@ -8523,7 +8572,7 @@
       <c r="C2" s="6"/>
       <c r="D2" s="6"/>
       <c r="E2" s="6" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="F2" s="6"/>
       <c r="G2" s="6"/>
@@ -8532,17 +8581,17 @@
       <c r="J2" s="6"/>
       <c r="K2" s="6"/>
       <c r="L2" s="6" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="M2" s="7"/>
       <c r="N2" s="6"/>
       <c r="O2" s="6"/>
-      <c r="P2" s="228">
+      <c r="P2" s="224">
         <f>16770000+7700000</f>
         <v>24470000</v>
       </c>
-      <c r="Q2" s="206"/>
-      <c r="R2" s="206"/>
+      <c r="Q2" s="210"/>
+      <c r="R2" s="210"/>
       <c r="S2" s="20"/>
     </row>
     <row r="3" spans="1:21" ht="12.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -8566,91 +8615,91 @@
       <c r="R3" s="59"/>
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A4" s="223" t="s">
+      <c r="A4" s="235" t="s">
+        <v>64</v>
+      </c>
+      <c r="B4" s="237" t="s">
         <v>65</v>
       </c>
-      <c r="B4" s="225" t="s">
+      <c r="C4" s="132"/>
+      <c r="D4" s="225" t="s">
         <v>66</v>
       </c>
-      <c r="C4" s="132"/>
-      <c r="D4" s="218" t="s">
+      <c r="E4" s="225" t="s">
         <v>67</v>
       </c>
-      <c r="E4" s="218" t="s">
+      <c r="F4" s="234" t="s">
         <v>68</v>
       </c>
-      <c r="F4" s="220" t="s">
+      <c r="G4" s="225" t="s">
         <v>69</v>
       </c>
-      <c r="G4" s="218" t="s">
+      <c r="H4" s="232" t="s">
         <v>70</v>
       </c>
-      <c r="H4" s="222" t="s">
+      <c r="I4" s="225" t="s">
+        <v>50</v>
+      </c>
+      <c r="J4" s="234" t="s">
         <v>71</v>
       </c>
-      <c r="I4" s="218" t="s">
-        <v>51</v>
-      </c>
-      <c r="J4" s="220" t="s">
+      <c r="K4" s="236" t="s">
         <v>72</v>
       </c>
-      <c r="K4" s="224" t="s">
+      <c r="L4" s="232" t="s">
         <v>73</v>
       </c>
-      <c r="L4" s="222" t="s">
+      <c r="M4" s="231" t="s">
         <v>74</v>
       </c>
-      <c r="M4" s="233" t="s">
-        <v>75</v>
-      </c>
-      <c r="N4" s="222" t="s">
-        <v>212</v>
-      </c>
-      <c r="O4" s="229"/>
-      <c r="P4" s="227" t="s">
+      <c r="N4" s="232" t="s">
+        <v>209</v>
+      </c>
+      <c r="O4" s="226"/>
+      <c r="P4" s="222" t="s">
+        <v>77</v>
+      </c>
+      <c r="Q4" s="229" t="s">
         <v>78</v>
       </c>
-      <c r="Q4" s="232" t="s">
+      <c r="R4" s="222" t="s">
         <v>79</v>
       </c>
-      <c r="R4" s="227" t="s">
-        <v>80</v>
-      </c>
       <c r="U4" s="42"/>
     </row>
     <row r="5" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="219"/>
-      <c r="B5" s="226"/>
+      <c r="A5" s="223"/>
+      <c r="B5" s="230"/>
       <c r="C5" s="133"/>
-      <c r="D5" s="219"/>
-      <c r="E5" s="219"/>
-      <c r="F5" s="221"/>
-      <c r="G5" s="219"/>
-      <c r="H5" s="221"/>
-      <c r="I5" s="219"/>
-      <c r="J5" s="221"/>
-      <c r="K5" s="221"/>
-      <c r="L5" s="221"/>
-      <c r="M5" s="219"/>
-      <c r="N5" s="221"/>
-      <c r="O5" s="230"/>
-      <c r="P5" s="234"/>
-      <c r="Q5" s="226"/>
-      <c r="R5" s="219"/>
+      <c r="D5" s="223"/>
+      <c r="E5" s="223"/>
+      <c r="F5" s="233"/>
+      <c r="G5" s="223"/>
+      <c r="H5" s="233"/>
+      <c r="I5" s="223"/>
+      <c r="J5" s="233"/>
+      <c r="K5" s="233"/>
+      <c r="L5" s="233"/>
+      <c r="M5" s="223"/>
+      <c r="N5" s="233"/>
+      <c r="O5" s="227"/>
+      <c r="P5" s="238"/>
+      <c r="Q5" s="230"/>
+      <c r="R5" s="223"/>
     </row>
     <row r="6" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B6" s="64"/>
       <c r="C6" s="64" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D6" s="64">
         <v>1</v>
       </c>
       <c r="E6" s="64" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F6" s="64"/>
       <c r="G6" s="71">
@@ -8687,23 +8736,23 @@
         <v>0.01</v>
       </c>
       <c r="U6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="7" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B7" s="64"/>
       <c r="C7" s="64" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D7" s="64">
         <f t="shared" ref="D7:D70" si="4">D6+1</f>
         <v>2</v>
       </c>
       <c r="E7" s="64" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F7" s="65"/>
       <c r="G7" s="71">
@@ -8744,7 +8793,7 @@
     </row>
     <row r="8" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B8" s="64">
         <v>1</v>
@@ -8755,7 +8804,7 @@
         <v>3</v>
       </c>
       <c r="E8" s="64" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F8" s="65"/>
       <c r="G8" s="71">
@@ -8795,7 +8844,7 @@
     </row>
     <row r="9" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B9" s="64">
         <v>2</v>
@@ -8806,7 +8855,7 @@
         <v>4</v>
       </c>
       <c r="E9" s="64" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F9" s="65"/>
       <c r="G9" s="71">
@@ -8847,7 +8896,7 @@
     </row>
     <row r="10" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B10" s="64">
         <v>3</v>
@@ -8858,7 +8907,7 @@
         <v>5</v>
       </c>
       <c r="E10" s="64" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F10" s="65"/>
       <c r="G10" s="71">
@@ -8899,7 +8948,7 @@
     </row>
     <row r="11" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B11" s="64">
         <v>4</v>
@@ -8910,10 +8959,10 @@
         <v>6</v>
       </c>
       <c r="E11" s="64" t="s">
+        <v>89</v>
+      </c>
+      <c r="F11" s="64" t="s">
         <v>90</v>
-      </c>
-      <c r="F11" s="64" t="s">
-        <v>91</v>
       </c>
       <c r="G11" s="71">
         <v>0.74990000000000001</v>
@@ -8952,7 +9001,7 @@
     </row>
     <row r="12" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B12" s="64">
         <v>5</v>
@@ -8963,10 +9012,10 @@
         <v>7</v>
       </c>
       <c r="E12" s="64" t="s">
+        <v>91</v>
+      </c>
+      <c r="F12" s="64" t="s">
         <v>92</v>
-      </c>
-      <c r="F12" s="64" t="s">
-        <v>93</v>
       </c>
       <c r="G12" s="71">
         <v>0.54249999999999998</v>
@@ -9005,7 +9054,7 @@
     </row>
     <row r="13" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B13" s="64">
         <v>6</v>
@@ -9016,7 +9065,7 @@
         <v>8</v>
       </c>
       <c r="E13" s="64" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F13" s="65"/>
       <c r="G13" s="71">
@@ -9056,7 +9105,7 @@
     </row>
     <row r="14" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B14" s="64">
         <v>7</v>
@@ -9067,10 +9116,10 @@
         <v>9</v>
       </c>
       <c r="E14" s="64" t="s">
+        <v>95</v>
+      </c>
+      <c r="F14" s="84" t="s">
         <v>96</v>
-      </c>
-      <c r="F14" s="84" t="s">
-        <v>97</v>
       </c>
       <c r="G14" s="71">
         <v>0.52439999999999998</v>
@@ -9107,12 +9156,12 @@
         <v>0.09</v>
       </c>
       <c r="U14" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="15" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B15" s="64">
         <v>8</v>
@@ -9123,10 +9172,10 @@
         <v>10</v>
       </c>
       <c r="E15" s="64" t="s">
+        <v>95</v>
+      </c>
+      <c r="F15" s="84" t="s">
         <v>96</v>
-      </c>
-      <c r="F15" s="84" t="s">
-        <v>97</v>
       </c>
       <c r="G15" s="71">
         <v>0.42399999999999999</v>
@@ -9163,25 +9212,25 @@
         <v>9.9999999999999992E-2</v>
       </c>
       <c r="U15" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="16" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B16" s="64">
         <v>1</v>
       </c>
       <c r="C16" s="64" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D16" s="64">
         <f t="shared" si="4"/>
         <v>11</v>
       </c>
       <c r="E16" s="64" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F16" s="65"/>
       <c r="G16" s="71">
@@ -9221,23 +9270,23 @@
     </row>
     <row r="17" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B17" s="64">
         <v>1</v>
       </c>
       <c r="C17" s="64" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D17" s="64">
         <f t="shared" si="4"/>
         <v>12</v>
       </c>
       <c r="E17" s="64" t="s">
+        <v>103</v>
+      </c>
+      <c r="F17" s="65" t="s">
         <v>104</v>
-      </c>
-      <c r="F17" s="65" t="s">
-        <v>105</v>
       </c>
       <c r="G17" s="71">
         <v>2.7492999999999999</v>
@@ -9276,23 +9325,23 @@
     </row>
     <row r="18" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B18" s="64">
         <v>2</v>
       </c>
       <c r="C18" s="64" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D18" s="64">
         <f t="shared" si="4"/>
         <v>13</v>
       </c>
       <c r="E18" s="64" t="s">
+        <v>105</v>
+      </c>
+      <c r="F18" s="65" t="s">
         <v>106</v>
-      </c>
-      <c r="F18" s="65" t="s">
-        <v>107</v>
       </c>
       <c r="G18" s="71">
         <v>2.3033000000000001</v>
@@ -9331,23 +9380,23 @@
     </row>
     <row r="19" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B19" s="64">
         <v>2</v>
       </c>
       <c r="C19" s="64" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D19" s="64">
         <f t="shared" si="4"/>
         <v>14</v>
       </c>
       <c r="E19" s="64" t="s">
+        <v>108</v>
+      </c>
+      <c r="F19" s="65" t="s">
         <v>109</v>
-      </c>
-      <c r="F19" s="65" t="s">
-        <v>110</v>
       </c>
       <c r="G19" s="71">
         <v>2.6368</v>
@@ -9384,25 +9433,25 @@
         <v>0.13999999999999999</v>
       </c>
       <c r="U19" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="20" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B20" s="64">
         <v>3</v>
       </c>
       <c r="C20" s="64" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D20" s="64">
         <f t="shared" si="4"/>
         <v>15</v>
       </c>
       <c r="E20" s="64" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F20" s="65"/>
       <c r="G20" s="71">
@@ -9442,23 +9491,23 @@
     </row>
     <row r="21" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B21" s="64">
         <v>3</v>
       </c>
       <c r="C21" s="64" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D21" s="64">
         <f t="shared" si="4"/>
         <v>16</v>
       </c>
       <c r="E21" s="64" t="s">
+        <v>113</v>
+      </c>
+      <c r="F21" s="64" t="s">
         <v>114</v>
-      </c>
-      <c r="F21" s="64" t="s">
-        <v>115</v>
       </c>
       <c r="G21" s="71">
         <v>2.6476999999999999</v>
@@ -9498,23 +9547,23 @@
     </row>
     <row r="22" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B22" s="64">
         <v>4</v>
       </c>
       <c r="C22" s="64" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D22" s="64">
         <f t="shared" si="4"/>
         <v>17</v>
       </c>
       <c r="E22" s="64" t="s">
+        <v>115</v>
+      </c>
+      <c r="F22" s="65" t="s">
         <v>116</v>
-      </c>
-      <c r="F22" s="65" t="s">
-        <v>117</v>
       </c>
       <c r="G22" s="71">
         <v>2.3235000000000001</v>
@@ -9553,23 +9602,23 @@
     </row>
     <row r="23" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B23" s="64">
         <v>4</v>
       </c>
       <c r="C23" s="64" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D23" s="64">
         <f t="shared" si="4"/>
         <v>18</v>
       </c>
       <c r="E23" s="64" t="s">
+        <v>118</v>
+      </c>
+      <c r="F23" s="142" t="s">
         <v>119</v>
-      </c>
-      <c r="F23" s="142" t="s">
-        <v>120</v>
       </c>
       <c r="G23" s="71">
         <v>2.6880000000000002</v>
@@ -9606,25 +9655,25 @@
         <v>0.18000000000000002</v>
       </c>
       <c r="U23" s="152" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="24" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B24" s="64">
         <v>5</v>
       </c>
       <c r="C24" s="64" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D24" s="64">
         <f t="shared" si="4"/>
         <v>19</v>
       </c>
       <c r="E24" s="64" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F24" s="65"/>
       <c r="G24" s="71">
@@ -9664,20 +9713,20 @@
     </row>
     <row r="25" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B25" s="64">
         <v>5</v>
       </c>
       <c r="C25" s="64" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D25" s="64">
         <f t="shared" si="4"/>
         <v>20</v>
       </c>
       <c r="E25" s="64" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="F25" s="64"/>
       <c r="G25" s="71">
@@ -9717,20 +9766,20 @@
     </row>
     <row r="26" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B26" s="64">
         <v>6</v>
       </c>
       <c r="C26" s="64" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D26" s="64">
         <f t="shared" si="4"/>
         <v>21</v>
       </c>
       <c r="E26" s="64" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F26" s="65"/>
       <c r="G26" s="71">
@@ -9770,23 +9819,23 @@
     </row>
     <row r="27" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B27" s="64">
         <v>6</v>
       </c>
       <c r="C27" s="64" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D27" s="64">
         <f t="shared" si="4"/>
         <v>22</v>
       </c>
       <c r="E27" s="64" t="s">
+        <v>126</v>
+      </c>
+      <c r="F27" s="84" t="s">
         <v>127</v>
-      </c>
-      <c r="F27" s="84" t="s">
-        <v>128</v>
       </c>
       <c r="G27" s="71">
         <v>2.6360000000000001</v>
@@ -9803,7 +9852,7 @@
         <f t="shared" si="0"/>
         <v>645029.20000000007</v>
       </c>
-      <c r="O27" s="183">
+      <c r="O27" s="182">
         <v>0</v>
       </c>
       <c r="P27" s="79">
@@ -9823,28 +9872,28 @@
         <v>0.22000000000000006</v>
       </c>
       <c r="T27" s="65" t="s">
+        <v>96</v>
+      </c>
+      <c r="U27" t="s">
         <v>97</v>
-      </c>
-      <c r="U27" t="s">
-        <v>98</v>
       </c>
     </row>
     <row r="28" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B28" s="64">
         <v>7</v>
       </c>
       <c r="C28" s="64" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D28" s="64">
         <f t="shared" si="4"/>
         <v>23</v>
       </c>
       <c r="E28" s="64" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F28" s="65"/>
       <c r="G28" s="71">
@@ -9884,20 +9933,20 @@
     </row>
     <row r="29" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B29" s="64">
         <v>7</v>
       </c>
       <c r="C29" s="64" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D29" s="64">
         <f t="shared" si="4"/>
         <v>24</v>
       </c>
       <c r="E29" s="64" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F29" s="65"/>
       <c r="G29" s="71">
@@ -9937,20 +9986,20 @@
     </row>
     <row r="30" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B30" s="64">
         <v>8</v>
       </c>
       <c r="C30" s="64" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D30" s="64">
         <f t="shared" si="4"/>
         <v>25</v>
       </c>
       <c r="E30" s="64" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="F30" s="64"/>
       <c r="G30" s="71">
@@ -9990,23 +10039,23 @@
     </row>
     <row r="31" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B31" s="64">
         <v>8</v>
       </c>
       <c r="C31" s="64" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D31" s="64">
         <f t="shared" si="4"/>
         <v>26</v>
       </c>
       <c r="E31" s="64" t="s">
+        <v>133</v>
+      </c>
+      <c r="F31" s="64" t="s">
         <v>134</v>
-      </c>
-      <c r="F31" s="64" t="s">
-        <v>135</v>
       </c>
       <c r="G31" s="71">
         <v>2.6469</v>
@@ -10045,20 +10094,20 @@
     </row>
     <row r="32" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="5" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B32" s="64">
         <v>9</v>
       </c>
       <c r="C32" s="64" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D32" s="64">
         <f t="shared" si="4"/>
         <v>27</v>
       </c>
       <c r="E32" s="64" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F32" s="65"/>
       <c r="G32" s="71">
@@ -10098,20 +10147,20 @@
     </row>
     <row r="33" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="5" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B33" s="64">
         <v>9</v>
       </c>
       <c r="C33" s="64" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D33" s="64">
         <f t="shared" si="4"/>
         <v>28</v>
       </c>
       <c r="E33" s="64" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F33" s="64"/>
       <c r="G33" s="71">
@@ -10151,23 +10200,23 @@
     </row>
     <row r="34" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="5" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B34" s="64">
         <v>10</v>
       </c>
       <c r="C34" s="64" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D34" s="64">
         <f t="shared" si="4"/>
         <v>29</v>
       </c>
       <c r="E34" s="64" t="s">
+        <v>137</v>
+      </c>
+      <c r="F34" s="64" t="s">
         <v>138</v>
-      </c>
-      <c r="F34" s="64" t="s">
-        <v>139</v>
       </c>
       <c r="G34" s="71">
         <v>2.4476</v>
@@ -10184,7 +10233,7 @@
         <f t="shared" si="0"/>
         <v>598927.72</v>
       </c>
-      <c r="O34" s="187">
+      <c r="O34" s="186">
         <v>18500</v>
       </c>
       <c r="P34" s="79">
@@ -10206,20 +10255,20 @@
     </row>
     <row r="35" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="5" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B35" s="64">
         <v>10</v>
       </c>
       <c r="C35" s="64" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D35" s="64">
         <f t="shared" si="4"/>
         <v>30</v>
       </c>
       <c r="E35" s="64" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F35" s="65"/>
       <c r="G35" s="71">
@@ -10259,23 +10308,23 @@
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="5" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B36" s="64">
         <v>11</v>
       </c>
       <c r="C36" s="64" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D36" s="64">
         <f t="shared" si="4"/>
         <v>31</v>
       </c>
       <c r="E36" s="64" t="s">
+        <v>140</v>
+      </c>
+      <c r="F36" s="64" t="s">
         <v>141</v>
-      </c>
-      <c r="F36" s="64" t="s">
-        <v>142</v>
       </c>
       <c r="G36" s="71">
         <v>2.3026</v>
@@ -10314,20 +10363,20 @@
     </row>
     <row r="37" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="5" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B37" s="64">
         <v>11</v>
       </c>
       <c r="C37" s="64" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D37" s="64">
         <f t="shared" si="4"/>
         <v>32</v>
       </c>
       <c r="E37" s="64" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F37" s="65"/>
       <c r="G37" s="71">
@@ -10367,20 +10416,20 @@
     </row>
     <row r="38" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="5" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B38" s="64">
         <v>12</v>
       </c>
       <c r="C38" s="64" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D38" s="64">
         <f t="shared" si="4"/>
         <v>33</v>
       </c>
       <c r="E38" s="64" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F38" s="65"/>
       <c r="G38" s="71">
@@ -10420,20 +10469,20 @@
     </row>
     <row r="39" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="5" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B39" s="64">
         <v>12</v>
       </c>
       <c r="C39" s="64" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D39" s="64">
         <f t="shared" si="4"/>
         <v>34</v>
       </c>
       <c r="E39" s="64" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F39" s="64"/>
       <c r="G39" s="71">
@@ -10473,23 +10522,23 @@
     </row>
     <row r="40" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="5" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B40" s="64">
         <v>1</v>
       </c>
       <c r="C40" s="64" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D40" s="64">
         <f t="shared" si="4"/>
         <v>35</v>
       </c>
       <c r="E40" s="64" t="s">
+        <v>146</v>
+      </c>
+      <c r="F40" s="65" t="s">
         <v>147</v>
-      </c>
-      <c r="F40" s="65" t="s">
-        <v>148</v>
       </c>
       <c r="G40" s="71">
         <v>1.0069999999999999</v>
@@ -10528,23 +10577,23 @@
     </row>
     <row r="41" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="5" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B41" s="64">
         <v>1</v>
       </c>
       <c r="C41" s="64" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D41" s="64">
         <f t="shared" si="4"/>
         <v>36</v>
       </c>
       <c r="E41" s="64" t="s">
+        <v>149</v>
+      </c>
+      <c r="F41" s="65" t="s">
         <v>150</v>
-      </c>
-      <c r="F41" s="65" t="s">
-        <v>151</v>
       </c>
       <c r="G41" s="71">
         <v>0.78120000000000001</v>
@@ -10581,7 +10630,7 @@
         <v>0.36000000000000015</v>
       </c>
       <c r="U41" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="42" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -10590,17 +10639,17 @@
         <v>1</v>
       </c>
       <c r="C42" s="63" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D42" s="64">
         <f t="shared" si="4"/>
         <v>37</v>
       </c>
       <c r="E42" s="63" t="s">
+        <v>149</v>
+      </c>
+      <c r="F42" s="65" t="s">
         <v>150</v>
-      </c>
-      <c r="F42" s="65" t="s">
-        <v>151</v>
       </c>
       <c r="G42" s="85">
         <v>1.2153</v>
@@ -10637,7 +10686,7 @@
         <v>0.37000000000000016</v>
       </c>
       <c r="U42" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="43" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -10645,17 +10694,17 @@
         <v>2</v>
       </c>
       <c r="C43" s="86" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D43" s="64">
         <f t="shared" si="4"/>
         <v>38</v>
       </c>
       <c r="E43" s="63" t="s">
+        <v>153</v>
+      </c>
+      <c r="F43" s="63" t="s">
         <v>154</v>
-      </c>
-      <c r="F43" s="63" t="s">
-        <v>155</v>
       </c>
       <c r="G43" s="85">
         <v>0.95489999999999997</v>
@@ -10697,14 +10746,14 @@
         <v>2</v>
       </c>
       <c r="C44" s="86" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D44" s="64">
         <f t="shared" si="4"/>
         <v>39</v>
       </c>
       <c r="E44" s="63" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F44" s="84"/>
       <c r="G44" s="85">
@@ -10747,17 +10796,17 @@
         <v>2</v>
       </c>
       <c r="C45" s="86" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D45" s="64">
         <f t="shared" si="4"/>
         <v>40</v>
       </c>
       <c r="E45" s="63" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F45" s="63" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="G45" s="85">
         <v>1.1545000000000001</v>
@@ -10799,17 +10848,17 @@
         <v>3</v>
       </c>
       <c r="C46" s="86" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D46" s="64">
         <f t="shared" si="4"/>
         <v>41</v>
       </c>
       <c r="E46" s="63" t="s">
+        <v>157</v>
+      </c>
+      <c r="F46" s="63" t="s">
         <v>158</v>
-      </c>
-      <c r="F46" s="63" t="s">
-        <v>159</v>
       </c>
       <c r="G46" s="85">
         <v>0.95489999999999997</v>
@@ -10851,14 +10900,14 @@
         <v>3</v>
       </c>
       <c r="C47" s="86" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D47" s="64">
         <f t="shared" si="4"/>
         <v>42</v>
       </c>
       <c r="E47" s="63" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F47" s="84"/>
       <c r="G47" s="85">
@@ -10901,14 +10950,14 @@
         <v>3</v>
       </c>
       <c r="C48" s="86" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D48" s="64">
         <f t="shared" si="4"/>
         <v>43</v>
       </c>
       <c r="E48" s="63" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="F48" s="84"/>
       <c r="G48" s="85">
@@ -10951,17 +11000,17 @@
         <v>4</v>
       </c>
       <c r="C49" s="86" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D49" s="64">
         <f t="shared" si="4"/>
         <v>44</v>
       </c>
       <c r="E49" s="63" t="s">
+        <v>161</v>
+      </c>
+      <c r="F49" s="84" t="s">
         <v>162</v>
-      </c>
-      <c r="F49" s="84" t="s">
-        <v>163</v>
       </c>
       <c r="G49" s="85">
         <v>0.95489999999999997</v>
@@ -11003,14 +11052,14 @@
         <v>4</v>
       </c>
       <c r="C50" s="86" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D50" s="64">
         <f t="shared" si="4"/>
         <v>45</v>
       </c>
       <c r="E50" s="63" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="F50" s="63"/>
       <c r="G50" s="85">
@@ -11048,7 +11097,7 @@
         <v>0.45000000000000023</v>
       </c>
       <c r="U50" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="51" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -11056,17 +11105,17 @@
         <v>4</v>
       </c>
       <c r="C51" s="86" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D51" s="64">
         <f t="shared" si="4"/>
         <v>46</v>
       </c>
       <c r="E51" s="63" t="s">
+        <v>165</v>
+      </c>
+      <c r="F51" s="63" t="s">
         <v>166</v>
-      </c>
-      <c r="F51" s="63" t="s">
-        <v>167</v>
       </c>
       <c r="G51" s="85">
         <v>1.1545000000000001</v>
@@ -11108,17 +11157,17 @@
         <v>5</v>
       </c>
       <c r="C52" s="86" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D52" s="64">
         <f t="shared" si="4"/>
         <v>47</v>
       </c>
       <c r="E52" s="63" t="s">
+        <v>167</v>
+      </c>
+      <c r="F52" s="84" t="s">
         <v>168</v>
-      </c>
-      <c r="F52" s="84" t="s">
-        <v>169</v>
       </c>
       <c r="G52" s="85">
         <v>0.95489999999999997</v>
@@ -11160,17 +11209,17 @@
         <v>5</v>
       </c>
       <c r="C53" s="86" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D53" s="64">
         <f t="shared" si="4"/>
         <v>48</v>
       </c>
       <c r="E53" s="63" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F53" s="63" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="G53" s="85">
         <v>0.75519999999999998</v>
@@ -11212,17 +11261,17 @@
         <v>5</v>
       </c>
       <c r="C54" s="86" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D54" s="64">
         <f t="shared" si="4"/>
         <v>49</v>
       </c>
       <c r="E54" s="63" t="s">
+        <v>170</v>
+      </c>
+      <c r="F54" s="63" t="s">
         <v>171</v>
-      </c>
-      <c r="F54" s="63" t="s">
-        <v>172</v>
       </c>
       <c r="G54" s="85">
         <v>1.1545000000000001</v>
@@ -11264,14 +11313,14 @@
         <v>6</v>
       </c>
       <c r="C55" s="86" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D55" s="64">
         <f t="shared" si="4"/>
         <v>50</v>
       </c>
       <c r="E55" s="63" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="F55" s="63"/>
       <c r="G55" s="85">
@@ -11314,14 +11363,14 @@
         <v>6</v>
       </c>
       <c r="C56" s="86" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D56" s="64">
         <f t="shared" si="4"/>
         <v>51</v>
       </c>
       <c r="E56" s="63" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="F56" s="63"/>
       <c r="G56" s="85">
@@ -11359,7 +11408,7 @@
         <v>0.51000000000000023</v>
       </c>
       <c r="U56" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="57" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -11367,14 +11416,14 @@
         <v>6</v>
       </c>
       <c r="C57" s="86" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D57" s="64">
         <f t="shared" si="4"/>
         <v>52</v>
       </c>
       <c r="E57" s="63" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="F57" s="84"/>
       <c r="G57" s="85">
@@ -11417,14 +11466,14 @@
         <v>7</v>
       </c>
       <c r="C58" s="86" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D58" s="64">
         <f t="shared" si="4"/>
         <v>53</v>
       </c>
       <c r="E58" s="63" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="F58" s="84"/>
       <c r="G58" s="85">
@@ -11467,14 +11516,14 @@
         <v>7</v>
       </c>
       <c r="C59" s="86" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D59" s="64">
         <f t="shared" si="4"/>
         <v>54</v>
       </c>
       <c r="E59" s="63" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F59" s="63"/>
       <c r="G59" s="85">
@@ -11517,17 +11566,17 @@
         <v>7</v>
       </c>
       <c r="C60" s="86" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D60" s="64">
         <f t="shared" si="4"/>
         <v>55</v>
       </c>
       <c r="E60" s="63" t="s">
+        <v>178</v>
+      </c>
+      <c r="F60" s="63" t="s">
         <v>179</v>
-      </c>
-      <c r="F60" s="63" t="s">
-        <v>180</v>
       </c>
       <c r="G60" s="85">
         <v>1.1545000000000001</v>
@@ -11569,17 +11618,17 @@
         <v>8</v>
       </c>
       <c r="C61" s="86" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D61" s="64">
         <f t="shared" si="4"/>
         <v>56</v>
       </c>
       <c r="E61" s="63" t="s">
+        <v>180</v>
+      </c>
+      <c r="F61" s="84" t="s">
         <v>181</v>
-      </c>
-      <c r="F61" s="84" t="s">
-        <v>182</v>
       </c>
       <c r="G61" s="85">
         <v>0.95489999999999997</v>
@@ -11619,17 +11668,17 @@
         <v>8</v>
       </c>
       <c r="C62" s="86" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D62" s="64">
         <f t="shared" si="4"/>
         <v>57</v>
       </c>
       <c r="E62" s="63" t="s">
+        <v>182</v>
+      </c>
+      <c r="F62" s="84" t="s">
         <v>183</v>
-      </c>
-      <c r="F62" s="84" t="s">
-        <v>184</v>
       </c>
       <c r="G62" s="85">
         <v>0.75519999999999998</v>
@@ -11671,14 +11720,14 @@
         <v>8</v>
       </c>
       <c r="C63" s="86" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D63" s="64">
         <f t="shared" si="4"/>
         <v>58</v>
       </c>
       <c r="E63" s="63" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="F63" s="84"/>
       <c r="G63" s="85">
@@ -11721,17 +11770,17 @@
         <v>9</v>
       </c>
       <c r="C64" s="86" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D64" s="64">
         <f t="shared" si="4"/>
         <v>59</v>
       </c>
       <c r="E64" s="63" t="s">
+        <v>185</v>
+      </c>
+      <c r="F64" s="63" t="s">
         <v>186</v>
-      </c>
-      <c r="F64" s="63" t="s">
-        <v>187</v>
       </c>
       <c r="G64" s="85">
         <v>0.95489999999999997</v>
@@ -11773,14 +11822,14 @@
         <v>9</v>
       </c>
       <c r="C65" s="86" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D65" s="64">
         <f t="shared" si="4"/>
         <v>60</v>
       </c>
       <c r="E65" s="63" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="F65" s="84"/>
       <c r="G65" s="85">
@@ -11818,7 +11867,7 @@
         <v>0.60000000000000031</v>
       </c>
       <c r="U65" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="66" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -11826,14 +11875,14 @@
         <v>9</v>
       </c>
       <c r="C66" s="86" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D66" s="64">
         <f t="shared" si="4"/>
         <v>61</v>
       </c>
       <c r="E66" s="63" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F66" s="63"/>
       <c r="G66" s="85">
@@ -11871,7 +11920,7 @@
         <v>0.61000000000000032</v>
       </c>
       <c r="U66" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="67" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -11879,17 +11928,17 @@
         <v>10</v>
       </c>
       <c r="C67" s="86" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D67" s="64">
         <f t="shared" si="4"/>
         <v>62</v>
       </c>
       <c r="E67" s="63" t="s">
+        <v>191</v>
+      </c>
+      <c r="F67" s="84" t="s">
         <v>192</v>
-      </c>
-      <c r="F67" s="84" t="s">
-        <v>193</v>
       </c>
       <c r="G67" s="85">
         <v>0.95489999999999997</v>
@@ -11926,7 +11975,7 @@
         <v>0.62000000000000033</v>
       </c>
       <c r="U67" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="68" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -11934,17 +11983,17 @@
         <v>10</v>
       </c>
       <c r="C68" s="86" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D68" s="64">
         <f t="shared" si="4"/>
         <v>63</v>
       </c>
       <c r="E68" s="63" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F68" s="63" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G68" s="85">
         <v>0.75519999999999998</v>
@@ -11986,14 +12035,14 @@
         <v>10</v>
       </c>
       <c r="C69" s="86" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D69" s="64">
         <f t="shared" si="4"/>
         <v>64</v>
       </c>
       <c r="E69" s="63" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F69" s="63"/>
       <c r="G69" s="85">
@@ -12036,14 +12085,14 @@
         <v>11</v>
       </c>
       <c r="C70" s="86" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D70" s="64">
         <f t="shared" si="4"/>
         <v>65</v>
       </c>
       <c r="E70" s="63" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="F70" s="84"/>
       <c r="G70" s="85">
@@ -12086,17 +12135,17 @@
         <v>11</v>
       </c>
       <c r="C71" s="86" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D71" s="64">
         <f t="shared" ref="D71:D75" si="10">D70+1</f>
         <v>66</v>
       </c>
       <c r="E71" s="63" t="s">
+        <v>196</v>
+      </c>
+      <c r="F71" s="84" t="s">
         <v>197</v>
-      </c>
-      <c r="F71" s="84" t="s">
-        <v>198</v>
       </c>
       <c r="G71" s="85">
         <v>0.75519999999999998</v>
@@ -12138,14 +12187,14 @@
         <v>11</v>
       </c>
       <c r="C72" s="86" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D72" s="64">
         <f t="shared" si="10"/>
         <v>67</v>
       </c>
       <c r="E72" s="63" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F72" s="63"/>
       <c r="G72" s="85">
@@ -12188,14 +12237,14 @@
         <v>12</v>
       </c>
       <c r="C73" s="87" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D73" s="64">
         <f t="shared" si="10"/>
         <v>68</v>
       </c>
       <c r="E73" s="88" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F73" s="88"/>
       <c r="G73" s="89">
@@ -12238,14 +12287,14 @@
         <v>12</v>
       </c>
       <c r="C74" s="86" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D74" s="64">
         <f t="shared" si="10"/>
         <v>69</v>
       </c>
       <c r="E74" s="64" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F74" s="96"/>
       <c r="G74" s="89">
@@ -12288,14 +12337,14 @@
         <v>12</v>
       </c>
       <c r="C75" s="86" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D75" s="64">
         <f t="shared" si="10"/>
         <v>70</v>
       </c>
       <c r="E75" s="64" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="F75" s="96"/>
       <c r="G75" s="89">
@@ -12488,102 +12537,94 @@
     </row>
     <row r="83" spans="2:18" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="84" spans="2:18" ht="9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E84" s="205" t="str">
+      <c r="E84" s="217" t="str">
         <f>RESUMEN!A14</f>
         <v>ESTIMADOS PROPIETARIOS E INQUILINOS: POR FAVOR LOS QUE ABONAN EN PRIMER VENCIMIENTO ABONEN EL MONTO DE PRIMER VENCIMIENTO, ASI AGILIZAN LA LIQUIDACION, RESPETEN LOS CENTAVOS CORRESPONDIENTES A LA UNIDAD FUNCIONAL. ES DE CARÁCTER OBLIGATORIO INFORMAR VIA MAIL LAS EXPENSAS. CASO CONTRARIO SE INFORMARA VIA CARTA DOCUMENTO A LA UNIDAD FUNCIONAL QUE CREEMOS QUE CORRESPONDE, CUYO COSTO SERA IMPUTADO A LA UNIDAD FUNCIONAL SOSPECHADA.</v>
       </c>
-      <c r="F84" s="206"/>
-      <c r="G84" s="206"/>
-      <c r="H84" s="206"/>
-      <c r="I84" s="206"/>
-      <c r="J84" s="206"/>
-      <c r="K84" s="206"/>
-      <c r="L84" s="206"/>
-      <c r="M84" s="206"/>
-      <c r="N84" s="206"/>
-      <c r="O84" s="206"/>
-      <c r="P84" s="206"/>
+      <c r="F84" s="210"/>
+      <c r="G84" s="210"/>
+      <c r="H84" s="210"/>
+      <c r="I84" s="210"/>
+      <c r="J84" s="210"/>
+      <c r="K84" s="210"/>
+      <c r="L84" s="210"/>
+      <c r="M84" s="210"/>
+      <c r="N84" s="210"/>
+      <c r="O84" s="210"/>
+      <c r="P84" s="210"/>
     </row>
     <row r="85" spans="2:18" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E85" s="206"/>
-      <c r="F85" s="206"/>
-      <c r="G85" s="206"/>
-      <c r="H85" s="206"/>
-      <c r="I85" s="206"/>
-      <c r="J85" s="206"/>
-      <c r="K85" s="206"/>
-      <c r="L85" s="206"/>
-      <c r="M85" s="206"/>
-      <c r="N85" s="206"/>
-      <c r="O85" s="206"/>
-      <c r="P85" s="206"/>
+      <c r="E85" s="210"/>
+      <c r="F85" s="210"/>
+      <c r="G85" s="210"/>
+      <c r="H85" s="210"/>
+      <c r="I85" s="210"/>
+      <c r="J85" s="210"/>
+      <c r="K85" s="210"/>
+      <c r="L85" s="210"/>
+      <c r="M85" s="210"/>
+      <c r="N85" s="210"/>
+      <c r="O85" s="210"/>
+      <c r="P85" s="210"/>
     </row>
     <row r="86" spans="2:18" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E86" s="206"/>
-      <c r="F86" s="206"/>
-      <c r="G86" s="206"/>
-      <c r="H86" s="206"/>
-      <c r="I86" s="206"/>
-      <c r="J86" s="206"/>
-      <c r="K86" s="206"/>
-      <c r="L86" s="206"/>
-      <c r="M86" s="206"/>
-      <c r="N86" s="206"/>
-      <c r="O86" s="206"/>
-      <c r="P86" s="206"/>
+      <c r="E86" s="210"/>
+      <c r="F86" s="210"/>
+      <c r="G86" s="210"/>
+      <c r="H86" s="210"/>
+      <c r="I86" s="210"/>
+      <c r="J86" s="210"/>
+      <c r="K86" s="210"/>
+      <c r="L86" s="210"/>
+      <c r="M86" s="210"/>
+      <c r="N86" s="210"/>
+      <c r="O86" s="210"/>
+      <c r="P86" s="210"/>
     </row>
     <row r="87" spans="2:18" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E87" s="206"/>
-      <c r="F87" s="206"/>
-      <c r="G87" s="206"/>
-      <c r="H87" s="206"/>
-      <c r="I87" s="206"/>
-      <c r="J87" s="206"/>
-      <c r="K87" s="206"/>
-      <c r="L87" s="206"/>
-      <c r="M87" s="206"/>
-      <c r="N87" s="206"/>
-      <c r="O87" s="206"/>
-      <c r="P87" s="206"/>
+      <c r="E87" s="210"/>
+      <c r="F87" s="210"/>
+      <c r="G87" s="210"/>
+      <c r="H87" s="210"/>
+      <c r="I87" s="210"/>
+      <c r="J87" s="210"/>
+      <c r="K87" s="210"/>
+      <c r="L87" s="210"/>
+      <c r="M87" s="210"/>
+      <c r="N87" s="210"/>
+      <c r="O87" s="210"/>
+      <c r="P87" s="210"/>
     </row>
     <row r="88" spans="2:18" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E88" s="206"/>
-      <c r="F88" s="206"/>
-      <c r="G88" s="206"/>
-      <c r="H88" s="206"/>
-      <c r="I88" s="206"/>
-      <c r="J88" s="206"/>
-      <c r="K88" s="206"/>
-      <c r="L88" s="206"/>
-      <c r="M88" s="206"/>
-      <c r="N88" s="206"/>
-      <c r="O88" s="206"/>
-      <c r="P88" s="206"/>
+      <c r="E88" s="210"/>
+      <c r="F88" s="210"/>
+      <c r="G88" s="210"/>
+      <c r="H88" s="210"/>
+      <c r="I88" s="210"/>
+      <c r="J88" s="210"/>
+      <c r="K88" s="210"/>
+      <c r="L88" s="210"/>
+      <c r="M88" s="210"/>
+      <c r="N88" s="210"/>
+      <c r="O88" s="210"/>
+      <c r="P88" s="210"/>
     </row>
     <row r="89" spans="2:18" ht="67.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E89" s="206"/>
-      <c r="F89" s="206"/>
-      <c r="G89" s="206"/>
-      <c r="H89" s="206"/>
-      <c r="I89" s="206"/>
-      <c r="J89" s="206"/>
-      <c r="K89" s="206"/>
-      <c r="L89" s="206"/>
-      <c r="M89" s="206"/>
-      <c r="N89" s="206"/>
-      <c r="O89" s="206"/>
-      <c r="P89" s="206"/>
+      <c r="E89" s="210"/>
+      <c r="F89" s="210"/>
+      <c r="G89" s="210"/>
+      <c r="H89" s="210"/>
+      <c r="I89" s="210"/>
+      <c r="J89" s="210"/>
+      <c r="K89" s="210"/>
+      <c r="L89" s="210"/>
+      <c r="M89" s="210"/>
+      <c r="N89" s="210"/>
+      <c r="O89" s="210"/>
+      <c r="P89" s="210"/>
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="E84:P89"/>
-    <mergeCell ref="P4:P5"/>
-    <mergeCell ref="J4:J5"/>
-    <mergeCell ref="K4:K5"/>
-    <mergeCell ref="L4:L5"/>
-    <mergeCell ref="M4:M5"/>
-    <mergeCell ref="N4:N5"/>
-    <mergeCell ref="O4:O5"/>
     <mergeCell ref="G1:P1"/>
     <mergeCell ref="P2:R2"/>
     <mergeCell ref="A4:A5"/>
@@ -12596,6 +12637,14 @@
     <mergeCell ref="I4:I5"/>
     <mergeCell ref="Q4:Q5"/>
     <mergeCell ref="R4:R5"/>
+    <mergeCell ref="E84:P89"/>
+    <mergeCell ref="P4:P5"/>
+    <mergeCell ref="J4:J5"/>
+    <mergeCell ref="K4:K5"/>
+    <mergeCell ref="L4:L5"/>
+    <mergeCell ref="M4:M5"/>
+    <mergeCell ref="N4:N5"/>
+    <mergeCell ref="O4:O5"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>

--- a/GORRITI/Septiembre/GORRITI-Septiembre.xlsx
+++ b/GORRITI/Septiembre/GORRITI-Septiembre.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\GORRITI\Septiembre\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05E5DAF3-9937-46B4-B9A9-30C20AF5ED6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E179A276-6F0D-4816-832B-E23B199A868E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="850" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,14 +21,14 @@
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">PRORRATEO!$A$1:$R$90</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'PRORRATEO DE PRUEBA  EMERGENCIA'!$A$1:$R$90</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$E$131</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$E$135</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="581" uniqueCount="245">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="584" uniqueCount="246">
   <si>
     <t>MAIL: consorciogorriti368@gmail.com</t>
   </si>
@@ -648,9 +648,6 @@
     <t>Articulos de limpieza</t>
   </si>
   <si>
-    <t>EN MAY, JUNI, JULI NO SE DEBITA EL MANTENIMIENTO DE CUENTA</t>
-  </si>
-  <si>
     <t>Castellano Alejandro - Abono de servicio de mantenimiento de grupo electrogeno y porton</t>
   </si>
   <si>
@@ -669,9 +666,6 @@
     <t>ANALIA AYELEN CAMERA</t>
   </si>
   <si>
-    <t>LA CAJA NOS DA EN $1.510.113 PESOS, CUANDO EN EL BANCO TENEMOS 636.353,64 Y EN EFECTIVO 400.000 APROX, LA DIFERENCIA ES DE $473.759,95 ENTRE LA CAJA REAL QUE TENEMOS Y LA CAJA QUE NOS DA EL EXCEL DE $1.510.113</t>
-  </si>
-  <si>
     <t>PREVISION ORDINARIA - ASCENSOR - LIQUIDADO EN COLUMNA APARTE</t>
   </si>
   <si>
@@ -762,7 +756,16 @@
     <t>Destapaciones ItaloAmericana - Mantenimiento de cañerias repaso ramales de planta baja, columnas del primer piso y sus dos salidas cloacales - Abonos Mayo Junio Agosto y Septiembre</t>
   </si>
   <si>
-    <t>Depositos si identificar</t>
+    <t>Depositos sin identificar - 15/09</t>
+  </si>
+  <si>
+    <t>Deposito ya identificado mes anterior</t>
+  </si>
+  <si>
+    <t>Deposito identificado diciembre 2024 - 13/12</t>
+  </si>
+  <si>
+    <t>Deposito identificado febrero 2025 - 05/02</t>
   </si>
 </sst>
 </file>
@@ -1513,7 +1516,7 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="248">
+  <cellXfs count="249">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1814,6 +1817,26 @@
     </xf>
     <xf numFmtId="165" fontId="20" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="22" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
@@ -1827,16 +1850,16 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1895,27 +1918,10 @@
     <xf numFmtId="0" fontId="16" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="8" fontId="8" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="8" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="8" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="8" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="8" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="16" fontId="22" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="25" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="7">
     <cellStyle name="Millares" xfId="3" builtinId="3"/>
@@ -2284,7 +2290,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M136"/>
+  <dimension ref="A1:M140"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="37.5703125" customWidth="1"/>
@@ -2292,8 +2298,9 @@
     <col min="3" max="3" width="15.85546875" hidden="1" customWidth="1"/>
     <col min="4" max="4" width="21.7109375" customWidth="1"/>
     <col min="5" max="5" width="14.7109375" customWidth="1"/>
-    <col min="6" max="6" width="13" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.140625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="10" width="13" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="18" customWidth="1"/>
     <col min="12" max="12" width="18.28515625" customWidth="1"/>
   </cols>
@@ -2350,7 +2357,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="18" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C6" s="194"/>
       <c r="D6" s="187" t="s">
@@ -2370,49 +2377,49 @@
       <c r="E7" s="19"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B9" s="209" t="s">
-        <v>217</v>
-      </c>
-      <c r="C9" s="210"/>
+      <c r="B9" s="217" t="s">
+        <v>215</v>
+      </c>
+      <c r="C9" s="218"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B10" s="210"/>
-      <c r="C10" s="210"/>
+      <c r="B10" s="218"/>
+      <c r="C10" s="218"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B11" s="210"/>
-      <c r="C11" s="210"/>
+      <c r="B11" s="218"/>
+      <c r="C11" s="218"/>
     </row>
     <row r="13" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="214" t="s">
+      <c r="A14" s="224" t="s">
         <v>10</v>
       </c>
-      <c r="B14" s="210"/>
-      <c r="C14" s="210"/>
-      <c r="D14" s="210"/>
-      <c r="E14" s="210"/>
+      <c r="B14" s="218"/>
+      <c r="C14" s="218"/>
+      <c r="D14" s="218"/>
+      <c r="E14" s="218"/>
     </row>
     <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="210"/>
-      <c r="B15" s="210"/>
-      <c r="C15" s="210"/>
-      <c r="D15" s="210"/>
-      <c r="E15" s="210"/>
+      <c r="A15" s="218"/>
+      <c r="B15" s="218"/>
+      <c r="C15" s="218"/>
+      <c r="D15" s="218"/>
+      <c r="E15" s="218"/>
     </row>
     <row r="16" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="210"/>
-      <c r="B16" s="210"/>
-      <c r="C16" s="210"/>
-      <c r="D16" s="210"/>
-      <c r="E16" s="210"/>
+      <c r="A16" s="218"/>
+      <c r="B16" s="218"/>
+      <c r="C16" s="218"/>
+      <c r="D16" s="218"/>
+      <c r="E16" s="218"/>
     </row>
     <row r="17" spans="1:8" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="210"/>
-      <c r="B17" s="210"/>
-      <c r="C17" s="210"/>
-      <c r="D17" s="210"/>
-      <c r="E17" s="210"/>
+      <c r="A17" s="218"/>
+      <c r="B17" s="218"/>
+      <c r="C17" s="218"/>
+      <c r="D17" s="218"/>
+      <c r="E17" s="218"/>
     </row>
     <row r="18" spans="1:8" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="19" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
@@ -2443,7 +2450,7 @@
       </c>
       <c r="B23" s="5"/>
       <c r="C23" s="5"/>
-      <c r="D23" s="239">
+      <c r="D23" s="156">
         <v>1357288</v>
       </c>
       <c r="E23" s="152"/>
@@ -2500,7 +2507,7 @@
       </c>
       <c r="B29" s="5"/>
       <c r="C29" s="5"/>
-      <c r="D29" s="239">
+      <c r="D29" s="156">
         <v>1120450</v>
       </c>
       <c r="E29" s="152"/>
@@ -2517,6 +2524,7 @@
         <v>1120450</v>
       </c>
       <c r="E30" s="158"/>
+      <c r="F30" s="20"/>
       <c r="G30" s="199"/>
     </row>
     <row r="31" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
@@ -2529,7 +2537,7 @@
         <v>-500000</v>
       </c>
       <c r="H31" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="32" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
@@ -2560,6 +2568,10 @@
         <v>2477738</v>
       </c>
       <c r="F33" s="20"/>
+      <c r="G33" s="20">
+        <f>E33-1800000</f>
+        <v>677738</v>
+      </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" s="33" t="s">
@@ -2571,42 +2583,42 @@
       <c r="E34" s="162"/>
     </row>
     <row r="35" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="213" t="s">
+      <c r="A35" s="223" t="s">
         <v>201</v>
       </c>
-      <c r="B35" s="208"/>
+      <c r="B35" s="216"/>
       <c r="C35" s="181"/>
-      <c r="D35" s="239">
+      <c r="D35" s="156">
         <v>60000</v>
       </c>
       <c r="E35" s="180" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
     </row>
     <row r="36" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="215" t="s">
-        <v>225</v>
-      </c>
-      <c r="B36" s="216"/>
+      <c r="A36" s="221" t="s">
+        <v>223</v>
+      </c>
+      <c r="B36" s="222"/>
       <c r="C36" s="181"/>
-      <c r="D36" s="239">
+      <c r="D36" s="156">
         <v>249000</v>
       </c>
       <c r="E36" s="180" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
     </row>
     <row r="37" spans="1:8" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="215" t="s">
-        <v>224</v>
-      </c>
-      <c r="B37" s="216"/>
+      <c r="A37" s="221" t="s">
+        <v>222</v>
+      </c>
+      <c r="B37" s="222"/>
       <c r="C37" s="51"/>
-      <c r="D37" s="239">
+      <c r="D37" s="156">
         <v>249000</v>
       </c>
       <c r="E37" s="180" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="H37" s="136"/>
     </row>
@@ -2632,21 +2644,22 @@
       <c r="E39" s="166"/>
     </row>
     <row r="40" spans="1:8" s="36" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="207" t="s">
+      <c r="A40" s="215" t="s">
         <v>21</v>
       </c>
-      <c r="B40" s="208"/>
+      <c r="B40" s="216"/>
       <c r="C40" s="53"/>
-      <c r="D40" s="240">
+      <c r="D40" s="210">
         <v>144149</v>
       </c>
       <c r="E40" s="167" t="s">
-        <v>220</v>
-      </c>
+        <v>218</v>
+      </c>
+      <c r="H40" s="248"/>
     </row>
     <row r="41" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="207"/>
-      <c r="B41" s="208"/>
+      <c r="A41" s="215"/>
+      <c r="B41" s="216"/>
       <c r="C41" s="53"/>
       <c r="D41" s="168"/>
       <c r="E41" s="167"/>
@@ -2678,27 +2691,27 @@
       </c>
       <c r="B44" s="5"/>
       <c r="C44" s="51"/>
-      <c r="D44" s="241">
+      <c r="D44" s="211">
         <v>1753141.39</v>
       </c>
       <c r="E44" s="171" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="G44" s="136"/>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" s="5" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="B45" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C45" s="5"/>
-      <c r="D45" s="183">
+      <c r="D45" s="168">
         <v>137546.85999999999</v>
       </c>
       <c r="E45" s="172" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
@@ -2710,7 +2723,7 @@
         <v>26</v>
       </c>
       <c r="C46" s="5"/>
-      <c r="D46" s="183">
+      <c r="D46" s="168">
         <v>248622.81</v>
       </c>
       <c r="E46" s="172" t="str">
@@ -2727,7 +2740,7 @@
         <v>27</v>
       </c>
       <c r="C47" s="5"/>
-      <c r="D47" s="183">
+      <c r="D47" s="168">
         <v>15282.98</v>
       </c>
       <c r="E47" s="173" t="str">
@@ -2762,11 +2775,11 @@
       </c>
       <c r="B50" s="5"/>
       <c r="C50" s="5"/>
-      <c r="D50" s="183">
+      <c r="D50" s="168">
         <v>824658.47</v>
       </c>
       <c r="E50" s="171" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
     </row>
     <row r="51" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2775,11 +2788,11 @@
       </c>
       <c r="B51" s="183"/>
       <c r="C51" s="5"/>
-      <c r="D51" s="183">
+      <c r="D51" s="168">
         <v>20038.91</v>
       </c>
       <c r="E51" s="171" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
@@ -2787,7 +2800,7 @@
         <v>32</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C52" s="5"/>
       <c r="D52" s="168">
@@ -2801,7 +2814,7 @@
       </c>
       <c r="B53" s="183"/>
       <c r="C53" s="5"/>
-      <c r="D53" s="183">
+      <c r="D53" s="168">
         <v>8423.4500000000007</v>
       </c>
       <c r="E53" s="179" t="str">
@@ -2815,11 +2828,11 @@
       </c>
       <c r="B54" s="5"/>
       <c r="C54" s="5"/>
-      <c r="D54" s="183">
+      <c r="D54" s="168">
         <v>5530.12</v>
       </c>
       <c r="E54" s="184" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.25">
@@ -2828,11 +2841,11 @@
       </c>
       <c r="B55" s="5"/>
       <c r="C55" s="5"/>
-      <c r="D55" s="183">
+      <c r="D55" s="168">
         <v>2086018.93</v>
       </c>
       <c r="E55" s="184" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.25">
@@ -2841,29 +2854,29 @@
       </c>
       <c r="B56" s="5"/>
       <c r="C56" s="5"/>
-      <c r="D56" s="183">
+      <c r="D56" s="168">
         <v>25159.5</v>
       </c>
       <c r="E56" s="184" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A57" s="207" t="s">
+      <c r="A57" s="215" t="s">
         <v>35</v>
       </c>
-      <c r="B57" s="208"/>
+      <c r="B57" s="216"/>
       <c r="C57" s="5"/>
-      <c r="D57" s="183">
+      <c r="D57" s="168">
         <v>2177347.2799999998</v>
       </c>
       <c r="E57" s="184" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
     </row>
     <row r="58" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="207"/>
-      <c r="B58" s="208"/>
+      <c r="A58" s="215"/>
+      <c r="B58" s="216"/>
       <c r="C58" s="154"/>
       <c r="D58" s="201"/>
       <c r="E58" s="202"/>
@@ -2890,90 +2903,90 @@
       <c r="E60" s="176"/>
     </row>
     <row r="61" spans="1:5" ht="29.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="215" t="s">
-        <v>207</v>
-      </c>
-      <c r="B61" s="208"/>
+      <c r="A61" s="221" t="s">
+        <v>206</v>
+      </c>
+      <c r="B61" s="216"/>
       <c r="C61" s="54"/>
-      <c r="D61" s="242">
+      <c r="D61" s="212">
         <v>70000</v>
       </c>
       <c r="E61" s="180" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
     </row>
     <row r="62" spans="1:5" ht="29.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="243" t="s">
-        <v>231</v>
-      </c>
-      <c r="B62" s="244"/>
-      <c r="C62" s="243"/>
-      <c r="D62" s="245">
+      <c r="A62" s="207" t="s">
+        <v>229</v>
+      </c>
+      <c r="B62" s="208"/>
+      <c r="C62" s="207"/>
+      <c r="D62" s="213">
         <v>175500</v>
       </c>
-      <c r="E62" s="246" t="s">
-        <v>221</v>
+      <c r="E62" s="209" t="s">
+        <v>219</v>
       </c>
     </row>
     <row r="63" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="243" t="s">
+      <c r="A63" s="207" t="s">
+        <v>228</v>
+      </c>
+      <c r="B63" s="208"/>
+      <c r="C63" s="207"/>
+      <c r="D63" s="213">
+        <v>222600</v>
+      </c>
+      <c r="E63" s="209" t="s">
         <v>230</v>
       </c>
-      <c r="B63" s="244"/>
-      <c r="C63" s="243"/>
-      <c r="D63" s="245">
-        <v>222600</v>
-      </c>
-      <c r="E63" s="246" t="s">
-        <v>232</v>
-      </c>
     </row>
     <row r="64" spans="1:5" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="243" t="s">
+      <c r="A64" s="207" t="s">
         <v>38</v>
       </c>
       <c r="B64" s="155"/>
       <c r="C64" s="5"/>
-      <c r="D64" s="183">
+      <c r="D64" s="168">
         <v>56800</v>
       </c>
-      <c r="E64" s="246" t="s">
-        <v>233</v>
+      <c r="E64" s="209" t="s">
+        <v>231</v>
       </c>
     </row>
     <row r="65" spans="1:10" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="215" t="s">
-        <v>238</v>
-      </c>
-      <c r="B65" s="216"/>
+      <c r="A65" s="221" t="s">
+        <v>236</v>
+      </c>
+      <c r="B65" s="222"/>
       <c r="C65" s="5"/>
-      <c r="D65" s="141">
+      <c r="D65" s="116">
         <v>250000</v>
       </c>
-      <c r="E65" s="246" t="s">
-        <v>239</v>
+      <c r="E65" s="209" t="s">
+        <v>237</v>
       </c>
     </row>
     <row r="66" spans="1:10" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="215" t="s">
-        <v>222</v>
-      </c>
-      <c r="B66" s="216"/>
+      <c r="A66" s="221" t="s">
+        <v>220</v>
+      </c>
+      <c r="B66" s="222"/>
       <c r="C66" s="195"/>
-      <c r="D66" s="141">
+      <c r="D66" s="116">
         <v>350000</v>
       </c>
       <c r="E66" s="180" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
     </row>
     <row r="67" spans="1:10" ht="39" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="211" t="s">
-        <v>226</v>
-      </c>
-      <c r="B67" s="212"/>
+      <c r="A67" s="219" t="s">
+        <v>224</v>
+      </c>
+      <c r="B67" s="220"/>
       <c r="C67" s="51"/>
-      <c r="D67" s="141">
+      <c r="D67" s="116">
         <v>24100</v>
       </c>
       <c r="E67" s="180"/>
@@ -2984,66 +2997,66 @@
       </c>
       <c r="B68" s="204"/>
       <c r="C68" s="51"/>
-      <c r="D68" s="141">
+      <c r="D68" s="116">
         <v>276800</v>
       </c>
       <c r="E68" s="180" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
     </row>
     <row r="69" spans="1:10" ht="39" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="211" t="s">
-        <v>228</v>
-      </c>
-      <c r="B69" s="212"/>
+      <c r="A69" s="219" t="s">
+        <v>226</v>
+      </c>
+      <c r="B69" s="220"/>
       <c r="C69" s="51"/>
-      <c r="D69" s="141">
+      <c r="D69" s="116">
         <v>2468400</v>
       </c>
       <c r="E69" s="180" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
     </row>
     <row r="70" spans="1:10" ht="39" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A70" s="211" t="s">
-        <v>236</v>
-      </c>
-      <c r="B70" s="212"/>
+      <c r="A70" s="219" t="s">
+        <v>234</v>
+      </c>
+      <c r="B70" s="220"/>
       <c r="C70" s="51"/>
-      <c r="D70" s="141">
+      <c r="D70" s="116">
         <v>550000</v>
       </c>
       <c r="E70" s="180" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
     </row>
     <row r="71" spans="1:10" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="215" t="s">
+      <c r="A71" s="221" t="s">
+        <v>239</v>
+      </c>
+      <c r="B71" s="222"/>
+      <c r="C71" s="5"/>
+      <c r="D71" s="116">
+        <v>190000</v>
+      </c>
+      <c r="E71" s="180" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="72" spans="1:10" ht="61.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A72" s="221" t="s">
         <v>241</v>
       </c>
-      <c r="B71" s="216"/>
-      <c r="C71" s="5"/>
-      <c r="D71" s="141">
-        <v>190000</v>
-      </c>
-      <c r="E71" s="180" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="72" spans="1:10" ht="61.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="215" t="s">
-        <v>243</v>
-      </c>
-      <c r="B72" s="216"/>
+      <c r="B72" s="222"/>
       <c r="C72" s="5"/>
-      <c r="D72" s="141">
+      <c r="D72" s="116">
         <v>450000</v>
       </c>
       <c r="E72" s="180" t="s">
-        <v>242</v>
-      </c>
-      <c r="I72" s="207"/>
-      <c r="J72" s="208"/>
+        <v>240</v>
+      </c>
+      <c r="I72" s="215"/>
+      <c r="J72" s="216"/>
     </row>
     <row r="73" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A73" s="27" t="s">
@@ -3072,8 +3085,9 @@
       </c>
       <c r="B75" s="5"/>
       <c r="C75" s="5"/>
-      <c r="D75" s="183">
-        <v>228026.21</v>
+      <c r="D75" s="168">
+        <f>228026.21+1383.76</f>
+        <v>229409.97</v>
       </c>
       <c r="E75" s="178"/>
     </row>
@@ -3085,9 +3099,6 @@
       <c r="C76" s="5"/>
       <c r="D76" s="168"/>
       <c r="E76" s="118"/>
-      <c r="G76" t="s">
-        <v>206</v>
-      </c>
     </row>
     <row r="77" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A77" s="50" t="s">
@@ -3098,7 +3109,7 @@
       <c r="D77" s="119"/>
       <c r="E77" s="113">
         <f>SUM(D75:D76)</f>
-        <v>228026.21</v>
+        <v>229409.97</v>
       </c>
     </row>
     <row r="78" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -3109,15 +3120,13 @@
       <c r="E78" s="120"/>
     </row>
     <row r="79" spans="1:10" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A79" s="219" t="s">
-        <v>214</v>
-      </c>
-      <c r="B79" s="220"/>
-      <c r="C79" s="220"/>
-      <c r="D79" s="221"/>
-      <c r="E79" s="121">
-        <v>3500000</v>
-      </c>
+      <c r="A79" s="227" t="s">
+        <v>212</v>
+      </c>
+      <c r="B79" s="228"/>
+      <c r="C79" s="228"/>
+      <c r="D79" s="229"/>
+      <c r="E79" s="121"/>
     </row>
     <row r="80" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A80" s="1"/>
@@ -3134,14 +3143,14 @@
       <c r="D81" s="124"/>
       <c r="E81" s="196">
         <f>(SUM(E30:E79))</f>
-        <v>19293883.91</v>
+        <v>15795267.67</v>
       </c>
       <c r="F81" s="151"/>
       <c r="G81" s="42"/>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.25">
       <c r="D82" s="122"/>
-      <c r="E82" s="122"/>
+      <c r="E82" s="214"/>
       <c r="G82" s="151"/>
     </row>
     <row r="83" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -3158,22 +3167,22 @@
       <c r="E84" s="126"/>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A85" s="207"/>
-      <c r="B85" s="208"/>
+      <c r="A85" s="215"/>
+      <c r="B85" s="216"/>
       <c r="C85" s="5"/>
       <c r="D85" s="141"/>
       <c r="E85" s="114"/>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A86" s="207"/>
-      <c r="B86" s="208"/>
+      <c r="A86" s="215"/>
+      <c r="B86" s="216"/>
       <c r="C86" s="5"/>
       <c r="D86" s="116"/>
       <c r="E86" s="114"/>
     </row>
     <row r="87" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A87" s="215"/>
-      <c r="B87" s="208"/>
+      <c r="A87" s="221"/>
+      <c r="B87" s="216"/>
       <c r="C87" s="5"/>
       <c r="D87" s="116"/>
       <c r="E87" s="114"/>
@@ -3226,7 +3235,7 @@
       </c>
       <c r="B96" s="109">
         <f>E81</f>
-        <v>19293883.91</v>
+        <v>15795267.67</v>
       </c>
     </row>
     <row r="97" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -3235,7 +3244,7 @@
       </c>
       <c r="B97" s="109">
         <f>E81-E79</f>
-        <v>15793883.91</v>
+        <v>15795267.67</v>
       </c>
     </row>
     <row r="98" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -3258,25 +3267,25 @@
     </row>
     <row r="100" spans="1:5" ht="34.5" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="101" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A101" s="217"/>
-      <c r="B101" s="210"/>
-      <c r="C101" s="210"/>
-      <c r="D101" s="210"/>
-      <c r="E101" s="210"/>
+      <c r="A101" s="225"/>
+      <c r="B101" s="218"/>
+      <c r="C101" s="218"/>
+      <c r="D101" s="218"/>
+      <c r="E101" s="218"/>
     </row>
     <row r="102" spans="1:5" ht="106.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A102" s="210"/>
-      <c r="B102" s="210"/>
-      <c r="C102" s="210"/>
-      <c r="D102" s="210"/>
-      <c r="E102" s="210"/>
+      <c r="A102" s="218"/>
+      <c r="B102" s="218"/>
+      <c r="C102" s="218"/>
+      <c r="D102" s="218"/>
+      <c r="E102" s="218"/>
     </row>
     <row r="103" spans="1:5" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A103" s="210"/>
-      <c r="B103" s="210"/>
-      <c r="C103" s="210"/>
-      <c r="D103" s="210"/>
-      <c r="E103" s="210"/>
+      <c r="A103" s="218"/>
+      <c r="B103" s="218"/>
+      <c r="C103" s="218"/>
+      <c r="D103" s="218"/>
+      <c r="E103" s="218"/>
     </row>
     <row r="105" spans="1:5" ht="0.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="21" t="s">
@@ -3298,7 +3307,7 @@
       </c>
       <c r="B107" s="38">
         <f>PRORRATEO!I81</f>
-        <v>14136349.759999996</v>
+        <v>14326349.759999996</v>
       </c>
       <c r="C107" s="22"/>
     </row>
@@ -3314,7 +3323,7 @@
         <v>51</v>
       </c>
       <c r="B109" s="118">
-        <f>B131</f>
+        <f>B135</f>
         <v>453000</v>
       </c>
       <c r="C109" s="22"/>
@@ -3337,11 +3346,11 @@
       </c>
       <c r="B112" s="46">
         <f>-B97</f>
-        <v>-15793883.91</v>
+        <v>-15795267.67</v>
       </c>
       <c r="C112" s="22"/>
     </row>
-    <row r="113" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A113" s="26" t="s">
         <v>54</v>
       </c>
@@ -3351,33 +3360,33 @@
       </c>
       <c r="C113" s="22"/>
     </row>
-    <row r="114" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A114" s="30" t="s">
         <v>39</v>
       </c>
       <c r="B114" s="58">
         <f>SUM(B106:B113)</f>
-        <v>-1204534.1500000041</v>
+        <v>-1015917.9100000039</v>
       </c>
       <c r="C114" s="25"/>
       <c r="D114" s="42"/>
     </row>
-    <row r="115" spans="1:7" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:11" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B115" s="39"/>
       <c r="C115" s="25"/>
       <c r="D115" s="42"/>
       <c r="E115" s="138"/>
       <c r="F115" s="139"/>
     </row>
-    <row r="116" spans="1:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:11" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B116" s="40"/>
       <c r="C116" s="25"/>
     </row>
-    <row r="117" spans="1:7" s="36" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:11" s="36" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B117" s="39"/>
       <c r="C117" s="35"/>
     </row>
-    <row r="118" spans="1:7" s="36" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:11" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A118" s="143" t="s">
         <v>55</v>
       </c>
@@ -3387,16 +3396,16 @@
       <c r="C118" s="35"/>
       <c r="D118" s="45"/>
     </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A119" s="53" t="s">
         <v>56</v>
       </c>
       <c r="B119" s="148">
         <f>-B97</f>
-        <v>-15793883.91</v>
-      </c>
-    </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.25">
+        <v>-15795267.67</v>
+      </c>
+    </row>
+    <row r="120" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A120" s="53" t="s">
         <v>57</v>
       </c>
@@ -3404,131 +3413,179 @@
         <f>-B98</f>
         <v>0</v>
       </c>
-      <c r="G120" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H120" s="247"/>
+    </row>
+    <row r="121" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A121" s="53" t="s">
+        <v>243</v>
+      </c>
+      <c r="B121" s="148">
+        <v>-190000</v>
+      </c>
+      <c r="H121" s="247"/>
+    </row>
+    <row r="122" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A122" s="53" t="s">
+        <v>244</v>
+      </c>
+      <c r="B122" s="148">
+        <v>-112065.15</v>
+      </c>
+      <c r="H122" s="247"/>
+    </row>
+    <row r="123" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A123" s="53" t="s">
+        <v>245</v>
+      </c>
+      <c r="B123" s="148">
+        <v>-65440</v>
+      </c>
+      <c r="H123" s="247"/>
+    </row>
+    <row r="124" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A124" s="53" t="s">
         <v>58</v>
       </c>
-      <c r="B121" s="148">
-        <f>B131</f>
+      <c r="B124" s="148">
+        <f>B135</f>
         <v>453000</v>
       </c>
-    </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A122" s="53" t="s">
+      <c r="H124" s="247"/>
+    </row>
+    <row r="125" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A125" s="53" t="s">
         <v>59</v>
       </c>
-      <c r="B122" s="149">
+      <c r="B125" s="149">
         <f>PRORRATEO!I81</f>
-        <v>14136349.759999996</v>
-      </c>
-    </row>
-    <row r="123" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A123" s="150" t="s">
+        <v>14326349.759999996</v>
+      </c>
+    </row>
+    <row r="126" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A126" s="150" t="s">
         <v>60</v>
       </c>
-      <c r="B123" s="185"/>
-    </row>
-    <row r="124" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A124" s="146" t="s">
+      <c r="B126" s="185"/>
+      <c r="H126" s="247"/>
+    </row>
+    <row r="127" spans="1:11" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A127" s="146" t="s">
         <v>61</v>
       </c>
-      <c r="B124" s="147">
-        <f>SUM(B118:C123)</f>
-        <v>305579.44062301703</v>
-      </c>
-      <c r="D124" s="24"/>
-      <c r="F124" s="24"/>
-    </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A125" s="145"/>
-      <c r="B125" s="145"/>
-      <c r="F125" s="151"/>
-    </row>
-    <row r="126" spans="1:7" ht="34.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="127" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A127" s="218" t="s">
+      <c r="B127" s="147">
+        <f>SUM(B118:C126)</f>
+        <v>126690.53062301688</v>
+      </c>
+      <c r="D127" s="24"/>
+      <c r="F127" s="24"/>
+      <c r="G127" s="42"/>
+    </row>
+    <row r="128" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A128" s="145"/>
+      <c r="B128" s="145"/>
+      <c r="D128" s="24"/>
+      <c r="E128" s="24"/>
+      <c r="F128" s="151"/>
+      <c r="G128" s="42"/>
+      <c r="H128" s="42"/>
+      <c r="I128" s="42"/>
+      <c r="J128" s="42"/>
+      <c r="K128" s="247"/>
+    </row>
+    <row r="129" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="130" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A130" s="226" t="s">
         <v>62</v>
       </c>
-      <c r="B127" s="210"/>
-      <c r="C127" s="210"/>
-    </row>
-    <row r="128" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A128" s="210"/>
-      <c r="B128" s="210"/>
-      <c r="C128" s="210"/>
-    </row>
-    <row r="129" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A129" s="128" t="s">
-        <v>244</v>
-      </c>
-      <c r="B129" s="205">
-        <f>246000+107000+100000</f>
+      <c r="B130" s="218"/>
+      <c r="C130" s="218"/>
+    </row>
+    <row r="131" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A131" s="218"/>
+      <c r="B131" s="218"/>
+      <c r="C131" s="218"/>
+    </row>
+    <row r="132" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A132" s="128" t="s">
+        <v>242</v>
+      </c>
+      <c r="B132" s="205">
+        <f>246000</f>
+        <v>246000</v>
+      </c>
+      <c r="C132" s="34">
+        <v>40000</v>
+      </c>
+    </row>
+    <row r="133" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A133" s="128" t="s">
+        <v>242</v>
+      </c>
+      <c r="B133" s="205">
+        <v>100000</v>
+      </c>
+      <c r="C133" s="39"/>
+    </row>
+    <row r="134" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A134" s="128" t="s">
+        <v>242</v>
+      </c>
+      <c r="B134" s="130">
+        <v>107000</v>
+      </c>
+      <c r="C134" s="39"/>
+    </row>
+    <row r="135" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A135" s="43" t="s">
+        <v>39</v>
+      </c>
+      <c r="B135" s="129">
+        <f>SUM(B132:B134)</f>
         <v>453000</v>
       </c>
-      <c r="C129" s="34">
-        <v>40000</v>
-      </c>
-    </row>
-    <row r="130" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A130" s="128"/>
-      <c r="B130" s="130"/>
-      <c r="C130" s="39"/>
-    </row>
-    <row r="131" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A131" s="43" t="s">
-        <v>39</v>
-      </c>
-      <c r="B131" s="129">
-        <f>SUM(B129:B130)</f>
-        <v>453000</v>
-      </c>
-      <c r="C131" s="44"/>
-    </row>
-    <row r="132" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="M132" s="8"/>
-    </row>
-    <row r="133" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A133" s="217"/>
-      <c r="B133" s="210"/>
-      <c r="C133" s="210"/>
-      <c r="D133" s="210"/>
-      <c r="E133" s="210"/>
-    </row>
-    <row r="134" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A134" s="210"/>
-      <c r="B134" s="210"/>
-      <c r="C134" s="210"/>
-      <c r="D134" s="210"/>
-      <c r="E134" s="210"/>
-    </row>
-    <row r="135" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A135" s="210"/>
-      <c r="B135" s="210"/>
-      <c r="C135" s="210"/>
-      <c r="D135" s="210"/>
-      <c r="E135" s="210"/>
+      <c r="C135" s="44"/>
     </row>
     <row r="136" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A136" s="210"/>
-      <c r="B136" s="210"/>
-      <c r="C136" s="210"/>
-      <c r="D136" s="210"/>
-      <c r="E136" s="210"/>
+      <c r="M136" s="8"/>
+    </row>
+    <row r="137" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A137" s="225"/>
+      <c r="B137" s="218"/>
+      <c r="C137" s="218"/>
+      <c r="D137" s="218"/>
+      <c r="E137" s="218"/>
+    </row>
+    <row r="138" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A138" s="218"/>
+      <c r="B138" s="218"/>
+      <c r="C138" s="218"/>
+      <c r="D138" s="218"/>
+      <c r="E138" s="218"/>
+    </row>
+    <row r="139" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A139" s="218"/>
+      <c r="B139" s="218"/>
+      <c r="C139" s="218"/>
+      <c r="D139" s="218"/>
+      <c r="E139" s="218"/>
+    </row>
+    <row r="140" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A140" s="218"/>
+      <c r="B140" s="218"/>
+      <c r="C140" s="218"/>
+      <c r="D140" s="218"/>
+      <c r="E140" s="218"/>
     </row>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="A133:E136"/>
+    <mergeCell ref="A137:E140"/>
     <mergeCell ref="A101:E103"/>
     <mergeCell ref="A87:B87"/>
     <mergeCell ref="A58:B58"/>
     <mergeCell ref="A61:B61"/>
     <mergeCell ref="A86:B86"/>
     <mergeCell ref="A85:B85"/>
-    <mergeCell ref="A127:C128"/>
+    <mergeCell ref="A130:C131"/>
     <mergeCell ref="A79:D79"/>
     <mergeCell ref="A65:B65"/>
     <mergeCell ref="I72:J72"/>
@@ -3588,16 +3645,16 @@
       <c r="D1" s="6"/>
       <c r="E1" s="6"/>
       <c r="F1" s="6"/>
-      <c r="G1" s="228"/>
-      <c r="H1" s="210"/>
-      <c r="I1" s="210"/>
-      <c r="J1" s="210"/>
-      <c r="K1" s="210"/>
-      <c r="L1" s="210"/>
-      <c r="M1" s="210"/>
-      <c r="N1" s="210"/>
-      <c r="O1" s="210"/>
-      <c r="P1" s="210"/>
+      <c r="G1" s="236"/>
+      <c r="H1" s="218"/>
+      <c r="I1" s="218"/>
+      <c r="J1" s="218"/>
+      <c r="K1" s="218"/>
+      <c r="L1" s="218"/>
+      <c r="M1" s="218"/>
+      <c r="N1" s="218"/>
+      <c r="O1" s="218"/>
+      <c r="P1" s="218"/>
       <c r="Q1" s="6"/>
       <c r="R1" s="6"/>
     </row>
@@ -3622,12 +3679,12 @@
       <c r="M2" s="7"/>
       <c r="N2" s="6"/>
       <c r="O2" s="6"/>
-      <c r="P2" s="224">
-        <f>U2-P3</f>
-        <v>12623528.600000001</v>
-      </c>
-      <c r="Q2" s="210"/>
-      <c r="R2" s="210"/>
+      <c r="P2" s="232">
+        <f>U3</f>
+        <v>13278709.43</v>
+      </c>
+      <c r="Q2" s="218"/>
+      <c r="R2" s="218"/>
       <c r="S2" s="20"/>
       <c r="U2">
         <v>16123528.600000001</v>
@@ -3646,94 +3703,97 @@
       <c r="J3" s="6"/>
       <c r="K3" s="6"/>
       <c r="L3" s="6" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="M3" s="6"/>
       <c r="N3" s="6"/>
       <c r="O3" s="6"/>
-      <c r="P3" s="224">
+      <c r="P3" s="232">
         <v>3500000</v>
       </c>
-      <c r="Q3" s="210"/>
-      <c r="R3" s="210"/>
+      <c r="Q3" s="218"/>
+      <c r="R3" s="218"/>
+      <c r="U3">
+        <v>13278709.43</v>
+      </c>
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A4" s="235" t="s">
+      <c r="A4" s="243" t="s">
         <v>64</v>
       </c>
-      <c r="B4" s="237" t="s">
+      <c r="B4" s="245" t="s">
         <v>65</v>
       </c>
       <c r="C4" s="132"/>
-      <c r="D4" s="225" t="s">
+      <c r="D4" s="233" t="s">
         <v>66</v>
       </c>
-      <c r="E4" s="225" t="s">
+      <c r="E4" s="233" t="s">
         <v>67</v>
       </c>
-      <c r="F4" s="234" t="s">
+      <c r="F4" s="242" t="s">
         <v>68</v>
       </c>
-      <c r="G4" s="225" t="s">
+      <c r="G4" s="233" t="s">
         <v>69</v>
       </c>
-      <c r="H4" s="232" t="s">
+      <c r="H4" s="240" t="s">
         <v>70</v>
       </c>
-      <c r="I4" s="225" t="s">
+      <c r="I4" s="233" t="s">
         <v>50</v>
       </c>
-      <c r="J4" s="234" t="s">
+      <c r="J4" s="242" t="s">
         <v>71</v>
       </c>
-      <c r="K4" s="236" t="s">
+      <c r="K4" s="244" t="s">
         <v>72</v>
       </c>
-      <c r="L4" s="232" t="s">
+      <c r="L4" s="240" t="s">
         <v>73</v>
       </c>
-      <c r="M4" s="231" t="s">
-        <v>215</v>
-      </c>
-      <c r="N4" s="232" t="s">
+      <c r="M4" s="239" t="s">
+        <v>213</v>
+      </c>
+      <c r="N4" s="240" t="s">
         <v>75</v>
       </c>
-      <c r="O4" s="226" t="s">
+      <c r="O4" s="234" t="s">
         <v>76</v>
       </c>
       <c r="P4" s="62" t="s">
         <v>77</v>
       </c>
-      <c r="Q4" s="229" t="s">
+      <c r="Q4" s="237" t="s">
         <v>78</v>
       </c>
-      <c r="R4" s="222" t="s">
+      <c r="R4" s="230" t="s">
         <v>79</v>
       </c>
       <c r="U4" s="42"/>
     </row>
     <row r="5" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="223"/>
-      <c r="B5" s="230"/>
+      <c r="A5" s="231"/>
+      <c r="B5" s="238"/>
       <c r="C5" s="133"/>
-      <c r="D5" s="223"/>
-      <c r="E5" s="223"/>
-      <c r="F5" s="233"/>
-      <c r="G5" s="223"/>
-      <c r="H5" s="233"/>
-      <c r="I5" s="223"/>
-      <c r="J5" s="233"/>
-      <c r="K5" s="233"/>
-      <c r="L5" s="233"/>
-      <c r="M5" s="223"/>
-      <c r="N5" s="233"/>
-      <c r="O5" s="227"/>
+      <c r="D5" s="231"/>
+      <c r="E5" s="231"/>
+      <c r="F5" s="241"/>
+      <c r="G5" s="231"/>
+      <c r="H5" s="241"/>
+      <c r="I5" s="231"/>
+      <c r="J5" s="241"/>
+      <c r="K5" s="241"/>
+      <c r="L5" s="241"/>
+      <c r="M5" s="231"/>
+      <c r="N5" s="241"/>
+      <c r="O5" s="235"/>
       <c r="P5" s="60" t="str">
         <f>RESUMEN!B9</f>
         <v>VTO 15/10</v>
       </c>
-      <c r="Q5" s="230"/>
-      <c r="R5" s="223"/>
+      <c r="Q5" s="238"/>
+      <c r="R5" s="231"/>
     </row>
     <row r="6" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
@@ -3756,7 +3816,7 @@
       <c r="H6" s="72">
         <v>82681.009999999995</v>
       </c>
-      <c r="I6" s="247">
+      <c r="I6" s="73">
         <f>1024281-I13-I7-I47-I48-I59-I69-I73</f>
         <v>82680.190000000061</v>
       </c>
@@ -3775,22 +3835,22 @@
       </c>
       <c r="N6" s="77">
         <f>P$2*G6%</f>
-        <v>64771.325246600012</v>
+        <v>68133.058085330005</v>
       </c>
       <c r="O6" s="78">
         <v>0</v>
       </c>
       <c r="P6" s="79">
         <f t="shared" ref="P6:P37" si="2">ROUND(SUM(K6:O6),0) + S6</f>
-        <v>82731.009999999995</v>
+        <v>86092.01</v>
       </c>
       <c r="Q6" s="80">
         <f t="shared" ref="Q6:Q37" si="3">ROUND(P6*6% + P6,0) + S6</f>
-        <v>87695.01</v>
+        <v>91258.01</v>
       </c>
       <c r="R6" s="81">
         <f t="shared" ref="R6:R37" si="4">ROUND(P6*3%,0) + P6</f>
-        <v>85213.01</v>
+        <v>88675.01</v>
       </c>
       <c r="S6" s="42">
         <v>0.01</v>
@@ -3821,7 +3881,7 @@
       <c r="H7" s="72">
         <v>98660.02</v>
       </c>
-      <c r="I7" s="247">
+      <c r="I7" s="73">
         <f>H7</f>
         <v>98660.02</v>
       </c>
@@ -3840,22 +3900,22 @@
       </c>
       <c r="N7" s="77">
         <f t="shared" ref="N7:N37" si="7">P$2*G7%</f>
-        <v>77243.37150340002</v>
+        <v>81252.423002170006</v>
       </c>
       <c r="O7" s="78">
         <v>0</v>
       </c>
       <c r="P7" s="79">
         <f t="shared" si="2"/>
-        <v>98660.02</v>
+        <v>102669.02</v>
       </c>
       <c r="Q7" s="80">
         <f t="shared" si="3"/>
-        <v>104580.02</v>
+        <v>108829.02</v>
       </c>
       <c r="R7" s="81">
         <f t="shared" si="4"/>
-        <v>101620.02</v>
+        <v>105749.02</v>
       </c>
       <c r="S7" s="42">
         <f t="shared" ref="S7:S38" si="8">S6+0.01</f>
@@ -3885,7 +3945,7 @@
       <c r="H8" s="72">
         <v>101553.03</v>
       </c>
-      <c r="I8" s="247">
+      <c r="I8" s="73">
         <f t="shared" ref="I8:I13" si="9">H8</f>
         <v>101553.03</v>
       </c>
@@ -3904,22 +3964,22 @@
       </c>
       <c r="N8" s="77">
         <f t="shared" si="7"/>
-        <v>77192.877389000016</v>
+        <v>81199.308164450005</v>
       </c>
       <c r="O8" s="78">
         <v>0</v>
       </c>
       <c r="P8" s="79">
         <f t="shared" si="2"/>
-        <v>98595.03</v>
+        <v>102602.03</v>
       </c>
       <c r="Q8" s="80">
         <f t="shared" si="3"/>
-        <v>104511.03</v>
+        <v>108758.03</v>
       </c>
       <c r="R8" s="81">
         <f t="shared" si="4"/>
-        <v>101553.03</v>
+        <v>105680.03</v>
       </c>
       <c r="S8" s="42">
         <f t="shared" si="8"/>
@@ -3948,7 +4008,7 @@
       <c r="H9" s="72">
         <v>83585.039999999994</v>
       </c>
-      <c r="I9" s="247">
+      <c r="I9" s="73">
         <f t="shared" si="9"/>
         <v>83585.039999999994</v>
       </c>
@@ -3967,22 +4027,22 @@
       </c>
       <c r="N9" s="77">
         <f t="shared" si="7"/>
-        <v>63534.219443800001</v>
+        <v>66831.744561189989</v>
       </c>
       <c r="O9" s="78">
         <v>0</v>
       </c>
       <c r="P9" s="79">
         <f t="shared" si="2"/>
-        <v>81150.039999999994</v>
+        <v>84447.039999999994</v>
       </c>
       <c r="Q9" s="80">
         <f t="shared" si="3"/>
-        <v>86019.04</v>
+        <v>89514.04</v>
       </c>
       <c r="R9" s="81">
         <f t="shared" si="4"/>
-        <v>83585.039999999994</v>
+        <v>86980.04</v>
       </c>
       <c r="S9" s="42">
         <f t="shared" si="8"/>
@@ -4012,7 +4072,7 @@
       <c r="H10" s="72">
         <v>83585.05</v>
       </c>
-      <c r="I10" s="247">
+      <c r="I10" s="73">
         <f t="shared" si="9"/>
         <v>83585.05</v>
       </c>
@@ -4031,22 +4091,22 @@
       </c>
       <c r="N10" s="77">
         <f t="shared" si="7"/>
-        <v>63534.219443800001</v>
+        <v>66831.744561189989</v>
       </c>
       <c r="O10" s="78">
         <v>0</v>
       </c>
       <c r="P10" s="79">
         <f t="shared" si="2"/>
-        <v>81150.05</v>
+        <v>84447.05</v>
       </c>
       <c r="Q10" s="80">
         <f t="shared" si="3"/>
-        <v>86019.05</v>
+        <v>89514.05</v>
       </c>
       <c r="R10" s="81">
         <f t="shared" si="4"/>
-        <v>83585.05</v>
+        <v>86980.05</v>
       </c>
       <c r="S10" s="42">
         <f t="shared" si="8"/>
@@ -4078,7 +4138,7 @@
       <c r="H11" s="72">
         <v>120910.06</v>
       </c>
-      <c r="I11" s="247">
+      <c r="I11" s="73">
         <f t="shared" si="9"/>
         <v>120910.06</v>
       </c>
@@ -4097,22 +4157,22 @@
       </c>
       <c r="N11" s="77">
         <f t="shared" si="7"/>
-        <v>94663.840971400015</v>
+        <v>99577.042015569998</v>
       </c>
       <c r="O11" s="78">
         <v>0</v>
       </c>
       <c r="P11" s="79">
         <f t="shared" si="2"/>
-        <v>120910.06</v>
+        <v>125824.06</v>
       </c>
       <c r="Q11" s="80">
         <f t="shared" si="3"/>
-        <v>128165.06</v>
+        <v>133374.06</v>
       </c>
       <c r="R11" s="81">
         <f t="shared" si="4"/>
-        <v>124537.06</v>
+        <v>129599.06</v>
       </c>
       <c r="S11" s="42">
         <f t="shared" si="8"/>
@@ -4143,7 +4203,7 @@
       <c r="H12" s="72">
         <v>87470.07</v>
       </c>
-      <c r="I12" s="247">
+      <c r="I12" s="73">
         <f t="shared" si="9"/>
         <v>87470.07</v>
       </c>
@@ -4162,22 +4222,22 @@
       </c>
       <c r="N12" s="77">
         <f t="shared" si="7"/>
-        <v>68482.642655000003</v>
+        <v>72036.998657749995</v>
       </c>
       <c r="O12" s="78">
         <v>0</v>
       </c>
       <c r="P12" s="79">
         <f t="shared" si="2"/>
-        <v>87470.07</v>
+        <v>91024.07</v>
       </c>
       <c r="Q12" s="80">
         <f t="shared" si="3"/>
-        <v>92718.07</v>
+        <v>96486.07</v>
       </c>
       <c r="R12" s="81">
         <f t="shared" si="4"/>
-        <v>90094.07</v>
+        <v>93755.07</v>
       </c>
       <c r="S12" s="42">
         <f t="shared" si="8"/>
@@ -4206,7 +4266,7 @@
       <c r="H13" s="72">
         <v>73152.08</v>
       </c>
-      <c r="I13" s="247">
+      <c r="I13" s="73">
         <f t="shared" si="9"/>
         <v>73152.08</v>
       </c>
@@ -4225,22 +4285,22 @@
       </c>
       <c r="N13" s="77">
         <f t="shared" si="7"/>
-        <v>57272.949258200009</v>
+        <v>60245.504683910003</v>
       </c>
       <c r="O13" s="78">
         <v>0</v>
       </c>
       <c r="P13" s="79">
         <f t="shared" si="2"/>
-        <v>73152.08</v>
+        <v>76125.08</v>
       </c>
       <c r="Q13" s="80">
         <f t="shared" si="3"/>
-        <v>77541.08</v>
+        <v>80693.08</v>
       </c>
       <c r="R13" s="81">
         <f t="shared" si="4"/>
-        <v>75347.08</v>
+        <v>78409.08</v>
       </c>
       <c r="S13" s="42">
         <f t="shared" si="8"/>
@@ -4287,22 +4347,22 @@
       </c>
       <c r="N14" s="77">
         <f t="shared" si="7"/>
-        <v>66197.783978399995</v>
+        <v>69633.552250919995</v>
       </c>
       <c r="O14" s="78">
         <v>0</v>
       </c>
       <c r="P14" s="79">
         <f t="shared" si="2"/>
-        <v>171640.09</v>
+        <v>175076.09</v>
       </c>
       <c r="Q14" s="80">
         <f t="shared" si="3"/>
-        <v>181938.09</v>
+        <v>185581.09</v>
       </c>
       <c r="R14" s="81">
         <f t="shared" si="4"/>
-        <v>176789.09</v>
+        <v>180328.09</v>
       </c>
       <c r="S14" s="42">
         <f t="shared" si="8"/>
@@ -4352,22 +4412,22 @@
       </c>
       <c r="N15" s="77">
         <f t="shared" si="7"/>
-        <v>53523.761264000008</v>
+        <v>56301.727983199999</v>
       </c>
       <c r="O15" s="78">
         <v>0</v>
       </c>
       <c r="P15" s="79">
         <f t="shared" si="2"/>
-        <v>72757.100000000006</v>
+        <v>75535.100000000006</v>
       </c>
       <c r="Q15" s="80">
         <f t="shared" si="3"/>
-        <v>77123.100000000006</v>
+        <v>80067.100000000006</v>
       </c>
       <c r="R15" s="81">
         <f t="shared" si="4"/>
-        <v>74940.100000000006</v>
+        <v>77801.100000000006</v>
       </c>
       <c r="S15" s="42">
         <f t="shared" si="8"/>
@@ -4417,22 +4477,22 @@
       </c>
       <c r="N16" s="77">
         <f t="shared" si="7"/>
-        <v>290757.73424380005</v>
+        <v>305848.51430119004</v>
       </c>
       <c r="O16" s="206">
         <v>0</v>
       </c>
       <c r="P16" s="79">
         <f t="shared" si="2"/>
-        <v>5178513.1100000003</v>
+        <v>5193604.1100000003</v>
       </c>
       <c r="Q16" s="80">
         <f t="shared" si="3"/>
-        <v>5489224.1100000003</v>
+        <v>5505220.1100000003</v>
       </c>
       <c r="R16" s="81">
         <f t="shared" si="4"/>
-        <v>5333868.1100000003</v>
+        <v>5349412.1100000003</v>
       </c>
       <c r="S16" s="42">
         <f t="shared" si="8"/>
@@ -4481,22 +4541,22 @@
       </c>
       <c r="N17" s="77">
         <f t="shared" si="7"/>
-        <v>347058.67179980007</v>
+        <v>365071.55835899001</v>
       </c>
       <c r="O17" s="78">
         <v>0</v>
       </c>
       <c r="P17" s="79">
         <f t="shared" si="2"/>
-        <v>899867.12</v>
+        <v>917880.12</v>
       </c>
       <c r="Q17" s="80">
         <f t="shared" si="3"/>
-        <v>953859.12</v>
+        <v>972953.12</v>
       </c>
       <c r="R17" s="81">
         <f t="shared" si="4"/>
-        <v>926863.12</v>
+        <v>945416.12</v>
       </c>
       <c r="S17" s="42">
         <f t="shared" si="8"/>
@@ -4529,7 +4589,7 @@
       <c r="H18" s="72">
         <v>371373.13</v>
       </c>
-      <c r="I18" s="247">
+      <c r="I18" s="73">
         <f>H18</f>
         <v>371373.13</v>
       </c>
@@ -4548,22 +4608,22 @@
       </c>
       <c r="N18" s="77">
         <f t="shared" si="7"/>
-        <v>290757.73424380005</v>
+        <v>305848.51430119004</v>
       </c>
       <c r="O18" s="78">
         <v>0</v>
       </c>
       <c r="P18" s="79">
         <f t="shared" si="2"/>
-        <v>371373.13</v>
+        <v>386464.13</v>
       </c>
       <c r="Q18" s="80">
         <f t="shared" si="3"/>
-        <v>393656.13</v>
+        <v>409652.13</v>
       </c>
       <c r="R18" s="81">
         <f t="shared" si="4"/>
-        <v>382514.13</v>
+        <v>398058.13</v>
       </c>
       <c r="S18" s="42">
         <f t="shared" si="8"/>
@@ -4596,17 +4656,18 @@
       <c r="H19" s="72">
         <v>786108.14</v>
       </c>
-      <c r="I19" s="247">
-        <v>47000.14</v>
+      <c r="I19" s="73">
+        <f>190000+47000.14</f>
+        <v>237000.14</v>
       </c>
       <c r="J19" s="74"/>
       <c r="K19" s="75">
         <f t="shared" si="0"/>
-        <v>739108</v>
+        <v>549108</v>
       </c>
       <c r="L19" s="75">
         <f t="shared" si="1"/>
-        <v>22173.239999999998</v>
+        <v>16473.239999999998</v>
       </c>
       <c r="M19" s="76">
         <f t="shared" si="6"/>
@@ -4614,22 +4675,22 @@
       </c>
       <c r="N19" s="77">
         <f t="shared" si="7"/>
-        <v>332857.20212480001</v>
+        <v>350133.01025023998</v>
       </c>
       <c r="O19" s="78">
         <v>0</v>
       </c>
       <c r="P19" s="79">
         <f t="shared" si="2"/>
-        <v>1186426.1399999999</v>
+        <v>1008002.14</v>
       </c>
       <c r="Q19" s="80">
         <f t="shared" si="3"/>
-        <v>1257612.1399999999</v>
+        <v>1068482.1399999999</v>
       </c>
       <c r="R19" s="81">
         <f t="shared" si="4"/>
-        <v>1222019.1399999999</v>
+        <v>1038242.14</v>
       </c>
       <c r="S19" s="42">
         <f t="shared" si="8"/>
@@ -4663,7 +4724,7 @@
       <c r="H20" s="72">
         <v>379499.15</v>
       </c>
-      <c r="I20" s="247">
+      <c r="I20" s="73">
         <f>H20</f>
         <v>379499.15</v>
       </c>
@@ -4682,22 +4743,22 @@
       </c>
       <c r="N20" s="77">
         <f t="shared" si="7"/>
-        <v>297119.99265820003</v>
+        <v>312540.98385391</v>
       </c>
       <c r="O20" s="78">
         <v>0</v>
       </c>
       <c r="P20" s="79">
         <f t="shared" si="2"/>
-        <v>379499.15</v>
+        <v>394920.15</v>
       </c>
       <c r="Q20" s="80">
         <f t="shared" si="3"/>
-        <v>402269.15</v>
+        <v>418615.15</v>
       </c>
       <c r="R20" s="81">
         <f t="shared" si="4"/>
-        <v>390884.15</v>
+        <v>406768.15</v>
       </c>
       <c r="S20" s="42">
         <f t="shared" si="8"/>
@@ -4730,7 +4791,7 @@
       <c r="H21" s="72">
         <v>426903.16</v>
       </c>
-      <c r="I21" s="247">
+      <c r="I21" s="73">
         <f>H21</f>
         <v>426903.16</v>
       </c>
@@ -4749,22 +4810,22 @@
       </c>
       <c r="N21" s="77">
         <f t="shared" si="7"/>
-        <v>334233.16674220003</v>
+        <v>351580.38957811001</v>
       </c>
       <c r="O21" s="78">
         <v>0</v>
       </c>
       <c r="P21" s="79">
         <f t="shared" si="2"/>
-        <v>426903.16</v>
+        <v>444250.16</v>
       </c>
       <c r="Q21" s="80">
         <f t="shared" si="3"/>
-        <v>452517.16</v>
+        <v>470905.16</v>
       </c>
       <c r="R21" s="81">
         <f t="shared" si="4"/>
-        <v>439710.16</v>
+        <v>457578.16</v>
       </c>
       <c r="S21" s="42">
         <f t="shared" si="8"/>
@@ -4798,7 +4859,7 @@
       <c r="H22" s="73">
         <v>374630.17</v>
       </c>
-      <c r="I22" s="247">
+      <c r="I22" s="73">
         <f>H22</f>
         <v>374630.17</v>
       </c>
@@ -4817,22 +4878,22 @@
       </c>
       <c r="N22" s="77">
         <f t="shared" si="7"/>
-        <v>293307.68702100008</v>
+        <v>308530.81360605004</v>
       </c>
       <c r="O22" s="78">
         <v>0</v>
       </c>
       <c r="P22" s="79">
         <f t="shared" si="2"/>
-        <v>374630.17</v>
+        <v>389853.17</v>
       </c>
       <c r="Q22" s="80">
         <f t="shared" si="3"/>
-        <v>397108.17</v>
+        <v>413244.17</v>
       </c>
       <c r="R22" s="81">
         <f t="shared" si="4"/>
-        <v>385869.17</v>
+        <v>401549.17</v>
       </c>
       <c r="S22" s="42">
         <f t="shared" si="8"/>
@@ -4865,7 +4926,7 @@
       <c r="H23" s="72">
         <v>458795.18</v>
       </c>
-      <c r="I23" s="247">
+      <c r="I23" s="73">
         <v>420000</v>
       </c>
       <c r="J23" s="74"/>
@@ -4883,22 +4944,22 @@
       </c>
       <c r="N23" s="77">
         <f t="shared" si="7"/>
-        <v>339320.44876800006</v>
+        <v>356931.70947840001</v>
       </c>
       <c r="O23" s="78">
         <v>0</v>
       </c>
       <c r="P23" s="79">
         <f t="shared" si="2"/>
-        <v>473359.18</v>
+        <v>490971.18</v>
       </c>
       <c r="Q23" s="80">
         <f t="shared" si="3"/>
-        <v>501761.18</v>
+        <v>520429.18</v>
       </c>
       <c r="R23" s="81">
         <f t="shared" si="4"/>
-        <v>487560.18</v>
+        <v>505700.18</v>
       </c>
       <c r="S23" s="42">
         <f t="shared" si="8"/>
@@ -4932,7 +4993,7 @@
       <c r="H24" s="72">
         <v>380515.19</v>
       </c>
-      <c r="I24" s="247">
+      <c r="I24" s="73">
         <f>H24</f>
         <v>380515.19</v>
       </c>
@@ -4951,22 +5012,22 @@
       </c>
       <c r="N24" s="77">
         <f t="shared" si="7"/>
-        <v>297915.27496000001</v>
+        <v>313377.542548</v>
       </c>
       <c r="O24" s="78">
         <v>0</v>
       </c>
       <c r="P24" s="79">
         <f t="shared" si="2"/>
-        <v>380515.19</v>
+        <v>395978.19</v>
       </c>
       <c r="Q24" s="80">
         <f t="shared" si="3"/>
-        <v>403346.19</v>
+        <v>419737.19</v>
       </c>
       <c r="R24" s="81">
         <f t="shared" si="4"/>
-        <v>391930.19</v>
+        <v>407857.19</v>
       </c>
       <c r="S24" s="42">
         <f t="shared" si="8"/>
@@ -4997,7 +5058,7 @@
       <c r="H25" s="72">
         <v>431668.2</v>
       </c>
-      <c r="I25" s="247">
+      <c r="I25" s="73">
         <v>445000</v>
       </c>
       <c r="J25" s="74"/>
@@ -5015,22 +5076,22 @@
       </c>
       <c r="N25" s="77">
         <f t="shared" si="7"/>
-        <v>343145.37793380005</v>
+        <v>360955.15843569004</v>
       </c>
       <c r="O25" s="78">
         <v>0</v>
       </c>
       <c r="P25" s="79">
         <f t="shared" si="2"/>
-        <v>424954.2</v>
+        <v>442764.2</v>
       </c>
       <c r="Q25" s="80">
         <f t="shared" si="3"/>
-        <v>450451.20000000001</v>
+        <v>469330.2</v>
       </c>
       <c r="R25" s="81">
         <f t="shared" si="4"/>
-        <v>437703.2</v>
+        <v>456047.2</v>
       </c>
       <c r="S25" s="42">
         <f t="shared" si="8"/>
@@ -5061,7 +5122,7 @@
       <c r="H26" s="72">
         <v>371373.21</v>
       </c>
-      <c r="I26" s="247">
+      <c r="I26" s="73">
         <f>H26</f>
         <v>371373.21</v>
       </c>
@@ -5080,22 +5141,22 @@
       </c>
       <c r="N26" s="77">
         <f t="shared" si="7"/>
-        <v>290757.73424380005</v>
+        <v>305848.51430119004</v>
       </c>
       <c r="O26" s="78">
         <v>0</v>
       </c>
       <c r="P26" s="79">
         <f t="shared" si="2"/>
-        <v>371373.21</v>
+        <v>386464.21</v>
       </c>
       <c r="Q26" s="80">
         <f t="shared" si="3"/>
-        <v>393656.21</v>
+        <v>409652.21</v>
       </c>
       <c r="R26" s="81">
         <f t="shared" si="4"/>
-        <v>382514.21</v>
+        <v>398058.21</v>
       </c>
       <c r="S26" s="42">
         <f t="shared" si="8"/>
@@ -5144,22 +5205,22 @@
       </c>
       <c r="N27" s="77">
         <f t="shared" si="7"/>
-        <v>332756.21389600006</v>
+        <v>350026.78057480004</v>
       </c>
       <c r="O27" s="182">
         <v>0</v>
       </c>
       <c r="P27" s="79">
         <f t="shared" si="2"/>
-        <v>862783.22</v>
+        <v>880053.22</v>
       </c>
       <c r="Q27" s="80">
         <f t="shared" si="3"/>
-        <v>914550.22</v>
+        <v>932856.22</v>
       </c>
       <c r="R27" s="81">
         <f t="shared" si="4"/>
-        <v>888666.22</v>
+        <v>906455.22</v>
       </c>
       <c r="S27" s="42">
         <f t="shared" si="8"/>
@@ -5196,7 +5257,7 @@
       <c r="H28" s="72">
         <v>371373.23</v>
       </c>
-      <c r="I28" s="247">
+      <c r="I28" s="73">
         <f>H28</f>
         <v>371373.23</v>
       </c>
@@ -5215,22 +5276,22 @@
       </c>
       <c r="N28" s="77">
         <f t="shared" si="7"/>
-        <v>290757.73424380005</v>
+        <v>305848.51430119004</v>
       </c>
       <c r="O28" s="78">
         <v>0</v>
       </c>
       <c r="P28" s="79">
         <f t="shared" si="2"/>
-        <v>371373.23</v>
+        <v>386464.23</v>
       </c>
       <c r="Q28" s="80">
         <f t="shared" si="3"/>
-        <v>393656.23</v>
+        <v>409652.23</v>
       </c>
       <c r="R28" s="81">
         <f t="shared" si="4"/>
-        <v>382514.23</v>
+        <v>398058.23</v>
       </c>
       <c r="S28" s="42">
         <f t="shared" si="8"/>
@@ -5261,7 +5322,7 @@
       <c r="H29" s="72">
         <v>421775.24</v>
       </c>
-      <c r="I29" s="247">
+      <c r="I29" s="73">
         <f t="shared" ref="I29:I33" si="10">H29</f>
         <v>421775.24</v>
       </c>
@@ -5280,22 +5341,22 @@
       </c>
       <c r="N29" s="77">
         <f t="shared" si="7"/>
-        <v>330218.8846474</v>
+        <v>347357.75997936999</v>
       </c>
       <c r="O29" s="78">
         <v>0</v>
       </c>
       <c r="P29" s="79">
         <f t="shared" si="2"/>
-        <v>421775.24</v>
+        <v>438914.24</v>
       </c>
       <c r="Q29" s="80">
         <f t="shared" si="3"/>
-        <v>447082.23999999999</v>
+        <v>465249.24</v>
       </c>
       <c r="R29" s="81">
         <f t="shared" si="4"/>
-        <v>434428.24</v>
+        <v>452081.24</v>
       </c>
       <c r="S29" s="42">
         <f t="shared" si="8"/>
@@ -5326,7 +5387,7 @@
       <c r="H30" s="72">
         <v>379499.25</v>
       </c>
-      <c r="I30" s="247">
+      <c r="I30" s="73">
         <f t="shared" si="10"/>
         <v>379499.25</v>
       </c>
@@ -5345,22 +5406,22 @@
       </c>
       <c r="N30" s="77">
         <f t="shared" si="7"/>
-        <v>297119.99265820003</v>
+        <v>312540.98385391</v>
       </c>
       <c r="O30" s="78">
         <v>0</v>
       </c>
       <c r="P30" s="79">
         <f t="shared" si="2"/>
-        <v>379499.25</v>
+        <v>394920.25</v>
       </c>
       <c r="Q30" s="80">
         <f t="shared" si="3"/>
-        <v>402269.25</v>
+        <v>418615.25</v>
       </c>
       <c r="R30" s="81">
         <f t="shared" si="4"/>
-        <v>390884.25</v>
+        <v>406768.25</v>
       </c>
       <c r="S30" s="42">
         <f t="shared" si="8"/>
@@ -5393,7 +5454,7 @@
       <c r="H31" s="72">
         <v>426774.26</v>
       </c>
-      <c r="I31" s="247">
+      <c r="I31" s="73">
         <f t="shared" si="10"/>
         <v>426774.26</v>
       </c>
@@ -5412,22 +5473,22 @@
       </c>
       <c r="N31" s="77">
         <f t="shared" si="7"/>
-        <v>334132.17851340002</v>
+        <v>351474.15990267001</v>
       </c>
       <c r="O31" s="78">
         <v>0</v>
       </c>
       <c r="P31" s="79">
         <f t="shared" si="2"/>
-        <v>426774.26</v>
+        <v>444116.26</v>
       </c>
       <c r="Q31" s="80">
         <f t="shared" si="3"/>
-        <v>452381.26</v>
+        <v>470763.26</v>
       </c>
       <c r="R31" s="81">
         <f t="shared" si="4"/>
-        <v>439577.26</v>
+        <v>457439.26</v>
       </c>
       <c r="S31" s="42">
         <f t="shared" si="8"/>
@@ -5458,7 +5519,7 @@
       <c r="H32" s="72">
         <v>379499.27</v>
       </c>
-      <c r="I32" s="247">
+      <c r="I32" s="73">
         <f>H32</f>
         <v>379499.27</v>
       </c>
@@ -5477,22 +5538,22 @@
       </c>
       <c r="N32" s="77">
         <f t="shared" si="7"/>
-        <v>297119.99265820003</v>
+        <v>312540.98385391</v>
       </c>
       <c r="O32" s="78">
         <v>0</v>
       </c>
       <c r="P32" s="79">
         <f t="shared" si="2"/>
-        <v>379499.27</v>
+        <v>394920.27</v>
       </c>
       <c r="Q32" s="80">
         <f t="shared" si="3"/>
-        <v>402269.27</v>
+        <v>418615.27</v>
       </c>
       <c r="R32" s="81">
         <f t="shared" si="4"/>
-        <v>390884.27</v>
+        <v>406768.27</v>
       </c>
       <c r="S32" s="42">
         <f t="shared" si="8"/>
@@ -5523,7 +5584,7 @@
       <c r="H33" s="72">
         <v>429902.28</v>
       </c>
-      <c r="I33" s="247">
+      <c r="I33" s="73">
         <f t="shared" si="10"/>
         <v>429902.28</v>
       </c>
@@ -5542,22 +5603,22 @@
       </c>
       <c r="N33" s="77">
         <f t="shared" si="7"/>
-        <v>336581.14306180004</v>
+        <v>354050.22953209002</v>
       </c>
       <c r="O33" s="127">
         <v>0</v>
       </c>
       <c r="P33" s="79">
         <f t="shared" si="2"/>
-        <v>429902.28</v>
+        <v>447371.28</v>
       </c>
       <c r="Q33" s="80">
         <f t="shared" si="3"/>
-        <v>455696.28</v>
+        <v>474214.28</v>
       </c>
       <c r="R33" s="81">
         <f t="shared" si="4"/>
-        <v>442799.28</v>
+        <v>460792.28</v>
       </c>
       <c r="S33" s="42">
         <f t="shared" si="8"/>
@@ -5590,7 +5651,7 @@
       <c r="H34" s="72">
         <v>413139.29</v>
       </c>
-      <c r="I34" s="247">
+      <c r="I34" s="73">
         <f>H34</f>
         <v>413139.29</v>
       </c>
@@ -5609,22 +5670,22 @@
       </c>
       <c r="N34" s="77">
         <f t="shared" si="7"/>
-        <v>308973.48601360008</v>
+        <v>325009.69200868002</v>
       </c>
       <c r="O34" s="186">
         <v>18500</v>
       </c>
       <c r="P34" s="79">
         <f t="shared" si="2"/>
-        <v>413139.29</v>
+        <v>429176.29</v>
       </c>
       <c r="Q34" s="80">
         <f t="shared" si="3"/>
-        <v>437928.29</v>
+        <v>454927.29</v>
       </c>
       <c r="R34" s="81">
         <f t="shared" si="4"/>
-        <v>425533.29</v>
+        <v>442051.29</v>
       </c>
       <c r="S34" s="42">
         <f t="shared" si="8"/>
@@ -5655,7 +5716,7 @@
       <c r="H35" s="72">
         <v>438286.3</v>
       </c>
-      <c r="I35" s="247">
+      <c r="I35" s="73">
         <v>371260</v>
       </c>
       <c r="J35" s="74"/>
@@ -5673,22 +5734,22 @@
       </c>
       <c r="N35" s="77">
         <f t="shared" si="7"/>
-        <v>343145.37793380005</v>
+        <v>360955.15843569004</v>
       </c>
       <c r="O35" s="78">
         <v>0</v>
       </c>
       <c r="P35" s="79">
         <f t="shared" si="2"/>
-        <v>507323.3</v>
+        <v>525133.30000000005</v>
       </c>
       <c r="Q35" s="80">
         <f t="shared" si="3"/>
-        <v>537763.30000000005</v>
+        <v>556641.30000000005</v>
       </c>
       <c r="R35" s="81">
         <f t="shared" si="4"/>
-        <v>522543.3</v>
+        <v>540887.30000000005</v>
       </c>
       <c r="S35" s="42">
         <f t="shared" si="8"/>
@@ -5721,7 +5782,7 @@
       <c r="H36" s="73">
         <v>371260.31</v>
       </c>
-      <c r="I36" s="247">
+      <c r="I36" s="73">
         <f>H36</f>
         <v>371260.31</v>
       </c>
@@ -5740,22 +5801,22 @@
       </c>
       <c r="N36" s="140">
         <f t="shared" si="7"/>
-        <v>290669.36954360007</v>
+        <v>305755.56333517999</v>
       </c>
       <c r="O36" s="83">
         <v>0</v>
       </c>
       <c r="P36" s="79">
         <f t="shared" si="2"/>
-        <v>371260.31</v>
+        <v>386347.31</v>
       </c>
       <c r="Q36" s="80">
         <f t="shared" si="3"/>
-        <v>393536.31</v>
+        <v>409528.31</v>
       </c>
       <c r="R36" s="81">
         <f t="shared" si="4"/>
-        <v>382398.31</v>
+        <v>397937.31</v>
       </c>
       <c r="S36" s="42">
         <f t="shared" si="8"/>
@@ -5786,7 +5847,7 @@
       <c r="H37" s="72">
         <v>563280.31999999995</v>
       </c>
-      <c r="I37" s="247">
+      <c r="I37" s="73">
         <v>428273.23</v>
       </c>
       <c r="J37" s="74"/>
@@ -5804,22 +5865,22 @@
       </c>
       <c r="N37" s="77">
         <f t="shared" si="7"/>
-        <v>335306.16667320009</v>
+        <v>352709.07987966004</v>
       </c>
       <c r="O37" s="78">
         <v>0</v>
       </c>
       <c r="P37" s="79">
         <f t="shared" si="2"/>
-        <v>567330.31999999995</v>
+        <v>584733.31999999995</v>
       </c>
       <c r="Q37" s="80">
         <f t="shared" si="3"/>
-        <v>601370.31999999995</v>
+        <v>619817.31999999995</v>
       </c>
       <c r="R37" s="81">
         <f t="shared" si="4"/>
-        <v>584350.31999999995</v>
+        <v>602275.31999999995</v>
       </c>
       <c r="S37" s="42">
         <f t="shared" si="8"/>
@@ -5850,7 +5911,7 @@
       <c r="H38" s="72">
         <v>376372.33</v>
       </c>
-      <c r="I38" s="247">
+      <c r="I38" s="73">
         <f t="shared" ref="I38:I40" si="11">H38</f>
         <v>376372.33</v>
       </c>
@@ -5869,22 +5930,22 @@
       </c>
       <c r="N38" s="77">
         <f t="shared" ref="N38:N69" si="14">P$2*G38%</f>
-        <v>294671.02810980001</v>
+        <v>309964.91422449</v>
       </c>
       <c r="O38" s="78">
         <v>0</v>
       </c>
       <c r="P38" s="79">
         <f t="shared" ref="P38:P69" si="15">ROUND(SUM(K38:O38),0) + S38</f>
-        <v>376372.33</v>
+        <v>391665.33</v>
       </c>
       <c r="Q38" s="80">
         <f t="shared" ref="Q38:Q69" si="16">ROUND(P38*6% + P38,0) + S38</f>
-        <v>398955.33</v>
+        <v>415165.33</v>
       </c>
       <c r="R38" s="81">
         <f t="shared" ref="R38:R69" si="17">ROUND(P38*3%,0) + P38</f>
-        <v>387663.33</v>
+        <v>403415.33</v>
       </c>
       <c r="S38" s="42">
         <f t="shared" si="8"/>
@@ -5915,7 +5976,7 @@
       <c r="H39" s="72">
         <v>423388.34</v>
       </c>
-      <c r="I39" s="247">
+      <c r="I39" s="73">
         <f t="shared" si="11"/>
         <v>423388.34</v>
       </c>
@@ -5934,22 +5995,22 @@
       </c>
       <c r="N39" s="77">
         <f t="shared" si="14"/>
-        <v>331481.23750740004</v>
+        <v>348685.63092237001</v>
       </c>
       <c r="O39" s="78">
         <v>0</v>
       </c>
       <c r="P39" s="79">
         <f t="shared" si="15"/>
-        <v>423388.34</v>
+        <v>440592.34</v>
       </c>
       <c r="Q39" s="80">
         <f t="shared" si="16"/>
-        <v>448792.34</v>
+        <v>467028.34</v>
       </c>
       <c r="R39" s="81">
         <f t="shared" si="17"/>
-        <v>436090.34</v>
+        <v>453810.34</v>
       </c>
       <c r="S39" s="42">
         <f t="shared" ref="S39:S75" si="19">S38+0.01</f>
@@ -5982,7 +6043,7 @@
       <c r="H40" s="72">
         <v>167235.35</v>
       </c>
-      <c r="I40" s="247">
+      <c r="I40" s="73">
         <f t="shared" si="11"/>
         <v>167235.35</v>
       </c>
@@ -6001,22 +6062,22 @@
       </c>
       <c r="N40" s="77">
         <f t="shared" si="14"/>
-        <v>127118.93300200001</v>
+        <v>133716.60396009998</v>
       </c>
       <c r="O40" s="78">
         <v>0</v>
       </c>
       <c r="P40" s="79">
         <f t="shared" si="15"/>
-        <v>162364.35</v>
+        <v>168962.35</v>
       </c>
       <c r="Q40" s="80">
         <f t="shared" si="16"/>
-        <v>172106.35</v>
+        <v>179100.35</v>
       </c>
       <c r="R40" s="81">
         <f t="shared" si="17"/>
-        <v>167235.35</v>
+        <v>174031.35</v>
       </c>
       <c r="S40" s="42">
         <f t="shared" si="19"/>
@@ -6049,7 +6110,7 @@
       <c r="H41" s="73">
         <v>133338.35999999999</v>
       </c>
-      <c r="I41" s="247">
+      <c r="I41" s="73">
         <f>H41</f>
         <v>133338.35999999999</v>
       </c>
@@ -6068,22 +6129,22 @@
       </c>
       <c r="N41" s="77">
         <f t="shared" si="14"/>
-        <v>98615.005423200011</v>
+        <v>103733.27806716</v>
       </c>
       <c r="O41" s="78">
         <v>0</v>
       </c>
       <c r="P41" s="79">
         <f t="shared" si="15"/>
-        <v>125957.36</v>
+        <v>131075.35999999999</v>
       </c>
       <c r="Q41" s="80">
         <f t="shared" si="16"/>
-        <v>133515.35999999999</v>
+        <v>138940.35999999999</v>
       </c>
       <c r="R41" s="81">
         <f t="shared" si="17"/>
-        <v>129736.36</v>
+        <v>135007.35999999999</v>
       </c>
       <c r="S41" s="42">
         <f t="shared" si="19"/>
@@ -6117,7 +6178,7 @@
       <c r="H42" s="72">
         <v>207430.37</v>
       </c>
-      <c r="I42" s="247">
+      <c r="I42" s="73">
         <f>H42</f>
         <v>207430.37</v>
       </c>
@@ -6136,22 +6197,22 @@
       </c>
       <c r="N42" s="77">
         <f t="shared" si="14"/>
-        <v>153413.74307580001</v>
+        <v>161376.15570279001</v>
       </c>
       <c r="O42" s="78">
         <v>0</v>
       </c>
       <c r="P42" s="79">
         <f t="shared" si="15"/>
-        <v>195949.37</v>
+        <v>203912.37</v>
       </c>
       <c r="Q42" s="80">
         <f t="shared" si="16"/>
-        <v>207706.37</v>
+        <v>216147.37</v>
       </c>
       <c r="R42" s="81">
         <f t="shared" si="17"/>
-        <v>201827.37</v>
+        <v>210029.37</v>
       </c>
       <c r="S42" s="42">
         <f t="shared" si="19"/>
@@ -6184,7 +6245,7 @@
       <c r="H43" s="72">
         <v>162985.38</v>
       </c>
-      <c r="I43" s="247">
+      <c r="I43" s="73">
         <f>H43</f>
         <v>162985.38</v>
       </c>
@@ -6203,22 +6264,22 @@
       </c>
       <c r="N43" s="77">
         <f t="shared" si="14"/>
-        <v>120542.07460140002</v>
+        <v>126798.39634707</v>
       </c>
       <c r="O43" s="78">
         <v>0</v>
       </c>
       <c r="P43" s="79">
         <f t="shared" si="15"/>
-        <v>153964.38</v>
+        <v>160220.38</v>
       </c>
       <c r="Q43" s="80">
         <f t="shared" si="16"/>
-        <v>163202.38</v>
+        <v>169834.38</v>
       </c>
       <c r="R43" s="81">
         <f t="shared" si="17"/>
-        <v>158583.38</v>
+        <v>165027.38</v>
       </c>
       <c r="S43" s="42">
         <f t="shared" si="19"/>
@@ -6262,22 +6323,22 @@
       </c>
       <c r="N44" s="77">
         <f t="shared" si="14"/>
-        <v>95332.887987200011</v>
+        <v>100280.81361535999</v>
       </c>
       <c r="O44" s="78">
         <v>0</v>
       </c>
       <c r="P44" s="79">
         <f t="shared" si="15"/>
-        <v>1068707.3899999999</v>
+        <v>1073655.3899999999</v>
       </c>
       <c r="Q44" s="80">
         <f t="shared" si="16"/>
-        <v>1132830.3899999999</v>
+        <v>1138075.3899999999</v>
       </c>
       <c r="R44" s="81">
         <f t="shared" si="17"/>
-        <v>1100768.3899999999</v>
+        <v>1105865.3899999999</v>
       </c>
       <c r="S44" s="42">
         <f t="shared" si="19"/>
@@ -6307,7 +6368,7 @@
       <c r="H45" s="72">
         <v>186146.4</v>
       </c>
-      <c r="I45" s="247">
+      <c r="I45" s="73">
         <f t="shared" ref="I45:I51" si="20">H45</f>
         <v>186146.4</v>
       </c>
@@ -6326,22 +6387,22 @@
       </c>
       <c r="N45" s="77">
         <f t="shared" si="14"/>
-        <v>145738.63768700004</v>
+        <v>153302.70036935003</v>
       </c>
       <c r="O45" s="78">
         <v>0</v>
       </c>
       <c r="P45" s="79">
         <f t="shared" si="15"/>
-        <v>186146.4</v>
+        <v>193710.4</v>
       </c>
       <c r="Q45" s="80">
         <f t="shared" si="16"/>
-        <v>197315.4</v>
+        <v>205333.4</v>
       </c>
       <c r="R45" s="81">
         <f t="shared" si="17"/>
-        <v>191730.4</v>
+        <v>199521.4</v>
       </c>
       <c r="S45" s="42">
         <f t="shared" si="19"/>
@@ -6371,7 +6432,7 @@
       <c r="H46" s="72">
         <v>153964.41</v>
       </c>
-      <c r="I46" s="247">
+      <c r="I46" s="73">
         <v>158583.41</v>
       </c>
       <c r="J46" s="74"/>
@@ -6389,22 +6450,22 @@
       </c>
       <c r="N46" s="77">
         <f t="shared" si="14"/>
-        <v>120542.07460140002</v>
+        <v>126798.39634707</v>
       </c>
       <c r="O46" s="78">
         <v>0</v>
       </c>
       <c r="P46" s="79">
         <f t="shared" si="15"/>
-        <v>149345.41</v>
+        <v>155601.41</v>
       </c>
       <c r="Q46" s="80">
         <f t="shared" si="16"/>
-        <v>158306.41</v>
+        <v>164937.41</v>
       </c>
       <c r="R46" s="81">
         <f t="shared" si="17"/>
-        <v>153825.41</v>
+        <v>160269.41</v>
       </c>
       <c r="S46" s="42">
         <f t="shared" si="19"/>
@@ -6432,7 +6493,7 @@
       <c r="H47" s="72">
         <v>121765.42</v>
       </c>
-      <c r="I47" s="247">
+      <c r="I47" s="73">
         <f t="shared" si="20"/>
         <v>121765.42</v>
       </c>
@@ -6451,22 +6512,22 @@
       </c>
       <c r="N47" s="77">
         <f t="shared" si="14"/>
-        <v>95332.887987200011</v>
+        <v>100280.81361535999</v>
       </c>
       <c r="O47" s="78">
         <v>0</v>
       </c>
       <c r="P47" s="79">
         <f t="shared" si="15"/>
-        <v>121765.42</v>
+        <v>126713.42</v>
       </c>
       <c r="Q47" s="80">
         <f t="shared" si="16"/>
-        <v>129071.42</v>
+        <v>134316.42000000001</v>
       </c>
       <c r="R47" s="81">
         <f t="shared" si="17"/>
-        <v>125418.42</v>
+        <v>130514.42</v>
       </c>
       <c r="S47" s="42">
         <f t="shared" si="19"/>
@@ -6494,7 +6555,7 @@
       <c r="H48" s="72">
         <v>186146.43</v>
       </c>
-      <c r="I48" s="247">
+      <c r="I48" s="73">
         <f t="shared" si="20"/>
         <v>186146.43</v>
       </c>
@@ -6513,22 +6574,22 @@
       </c>
       <c r="N48" s="77">
         <f t="shared" si="14"/>
-        <v>145738.63768700004</v>
+        <v>153302.70036935003</v>
       </c>
       <c r="O48" s="78">
         <v>0</v>
       </c>
       <c r="P48" s="79">
         <f t="shared" si="15"/>
-        <v>186146.43</v>
+        <v>193710.43</v>
       </c>
       <c r="Q48" s="80">
         <f t="shared" si="16"/>
-        <v>197315.43</v>
+        <v>205333.43</v>
       </c>
       <c r="R48" s="81">
         <f t="shared" si="17"/>
-        <v>191730.43</v>
+        <v>199521.43</v>
       </c>
       <c r="S48" s="42">
         <f t="shared" si="19"/>
@@ -6558,7 +6619,7 @@
       <c r="H49" s="72">
         <v>153964.44</v>
       </c>
-      <c r="I49" s="247">
+      <c r="I49" s="73">
         <f t="shared" si="20"/>
         <v>153964.44</v>
       </c>
@@ -6577,22 +6638,22 @@
       </c>
       <c r="N49" s="77">
         <f t="shared" si="14"/>
-        <v>120542.07460140002</v>
+        <v>126798.39634707</v>
       </c>
       <c r="O49" s="78">
         <v>0</v>
       </c>
       <c r="P49" s="79">
         <f t="shared" si="15"/>
-        <v>153964.44</v>
+        <v>160220.44</v>
       </c>
       <c r="Q49" s="80">
         <f t="shared" si="16"/>
-        <v>163202.44</v>
+        <v>169834.44</v>
       </c>
       <c r="R49" s="81">
         <f t="shared" si="17"/>
-        <v>158583.44</v>
+        <v>165027.44</v>
       </c>
       <c r="S49" s="42">
         <f t="shared" si="19"/>
@@ -6620,7 +6681,7 @@
       <c r="H50" s="72">
         <v>121765.45</v>
       </c>
-      <c r="I50" s="247">
+      <c r="I50" s="73">
         <f t="shared" si="20"/>
         <v>121765.45</v>
       </c>
@@ -6639,22 +6700,22 @@
       </c>
       <c r="N50" s="77">
         <f t="shared" si="14"/>
-        <v>95332.887987200011</v>
+        <v>100280.81361535999</v>
       </c>
       <c r="O50" s="78">
         <v>0</v>
       </c>
       <c r="P50" s="79">
         <f t="shared" si="15"/>
-        <v>121765.45</v>
+        <v>126713.45</v>
       </c>
       <c r="Q50" s="80">
         <f t="shared" si="16"/>
-        <v>129071.45</v>
+        <v>134316.45000000001</v>
       </c>
       <c r="R50" s="81">
         <f t="shared" si="17"/>
-        <v>125418.45</v>
+        <v>130514.45</v>
       </c>
       <c r="S50" s="42">
         <f t="shared" si="19"/>
@@ -6687,7 +6748,7 @@
       <c r="H51" s="72">
         <v>186146.46</v>
       </c>
-      <c r="I51" s="247">
+      <c r="I51" s="73">
         <f t="shared" si="20"/>
         <v>186146.46</v>
       </c>
@@ -6706,22 +6767,22 @@
       </c>
       <c r="N51" s="77">
         <f t="shared" si="14"/>
-        <v>145738.63768700004</v>
+        <v>153302.70036935003</v>
       </c>
       <c r="O51" s="78">
         <v>0</v>
       </c>
       <c r="P51" s="79">
         <f t="shared" si="15"/>
-        <v>186146.46</v>
+        <v>193710.46</v>
       </c>
       <c r="Q51" s="80">
         <f t="shared" si="16"/>
-        <v>197315.46</v>
+        <v>205333.46</v>
       </c>
       <c r="R51" s="81">
         <f t="shared" si="17"/>
-        <v>191730.46</v>
+        <v>199521.46</v>
       </c>
       <c r="S51" s="42">
         <f t="shared" si="19"/>
@@ -6751,7 +6812,7 @@
       <c r="H52" s="72">
         <v>158238.47</v>
       </c>
-      <c r="I52" s="247">
+      <c r="I52" s="73">
         <v>162945.47</v>
       </c>
       <c r="J52" s="74"/>
@@ -6769,22 +6830,22 @@
       </c>
       <c r="N52" s="77">
         <f t="shared" si="14"/>
-        <v>120542.07460140002</v>
+        <v>126798.39634707</v>
       </c>
       <c r="O52" s="78">
         <v>0</v>
       </c>
       <c r="P52" s="79">
         <f t="shared" si="15"/>
-        <v>149257.47</v>
+        <v>155513.47</v>
       </c>
       <c r="Q52" s="80">
         <f t="shared" si="16"/>
-        <v>158213.47</v>
+        <v>164844.47</v>
       </c>
       <c r="R52" s="81">
         <f t="shared" si="17"/>
-        <v>153735.47</v>
+        <v>160178.47</v>
       </c>
       <c r="S52" s="42">
         <f t="shared" si="19"/>
@@ -6814,7 +6875,7 @@
       <c r="H53" s="72">
         <v>121762.48</v>
       </c>
-      <c r="I53" s="247">
+      <c r="I53" s="73">
         <f>H53</f>
         <v>121762.48</v>
       </c>
@@ -6833,22 +6894,22 @@
       </c>
       <c r="N53" s="77">
         <f t="shared" si="14"/>
-        <v>95332.887987200011</v>
+        <v>100280.81361535999</v>
       </c>
       <c r="O53" s="78">
         <v>0</v>
       </c>
       <c r="P53" s="79">
         <f t="shared" si="15"/>
-        <v>121765.48</v>
+        <v>126713.48</v>
       </c>
       <c r="Q53" s="80">
         <f t="shared" si="16"/>
-        <v>129071.48</v>
+        <v>134316.48000000001</v>
       </c>
       <c r="R53" s="81">
         <f t="shared" si="17"/>
-        <v>125418.48</v>
+        <v>130514.48</v>
       </c>
       <c r="S53" s="42">
         <f t="shared" si="19"/>
@@ -6878,7 +6939,7 @@
       <c r="H54" s="72">
         <v>186146.49</v>
       </c>
-      <c r="I54" s="247">
+      <c r="I54" s="73">
         <f t="shared" ref="I54:I59" si="21">H54</f>
         <v>186146.49</v>
       </c>
@@ -6897,22 +6958,22 @@
       </c>
       <c r="N54" s="77">
         <f t="shared" si="14"/>
-        <v>145738.63768700004</v>
+        <v>153302.70036935003</v>
       </c>
       <c r="O54" s="78">
         <v>0</v>
       </c>
       <c r="P54" s="79">
         <f t="shared" si="15"/>
-        <v>186146.49</v>
+        <v>193710.49</v>
       </c>
       <c r="Q54" s="80">
         <f t="shared" si="16"/>
-        <v>197315.49</v>
+        <v>205333.49</v>
       </c>
       <c r="R54" s="81">
         <f t="shared" si="17"/>
-        <v>191730.49</v>
+        <v>199521.49</v>
       </c>
       <c r="S54" s="42">
         <f t="shared" si="19"/>
@@ -6940,7 +7001,7 @@
       <c r="H55" s="72">
         <v>153964.5</v>
       </c>
-      <c r="I55" s="247">
+      <c r="I55" s="73">
         <f>H55</f>
         <v>153964.5</v>
       </c>
@@ -6959,22 +7020,22 @@
       </c>
       <c r="N55" s="77">
         <f t="shared" si="14"/>
-        <v>120542.07460140002</v>
+        <v>126798.39634707</v>
       </c>
       <c r="O55" s="78">
         <v>0</v>
       </c>
       <c r="P55" s="79">
         <f t="shared" si="15"/>
-        <v>153964.5</v>
+        <v>160220.5</v>
       </c>
       <c r="Q55" s="80">
         <f t="shared" si="16"/>
-        <v>163202.5</v>
+        <v>169834.5</v>
       </c>
       <c r="R55" s="81">
         <f t="shared" si="17"/>
-        <v>158583.5</v>
+        <v>165027.5</v>
       </c>
       <c r="S55" s="42">
         <f t="shared" si="19"/>
@@ -7002,7 +7063,7 @@
       <c r="H56" s="72">
         <v>125418.45</v>
       </c>
-      <c r="I56" s="247">
+      <c r="I56" s="73">
         <v>124933</v>
       </c>
       <c r="J56" s="74"/>
@@ -7020,22 +7081,22 @@
       </c>
       <c r="N56" s="77">
         <f t="shared" si="14"/>
-        <v>95332.887987200011</v>
+        <v>100280.81361535999</v>
       </c>
       <c r="O56" s="78">
         <v>0</v>
       </c>
       <c r="P56" s="79">
         <f t="shared" si="15"/>
-        <v>122265.51</v>
+        <v>127213.51</v>
       </c>
       <c r="Q56" s="80">
         <f t="shared" si="16"/>
-        <v>129601.51</v>
+        <v>134846.51</v>
       </c>
       <c r="R56" s="81">
         <f t="shared" si="17"/>
-        <v>125933.51</v>
+        <v>131029.51</v>
       </c>
       <c r="S56" s="42">
         <f t="shared" si="19"/>
@@ -7066,7 +7127,7 @@
       <c r="H57" s="72">
         <v>69879.520000000004</v>
       </c>
-      <c r="I57" s="247">
+      <c r="I57" s="73">
         <f>H57</f>
         <v>69879.520000000004</v>
       </c>
@@ -7085,22 +7146,22 @@
       </c>
       <c r="N57" s="77">
         <f t="shared" si="14"/>
-        <v>145738.63768700004</v>
+        <v>153302.70036935003</v>
       </c>
       <c r="O57" s="78">
         <v>0</v>
       </c>
       <c r="P57" s="79">
         <f t="shared" si="15"/>
-        <v>186146.52</v>
+        <v>193710.52</v>
       </c>
       <c r="Q57" s="80">
         <f t="shared" si="16"/>
-        <v>197315.52</v>
+        <v>205333.52</v>
       </c>
       <c r="R57" s="81">
         <f t="shared" si="17"/>
-        <v>191730.52</v>
+        <v>199521.52</v>
       </c>
       <c r="S57" s="42">
         <f t="shared" si="19"/>
@@ -7128,7 +7189,7 @@
       <c r="H58" s="72">
         <v>153964.53</v>
       </c>
-      <c r="I58" s="247">
+      <c r="I58" s="73">
         <f t="shared" si="21"/>
         <v>153964.53</v>
       </c>
@@ -7147,22 +7208,22 @@
       </c>
       <c r="N58" s="77">
         <f t="shared" si="14"/>
-        <v>120542.07460140002</v>
+        <v>126798.39634707</v>
       </c>
       <c r="O58" s="78">
         <v>0</v>
       </c>
       <c r="P58" s="79">
         <f t="shared" si="15"/>
-        <v>153964.53</v>
+        <v>160220.53</v>
       </c>
       <c r="Q58" s="80">
         <f t="shared" si="16"/>
-        <v>163202.53</v>
+        <v>169834.53</v>
       </c>
       <c r="R58" s="81">
         <f t="shared" si="17"/>
-        <v>158583.53</v>
+        <v>165027.53</v>
       </c>
       <c r="S58" s="42">
         <f t="shared" si="19"/>
@@ -7190,7 +7251,7 @@
       <c r="H59" s="72">
         <v>121765.54</v>
       </c>
-      <c r="I59" s="247">
+      <c r="I59" s="73">
         <f t="shared" si="21"/>
         <v>121765.54</v>
       </c>
@@ -7209,22 +7270,22 @@
       </c>
       <c r="N59" s="77">
         <f t="shared" si="14"/>
-        <v>95332.887987200011</v>
+        <v>100280.81361535999</v>
       </c>
       <c r="O59" s="78">
         <v>0</v>
       </c>
       <c r="P59" s="79">
         <f t="shared" si="15"/>
-        <v>121765.54</v>
+        <v>126713.54</v>
       </c>
       <c r="Q59" s="80">
         <f t="shared" si="16"/>
-        <v>129071.54</v>
+        <v>134316.54</v>
       </c>
       <c r="R59" s="81">
         <f t="shared" si="17"/>
-        <v>125418.54</v>
+        <v>130514.54</v>
       </c>
       <c r="S59" s="42">
         <f t="shared" si="19"/>
@@ -7243,7 +7304,7 @@
         <v>55</v>
       </c>
       <c r="E60" s="63" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F60" s="63"/>
       <c r="G60" s="85">
@@ -7268,22 +7329,22 @@
       </c>
       <c r="N60" s="77">
         <f t="shared" si="14"/>
-        <v>145738.63768700004</v>
+        <v>153302.70036935003</v>
       </c>
       <c r="O60" s="78">
         <v>0</v>
       </c>
       <c r="P60" s="79">
         <f t="shared" si="15"/>
-        <v>1034981.55</v>
+        <v>1042545.55</v>
       </c>
       <c r="Q60" s="80">
         <f t="shared" si="16"/>
-        <v>1097080.55</v>
+        <v>1105098.55</v>
       </c>
       <c r="R60" s="81">
         <f t="shared" si="17"/>
-        <v>1066030.55</v>
+        <v>1073821.55</v>
       </c>
       <c r="S60" s="42">
         <f t="shared" si="19"/>
@@ -7313,7 +7374,7 @@
       <c r="H61" s="72">
         <v>174707.56</v>
       </c>
-      <c r="I61" s="247">
+      <c r="I61" s="73">
         <f>H61</f>
         <v>174707.56</v>
       </c>
@@ -7332,20 +7393,20 @@
       </c>
       <c r="N61" s="77">
         <f t="shared" si="14"/>
-        <v>120542.07460140002</v>
+        <v>126798.39634707</v>
       </c>
       <c r="O61" s="78"/>
       <c r="P61" s="79">
         <f t="shared" si="15"/>
-        <v>153964.56</v>
+        <v>160220.56</v>
       </c>
       <c r="Q61" s="80">
         <f t="shared" si="16"/>
-        <v>163202.56</v>
+        <v>169834.56</v>
       </c>
       <c r="R61" s="81">
         <f t="shared" si="17"/>
-        <v>158583.56</v>
+        <v>165027.56</v>
       </c>
       <c r="S61" s="42">
         <f t="shared" si="19"/>
@@ -7375,7 +7436,7 @@
       <c r="H62" s="72">
         <v>121765.57</v>
       </c>
-      <c r="I62" s="247">
+      <c r="I62" s="73">
         <v>103329.57</v>
       </c>
       <c r="J62" s="74"/>
@@ -7393,22 +7454,22 @@
       </c>
       <c r="N62" s="77">
         <f t="shared" si="14"/>
-        <v>95332.887987200011</v>
+        <v>100280.81361535999</v>
       </c>
       <c r="O62" s="78">
         <v>0</v>
       </c>
       <c r="P62" s="79">
         <f t="shared" si="15"/>
-        <v>140754.57</v>
+        <v>145702.57</v>
       </c>
       <c r="Q62" s="80">
         <f t="shared" si="16"/>
-        <v>149200.57</v>
+        <v>154445.57</v>
       </c>
       <c r="R62" s="81">
         <f t="shared" si="17"/>
-        <v>144977.57</v>
+        <v>150073.57</v>
       </c>
       <c r="S62" s="42">
         <f t="shared" si="19"/>
@@ -7436,7 +7497,7 @@
       <c r="H63" s="72">
         <v>191314.58</v>
       </c>
-      <c r="I63" s="247">
+      <c r="I63" s="73">
         <f>H63</f>
         <v>191314.58</v>
       </c>
@@ -7455,22 +7516,22 @@
       </c>
       <c r="N63" s="77">
         <f t="shared" si="14"/>
-        <v>145738.63768700004</v>
+        <v>153302.70036935003</v>
       </c>
       <c r="O63" s="78">
         <v>0</v>
       </c>
       <c r="P63" s="79">
         <f t="shared" si="15"/>
-        <v>186146.58</v>
+        <v>193710.58</v>
       </c>
       <c r="Q63" s="80">
         <f t="shared" si="16"/>
-        <v>197315.58</v>
+        <v>205333.58</v>
       </c>
       <c r="R63" s="81">
         <f t="shared" si="17"/>
-        <v>191730.58</v>
+        <v>199521.58</v>
       </c>
       <c r="S63" s="42">
         <f t="shared" si="19"/>
@@ -7498,7 +7559,7 @@
       <c r="H64" s="72">
         <v>20475.59</v>
       </c>
-      <c r="I64" s="247">
+      <c r="I64" s="73">
         <f>H64*2</f>
         <v>40951.18</v>
       </c>
@@ -7517,22 +7578,22 @@
       </c>
       <c r="N64" s="77">
         <f t="shared" si="14"/>
-        <v>120542.07460140002</v>
+        <v>126798.39634707</v>
       </c>
       <c r="O64" s="78">
         <v>0</v>
       </c>
       <c r="P64" s="79">
         <f t="shared" si="15"/>
-        <v>133488.59</v>
+        <v>139744.59</v>
       </c>
       <c r="Q64" s="80">
         <f t="shared" si="16"/>
-        <v>141498.59</v>
+        <v>148129.59</v>
       </c>
       <c r="R64" s="81">
         <f t="shared" si="17"/>
-        <v>137493.59</v>
+        <v>143936.59</v>
       </c>
       <c r="S64" s="42">
         <f t="shared" si="19"/>
@@ -7560,7 +7621,7 @@
       <c r="H65" s="72">
         <v>121765.6</v>
       </c>
-      <c r="I65" s="247">
+      <c r="I65" s="73">
         <f t="shared" ref="I65:I70" si="22">H65</f>
         <v>121765.6</v>
       </c>
@@ -7579,22 +7640,22 @@
       </c>
       <c r="N65" s="77">
         <f t="shared" si="14"/>
-        <v>95332.887987200011</v>
+        <v>100280.81361535999</v>
       </c>
       <c r="O65" s="78">
         <v>0</v>
       </c>
       <c r="P65" s="79">
         <f t="shared" si="15"/>
-        <v>121765.6</v>
+        <v>126713.60000000001</v>
       </c>
       <c r="Q65" s="80">
         <f t="shared" si="16"/>
-        <v>129072.6</v>
+        <v>134316.6</v>
       </c>
       <c r="R65" s="81">
         <f t="shared" si="17"/>
-        <v>125418.6</v>
+        <v>130514.6</v>
       </c>
       <c r="S65" s="42">
         <f t="shared" si="19"/>
@@ -7625,7 +7686,7 @@
       <c r="H66" s="72">
         <v>186146.61</v>
       </c>
-      <c r="I66" s="247">
+      <c r="I66" s="73">
         <f t="shared" si="22"/>
         <v>186146.61</v>
       </c>
@@ -7644,22 +7705,22 @@
       </c>
       <c r="N66" s="77">
         <f t="shared" si="14"/>
-        <v>145738.63768700004</v>
+        <v>153302.70036935003</v>
       </c>
       <c r="O66" s="78">
         <v>0</v>
       </c>
       <c r="P66" s="79">
         <f t="shared" si="15"/>
-        <v>186146.61</v>
+        <v>193710.61</v>
       </c>
       <c r="Q66" s="80">
         <f t="shared" si="16"/>
-        <v>197315.61</v>
+        <v>205333.61</v>
       </c>
       <c r="R66" s="81">
         <f t="shared" si="17"/>
-        <v>191730.61</v>
+        <v>199521.61</v>
       </c>
       <c r="S66" s="42">
         <f t="shared" si="19"/>
@@ -7692,7 +7753,7 @@
       <c r="H67" s="72">
         <v>153964.62</v>
       </c>
-      <c r="I67" s="247">
+      <c r="I67" s="73">
         <f t="shared" si="22"/>
         <v>153964.62</v>
       </c>
@@ -7711,22 +7772,22 @@
       </c>
       <c r="N67" s="77">
         <f t="shared" si="14"/>
-        <v>120542.07460140002</v>
+        <v>126798.39634707</v>
       </c>
       <c r="O67" s="78">
         <v>0</v>
       </c>
       <c r="P67" s="79">
         <f t="shared" si="15"/>
-        <v>153964.62</v>
+        <v>160220.62</v>
       </c>
       <c r="Q67" s="80">
         <f t="shared" si="16"/>
-        <v>163202.62</v>
+        <v>169834.62</v>
       </c>
       <c r="R67" s="81">
         <f t="shared" si="17"/>
-        <v>158583.62</v>
+        <v>165027.62</v>
       </c>
       <c r="S67" s="42">
         <f t="shared" si="19"/>
@@ -7759,7 +7820,7 @@
       <c r="H68" s="72">
         <v>121765.63</v>
       </c>
-      <c r="I68" s="247">
+      <c r="I68" s="73">
         <f t="shared" si="22"/>
         <v>121765.63</v>
       </c>
@@ -7778,22 +7839,22 @@
       </c>
       <c r="N68" s="77">
         <f t="shared" si="14"/>
-        <v>95332.887987200011</v>
+        <v>100280.81361535999</v>
       </c>
       <c r="O68" s="78">
         <v>0</v>
       </c>
       <c r="P68" s="79">
         <f t="shared" si="15"/>
-        <v>121765.63</v>
+        <v>126713.63</v>
       </c>
       <c r="Q68" s="80">
         <f t="shared" si="16"/>
-        <v>129072.63</v>
+        <v>134316.63</v>
       </c>
       <c r="R68" s="81">
         <f t="shared" si="17"/>
-        <v>125418.63</v>
+        <v>130514.63</v>
       </c>
       <c r="S68" s="42">
         <f t="shared" si="19"/>
@@ -7821,7 +7882,7 @@
       <c r="H69" s="72">
         <v>186146.64</v>
       </c>
-      <c r="I69" s="247">
+      <c r="I69" s="73">
         <f t="shared" si="22"/>
         <v>186146.64</v>
       </c>
@@ -7840,22 +7901,22 @@
       </c>
       <c r="N69" s="77">
         <f t="shared" si="14"/>
-        <v>145738.63768700004</v>
+        <v>153302.70036935003</v>
       </c>
       <c r="O69" s="78">
         <v>0</v>
       </c>
       <c r="P69" s="79">
         <f t="shared" si="15"/>
-        <v>186146.64</v>
+        <v>193710.64</v>
       </c>
       <c r="Q69" s="80">
         <f t="shared" si="16"/>
-        <v>197315.64</v>
+        <v>205333.64</v>
       </c>
       <c r="R69" s="81">
         <f t="shared" si="17"/>
-        <v>191730.64</v>
+        <v>199521.64</v>
       </c>
       <c r="S69" s="42">
         <f t="shared" si="19"/>
@@ -7883,7 +7944,7 @@
       <c r="H70" s="72">
         <v>153964.65</v>
       </c>
-      <c r="I70" s="247">
+      <c r="I70" s="73">
         <f t="shared" si="22"/>
         <v>153964.65</v>
       </c>
@@ -7902,22 +7963,22 @@
       </c>
       <c r="N70" s="77">
         <f t="shared" ref="N70:N75" si="25">P$2*G70%</f>
-        <v>120542.07460140002</v>
+        <v>126798.39634707</v>
       </c>
       <c r="O70" s="78">
         <v>0</v>
       </c>
       <c r="P70" s="79">
         <f t="shared" ref="P70:P75" si="26">ROUND(SUM(K70:O70),0) + S70</f>
-        <v>153964.65</v>
+        <v>160220.65</v>
       </c>
       <c r="Q70" s="80">
         <f t="shared" ref="Q70:Q75" si="27">ROUND(P70*6% + P70,0) + S70</f>
-        <v>163203.65</v>
+        <v>169834.65</v>
       </c>
       <c r="R70" s="81">
         <f t="shared" ref="R70:R75" si="28">ROUND(P70*3%,0) + P70</f>
-        <v>158583.65</v>
+        <v>165027.65</v>
       </c>
       <c r="S70" s="42">
         <f t="shared" si="19"/>
@@ -7947,7 +8008,7 @@
       <c r="H71" s="72">
         <v>432928.66</v>
       </c>
-      <c r="I71" s="247">
+      <c r="I71" s="73">
         <f>240226+192702.66</f>
         <v>432928.66000000003</v>
       </c>
@@ -7966,22 +8027,22 @@
       </c>
       <c r="N71" s="77">
         <f t="shared" si="25"/>
-        <v>95332.887987200011</v>
+        <v>100280.81361535999</v>
       </c>
       <c r="O71" s="78">
         <v>0</v>
       </c>
       <c r="P71" s="79">
         <f t="shared" si="26"/>
-        <v>121765.66</v>
+        <v>126713.66</v>
       </c>
       <c r="Q71" s="80">
         <f t="shared" si="27"/>
-        <v>129072.66</v>
+        <v>134316.66</v>
       </c>
       <c r="R71" s="81">
         <f t="shared" si="28"/>
-        <v>125418.66</v>
+        <v>130514.66</v>
       </c>
       <c r="S71" s="42">
         <f t="shared" si="19"/>
@@ -8009,7 +8070,7 @@
       <c r="H72" s="72">
         <v>186146.67</v>
       </c>
-      <c r="I72" s="247">
+      <c r="I72" s="73">
         <f>H72</f>
         <v>186146.67</v>
       </c>
@@ -8028,22 +8089,22 @@
       </c>
       <c r="N72" s="77">
         <f t="shared" si="25"/>
-        <v>145738.63768700004</v>
+        <v>153302.70036935003</v>
       </c>
       <c r="O72" s="78">
         <v>0</v>
       </c>
       <c r="P72" s="79">
         <f t="shared" si="26"/>
-        <v>186146.67</v>
+        <v>193710.67</v>
       </c>
       <c r="Q72" s="80">
         <f t="shared" si="27"/>
-        <v>197315.67</v>
+        <v>205333.67</v>
       </c>
       <c r="R72" s="81">
         <f t="shared" si="28"/>
-        <v>191730.67</v>
+        <v>199521.67</v>
       </c>
       <c r="S72" s="42">
         <f t="shared" si="19"/>
@@ -8071,7 +8132,7 @@
       <c r="H73" s="90">
         <v>153964.68</v>
       </c>
-      <c r="I73" s="247">
+      <c r="I73" s="73">
         <f>H73</f>
         <v>153964.68</v>
       </c>
@@ -8090,22 +8151,22 @@
       </c>
       <c r="N73" s="94">
         <f t="shared" si="25"/>
-        <v>120542.07460140002</v>
+        <v>126798.39634707</v>
       </c>
       <c r="O73" s="95">
         <v>0</v>
       </c>
       <c r="P73" s="79">
         <f t="shared" si="26"/>
-        <v>153964.68</v>
+        <v>160220.68</v>
       </c>
       <c r="Q73" s="80">
         <f t="shared" si="27"/>
-        <v>163203.68</v>
+        <v>169834.68</v>
       </c>
       <c r="R73" s="81">
         <f t="shared" si="28"/>
-        <v>158583.67999999999</v>
+        <v>165027.68</v>
       </c>
       <c r="S73" s="42">
         <f t="shared" si="19"/>
@@ -8133,7 +8194,7 @@
       <c r="H74" s="90">
         <v>121765.69</v>
       </c>
-      <c r="I74" s="247">
+      <c r="I74" s="73">
         <f>H74</f>
         <v>121765.69</v>
       </c>
@@ -8152,22 +8213,22 @@
       </c>
       <c r="N74" s="94">
         <f t="shared" si="25"/>
-        <v>95332.887987200011</v>
+        <v>100280.81361535999</v>
       </c>
       <c r="O74" s="95">
         <v>0</v>
       </c>
       <c r="P74" s="79">
         <f t="shared" si="26"/>
-        <v>121765.69</v>
+        <v>126713.69</v>
       </c>
       <c r="Q74" s="80">
         <f t="shared" si="27"/>
-        <v>129072.69</v>
+        <v>134317.69</v>
       </c>
       <c r="R74" s="81">
         <f t="shared" si="28"/>
-        <v>125418.69</v>
+        <v>130514.69</v>
       </c>
       <c r="S74" s="42">
         <f t="shared" si="19"/>
@@ -8195,7 +8256,7 @@
       <c r="H75" s="90">
         <v>186211.7</v>
       </c>
-      <c r="I75" s="247">
+      <c r="I75" s="73">
         <f>H75</f>
         <v>186211.7</v>
       </c>
@@ -8214,22 +8275,22 @@
       </c>
       <c r="N75" s="94">
         <f t="shared" si="25"/>
-        <v>145789.13180140001</v>
+        <v>153355.81520707</v>
       </c>
       <c r="O75" s="95">
         <v>0</v>
       </c>
       <c r="P75" s="79">
         <f t="shared" si="26"/>
-        <v>186211.7</v>
+        <v>193777.7</v>
       </c>
       <c r="Q75" s="80">
         <f t="shared" si="27"/>
-        <v>197384.7</v>
+        <v>205404.7</v>
       </c>
       <c r="R75" s="81">
         <f t="shared" si="28"/>
-        <v>191797.7</v>
+        <v>199590.7</v>
       </c>
       <c r="S75" s="42">
         <f t="shared" si="19"/>
@@ -8352,7 +8413,7 @@
       </c>
       <c r="I81" s="61">
         <f>SUM(I6:I80)</f>
-        <v>14136349.759999996</v>
+        <v>14326349.759999996</v>
       </c>
       <c r="J81" s="52">
         <f>SUM(J6:J80)</f>
@@ -8360,7 +8421,7 @@
       </c>
       <c r="K81" s="61">
         <f>SUM(K6:K80)</f>
-        <v>8323442.0299999993</v>
+        <v>8133442.0299999993</v>
       </c>
       <c r="L81" s="61"/>
       <c r="M81" s="61">
@@ -8369,7 +8430,7 @@
       </c>
       <c r="N81" s="61">
         <f>SUM(N6:N80)</f>
-        <v>12623528.600000003</v>
+        <v>13278709.430000003</v>
       </c>
       <c r="O81" s="61">
         <f>SUM(O6:O80)</f>
@@ -8377,11 +8438,11 @@
       </c>
       <c r="P81" s="106">
         <f>SUM(P6:P80)</f>
-        <v>24716492.850000001</v>
+        <v>25175972.850000001</v>
       </c>
       <c r="Q81" s="106">
         <f>SUM(Q6:Q80)</f>
-        <v>26199503.850000001</v>
+        <v>26686550.850000001</v>
       </c>
       <c r="R81" s="106"/>
     </row>
@@ -8391,91 +8452,91 @@
     </row>
     <row r="83" spans="2:18" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="84" spans="2:18" ht="9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E84" s="217" t="str">
+      <c r="E84" s="225" t="str">
         <f>RESUMEN!A14</f>
         <v>ESTIMADOS PROPIETARIOS E INQUILINOS: POR FAVOR LOS QUE ABONAN EN PRIMER VENCIMIENTO ABONEN EL MONTO DE PRIMER VENCIMIENTO, ASI AGILIZAN LA LIQUIDACION, RESPETEN LOS CENTAVOS CORRESPONDIENTES A LA UNIDAD FUNCIONAL. ES DE CARÁCTER OBLIGATORIO INFORMAR VIA MAIL LAS EXPENSAS. CASO CONTRARIO SE INFORMARA VIA CARTA DOCUMENTO A LA UNIDAD FUNCIONAL QUE CREEMOS QUE CORRESPONDE, CUYO COSTO SERA IMPUTADO A LA UNIDAD FUNCIONAL SOSPECHADA.</v>
       </c>
-      <c r="F84" s="210"/>
-      <c r="G84" s="210"/>
-      <c r="H84" s="210"/>
-      <c r="I84" s="210"/>
-      <c r="J84" s="210"/>
-      <c r="K84" s="210"/>
-      <c r="L84" s="210"/>
-      <c r="M84" s="210"/>
-      <c r="N84" s="210"/>
-      <c r="O84" s="210"/>
-      <c r="P84" s="210"/>
+      <c r="F84" s="218"/>
+      <c r="G84" s="218"/>
+      <c r="H84" s="218"/>
+      <c r="I84" s="218"/>
+      <c r="J84" s="218"/>
+      <c r="K84" s="218"/>
+      <c r="L84" s="218"/>
+      <c r="M84" s="218"/>
+      <c r="N84" s="218"/>
+      <c r="O84" s="218"/>
+      <c r="P84" s="218"/>
     </row>
     <row r="85" spans="2:18" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E85" s="210"/>
-      <c r="F85" s="210"/>
-      <c r="G85" s="210"/>
-      <c r="H85" s="210"/>
-      <c r="I85" s="210"/>
-      <c r="J85" s="210"/>
-      <c r="K85" s="210"/>
-      <c r="L85" s="210"/>
-      <c r="M85" s="210"/>
-      <c r="N85" s="210"/>
-      <c r="O85" s="210"/>
-      <c r="P85" s="210"/>
+      <c r="E85" s="218"/>
+      <c r="F85" s="218"/>
+      <c r="G85" s="218"/>
+      <c r="H85" s="218"/>
+      <c r="I85" s="218"/>
+      <c r="J85" s="218"/>
+      <c r="K85" s="218"/>
+      <c r="L85" s="218"/>
+      <c r="M85" s="218"/>
+      <c r="N85" s="218"/>
+      <c r="O85" s="218"/>
+      <c r="P85" s="218"/>
     </row>
     <row r="86" spans="2:18" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E86" s="210"/>
-      <c r="F86" s="210"/>
-      <c r="G86" s="210"/>
-      <c r="H86" s="210"/>
-      <c r="I86" s="210"/>
-      <c r="J86" s="210"/>
-      <c r="K86" s="210"/>
-      <c r="L86" s="210"/>
-      <c r="M86" s="210"/>
-      <c r="N86" s="210"/>
-      <c r="O86" s="210"/>
-      <c r="P86" s="210"/>
+      <c r="E86" s="218"/>
+      <c r="F86" s="218"/>
+      <c r="G86" s="218"/>
+      <c r="H86" s="218"/>
+      <c r="I86" s="218"/>
+      <c r="J86" s="218"/>
+      <c r="K86" s="218"/>
+      <c r="L86" s="218"/>
+      <c r="M86" s="218"/>
+      <c r="N86" s="218"/>
+      <c r="O86" s="218"/>
+      <c r="P86" s="218"/>
     </row>
     <row r="87" spans="2:18" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E87" s="210"/>
-      <c r="F87" s="210"/>
-      <c r="G87" s="210"/>
-      <c r="H87" s="210"/>
-      <c r="I87" s="210"/>
-      <c r="J87" s="210"/>
-      <c r="K87" s="210"/>
-      <c r="L87" s="210"/>
-      <c r="M87" s="210"/>
-      <c r="N87" s="210"/>
-      <c r="O87" s="210"/>
-      <c r="P87" s="210"/>
+      <c r="E87" s="218"/>
+      <c r="F87" s="218"/>
+      <c r="G87" s="218"/>
+      <c r="H87" s="218"/>
+      <c r="I87" s="218"/>
+      <c r="J87" s="218"/>
+      <c r="K87" s="218"/>
+      <c r="L87" s="218"/>
+      <c r="M87" s="218"/>
+      <c r="N87" s="218"/>
+      <c r="O87" s="218"/>
+      <c r="P87" s="218"/>
     </row>
     <row r="88" spans="2:18" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E88" s="210"/>
-      <c r="F88" s="210"/>
-      <c r="G88" s="210"/>
-      <c r="H88" s="210"/>
-      <c r="I88" s="210"/>
-      <c r="J88" s="210"/>
-      <c r="K88" s="210"/>
-      <c r="L88" s="210"/>
-      <c r="M88" s="210"/>
-      <c r="N88" s="210"/>
-      <c r="O88" s="210"/>
-      <c r="P88" s="210"/>
+      <c r="E88" s="218"/>
+      <c r="F88" s="218"/>
+      <c r="G88" s="218"/>
+      <c r="H88" s="218"/>
+      <c r="I88" s="218"/>
+      <c r="J88" s="218"/>
+      <c r="K88" s="218"/>
+      <c r="L88" s="218"/>
+      <c r="M88" s="218"/>
+      <c r="N88" s="218"/>
+      <c r="O88" s="218"/>
+      <c r="P88" s="218"/>
     </row>
     <row r="89" spans="2:18" ht="67.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E89" s="210"/>
-      <c r="F89" s="210"/>
-      <c r="G89" s="210"/>
-      <c r="H89" s="210"/>
-      <c r="I89" s="210"/>
-      <c r="J89" s="210"/>
-      <c r="K89" s="210"/>
-      <c r="L89" s="210"/>
-      <c r="M89" s="210"/>
-      <c r="N89" s="210"/>
-      <c r="O89" s="210"/>
-      <c r="P89" s="210"/>
+      <c r="E89" s="218"/>
+      <c r="F89" s="218"/>
+      <c r="G89" s="218"/>
+      <c r="H89" s="218"/>
+      <c r="I89" s="218"/>
+      <c r="J89" s="218"/>
+      <c r="K89" s="218"/>
+      <c r="L89" s="218"/>
+      <c r="M89" s="218"/>
+      <c r="N89" s="218"/>
+      <c r="O89" s="218"/>
+      <c r="P89" s="218"/>
     </row>
   </sheetData>
   <mergeCells count="20">
@@ -8553,16 +8614,16 @@
       <c r="D1" s="6"/>
       <c r="E1" s="6"/>
       <c r="F1" s="6"/>
-      <c r="G1" s="228"/>
-      <c r="H1" s="210"/>
-      <c r="I1" s="210"/>
-      <c r="J1" s="210"/>
-      <c r="K1" s="210"/>
-      <c r="L1" s="210"/>
-      <c r="M1" s="210"/>
-      <c r="N1" s="210"/>
-      <c r="O1" s="210"/>
-      <c r="P1" s="210"/>
+      <c r="G1" s="236"/>
+      <c r="H1" s="218"/>
+      <c r="I1" s="218"/>
+      <c r="J1" s="218"/>
+      <c r="K1" s="218"/>
+      <c r="L1" s="218"/>
+      <c r="M1" s="218"/>
+      <c r="N1" s="218"/>
+      <c r="O1" s="218"/>
+      <c r="P1" s="218"/>
       <c r="Q1" s="6"/>
       <c r="R1" s="6"/>
     </row>
@@ -8572,7 +8633,7 @@
       <c r="C2" s="6"/>
       <c r="D2" s="6"/>
       <c r="E2" s="6" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="F2" s="6"/>
       <c r="G2" s="6"/>
@@ -8581,17 +8642,17 @@
       <c r="J2" s="6"/>
       <c r="K2" s="6"/>
       <c r="L2" s="6" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="M2" s="7"/>
       <c r="N2" s="6"/>
       <c r="O2" s="6"/>
-      <c r="P2" s="224">
+      <c r="P2" s="232">
         <f>16770000+7700000</f>
         <v>24470000</v>
       </c>
-      <c r="Q2" s="210"/>
-      <c r="R2" s="210"/>
+      <c r="Q2" s="218"/>
+      <c r="R2" s="218"/>
       <c r="S2" s="20"/>
     </row>
     <row r="3" spans="1:21" ht="12.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -8615,77 +8676,77 @@
       <c r="R3" s="59"/>
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A4" s="235" t="s">
+      <c r="A4" s="243" t="s">
         <v>64</v>
       </c>
-      <c r="B4" s="237" t="s">
+      <c r="B4" s="245" t="s">
         <v>65</v>
       </c>
       <c r="C4" s="132"/>
-      <c r="D4" s="225" t="s">
+      <c r="D4" s="233" t="s">
         <v>66</v>
       </c>
-      <c r="E4" s="225" t="s">
+      <c r="E4" s="233" t="s">
         <v>67</v>
       </c>
-      <c r="F4" s="234" t="s">
+      <c r="F4" s="242" t="s">
         <v>68</v>
       </c>
-      <c r="G4" s="225" t="s">
+      <c r="G4" s="233" t="s">
         <v>69</v>
       </c>
-      <c r="H4" s="232" t="s">
+      <c r="H4" s="240" t="s">
         <v>70</v>
       </c>
-      <c r="I4" s="225" t="s">
+      <c r="I4" s="233" t="s">
         <v>50</v>
       </c>
-      <c r="J4" s="234" t="s">
+      <c r="J4" s="242" t="s">
         <v>71</v>
       </c>
-      <c r="K4" s="236" t="s">
+      <c r="K4" s="244" t="s">
         <v>72</v>
       </c>
-      <c r="L4" s="232" t="s">
+      <c r="L4" s="240" t="s">
         <v>73</v>
       </c>
-      <c r="M4" s="231" t="s">
+      <c r="M4" s="239" t="s">
         <v>74</v>
       </c>
-      <c r="N4" s="232" t="s">
-        <v>209</v>
-      </c>
-      <c r="O4" s="226"/>
-      <c r="P4" s="222" t="s">
+      <c r="N4" s="240" t="s">
+        <v>208</v>
+      </c>
+      <c r="O4" s="234"/>
+      <c r="P4" s="230" t="s">
         <v>77</v>
       </c>
-      <c r="Q4" s="229" t="s">
+      <c r="Q4" s="237" t="s">
         <v>78</v>
       </c>
-      <c r="R4" s="222" t="s">
+      <c r="R4" s="230" t="s">
         <v>79</v>
       </c>
       <c r="U4" s="42"/>
     </row>
     <row r="5" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="223"/>
-      <c r="B5" s="230"/>
+      <c r="A5" s="231"/>
+      <c r="B5" s="238"/>
       <c r="C5" s="133"/>
-      <c r="D5" s="223"/>
-      <c r="E5" s="223"/>
-      <c r="F5" s="233"/>
-      <c r="G5" s="223"/>
-      <c r="H5" s="233"/>
-      <c r="I5" s="223"/>
-      <c r="J5" s="233"/>
-      <c r="K5" s="233"/>
-      <c r="L5" s="233"/>
-      <c r="M5" s="223"/>
-      <c r="N5" s="233"/>
-      <c r="O5" s="227"/>
-      <c r="P5" s="238"/>
-      <c r="Q5" s="230"/>
-      <c r="R5" s="223"/>
+      <c r="D5" s="231"/>
+      <c r="E5" s="231"/>
+      <c r="F5" s="241"/>
+      <c r="G5" s="231"/>
+      <c r="H5" s="241"/>
+      <c r="I5" s="231"/>
+      <c r="J5" s="241"/>
+      <c r="K5" s="241"/>
+      <c r="L5" s="241"/>
+      <c r="M5" s="231"/>
+      <c r="N5" s="241"/>
+      <c r="O5" s="235"/>
+      <c r="P5" s="246"/>
+      <c r="Q5" s="238"/>
+      <c r="R5" s="231"/>
     </row>
     <row r="6" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
@@ -12537,91 +12598,91 @@
     </row>
     <row r="83" spans="2:18" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="84" spans="2:18" ht="9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E84" s="217" t="str">
+      <c r="E84" s="225" t="str">
         <f>RESUMEN!A14</f>
         <v>ESTIMADOS PROPIETARIOS E INQUILINOS: POR FAVOR LOS QUE ABONAN EN PRIMER VENCIMIENTO ABONEN EL MONTO DE PRIMER VENCIMIENTO, ASI AGILIZAN LA LIQUIDACION, RESPETEN LOS CENTAVOS CORRESPONDIENTES A LA UNIDAD FUNCIONAL. ES DE CARÁCTER OBLIGATORIO INFORMAR VIA MAIL LAS EXPENSAS. CASO CONTRARIO SE INFORMARA VIA CARTA DOCUMENTO A LA UNIDAD FUNCIONAL QUE CREEMOS QUE CORRESPONDE, CUYO COSTO SERA IMPUTADO A LA UNIDAD FUNCIONAL SOSPECHADA.</v>
       </c>
-      <c r="F84" s="210"/>
-      <c r="G84" s="210"/>
-      <c r="H84" s="210"/>
-      <c r="I84" s="210"/>
-      <c r="J84" s="210"/>
-      <c r="K84" s="210"/>
-      <c r="L84" s="210"/>
-      <c r="M84" s="210"/>
-      <c r="N84" s="210"/>
-      <c r="O84" s="210"/>
-      <c r="P84" s="210"/>
+      <c r="F84" s="218"/>
+      <c r="G84" s="218"/>
+      <c r="H84" s="218"/>
+      <c r="I84" s="218"/>
+      <c r="J84" s="218"/>
+      <c r="K84" s="218"/>
+      <c r="L84" s="218"/>
+      <c r="M84" s="218"/>
+      <c r="N84" s="218"/>
+      <c r="O84" s="218"/>
+      <c r="P84" s="218"/>
     </row>
     <row r="85" spans="2:18" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E85" s="210"/>
-      <c r="F85" s="210"/>
-      <c r="G85" s="210"/>
-      <c r="H85" s="210"/>
-      <c r="I85" s="210"/>
-      <c r="J85" s="210"/>
-      <c r="K85" s="210"/>
-      <c r="L85" s="210"/>
-      <c r="M85" s="210"/>
-      <c r="N85" s="210"/>
-      <c r="O85" s="210"/>
-      <c r="P85" s="210"/>
+      <c r="E85" s="218"/>
+      <c r="F85" s="218"/>
+      <c r="G85" s="218"/>
+      <c r="H85" s="218"/>
+      <c r="I85" s="218"/>
+      <c r="J85" s="218"/>
+      <c r="K85" s="218"/>
+      <c r="L85" s="218"/>
+      <c r="M85" s="218"/>
+      <c r="N85" s="218"/>
+      <c r="O85" s="218"/>
+      <c r="P85" s="218"/>
     </row>
     <row r="86" spans="2:18" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E86" s="210"/>
-      <c r="F86" s="210"/>
-      <c r="G86" s="210"/>
-      <c r="H86" s="210"/>
-      <c r="I86" s="210"/>
-      <c r="J86" s="210"/>
-      <c r="K86" s="210"/>
-      <c r="L86" s="210"/>
-      <c r="M86" s="210"/>
-      <c r="N86" s="210"/>
-      <c r="O86" s="210"/>
-      <c r="P86" s="210"/>
+      <c r="E86" s="218"/>
+      <c r="F86" s="218"/>
+      <c r="G86" s="218"/>
+      <c r="H86" s="218"/>
+      <c r="I86" s="218"/>
+      <c r="J86" s="218"/>
+      <c r="K86" s="218"/>
+      <c r="L86" s="218"/>
+      <c r="M86" s="218"/>
+      <c r="N86" s="218"/>
+      <c r="O86" s="218"/>
+      <c r="P86" s="218"/>
     </row>
     <row r="87" spans="2:18" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E87" s="210"/>
-      <c r="F87" s="210"/>
-      <c r="G87" s="210"/>
-      <c r="H87" s="210"/>
-      <c r="I87" s="210"/>
-      <c r="J87" s="210"/>
-      <c r="K87" s="210"/>
-      <c r="L87" s="210"/>
-      <c r="M87" s="210"/>
-      <c r="N87" s="210"/>
-      <c r="O87" s="210"/>
-      <c r="P87" s="210"/>
+      <c r="E87" s="218"/>
+      <c r="F87" s="218"/>
+      <c r="G87" s="218"/>
+      <c r="H87" s="218"/>
+      <c r="I87" s="218"/>
+      <c r="J87" s="218"/>
+      <c r="K87" s="218"/>
+      <c r="L87" s="218"/>
+      <c r="M87" s="218"/>
+      <c r="N87" s="218"/>
+      <c r="O87" s="218"/>
+      <c r="P87" s="218"/>
     </row>
     <row r="88" spans="2:18" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E88" s="210"/>
-      <c r="F88" s="210"/>
-      <c r="G88" s="210"/>
-      <c r="H88" s="210"/>
-      <c r="I88" s="210"/>
-      <c r="J88" s="210"/>
-      <c r="K88" s="210"/>
-      <c r="L88" s="210"/>
-      <c r="M88" s="210"/>
-      <c r="N88" s="210"/>
-      <c r="O88" s="210"/>
-      <c r="P88" s="210"/>
+      <c r="E88" s="218"/>
+      <c r="F88" s="218"/>
+      <c r="G88" s="218"/>
+      <c r="H88" s="218"/>
+      <c r="I88" s="218"/>
+      <c r="J88" s="218"/>
+      <c r="K88" s="218"/>
+      <c r="L88" s="218"/>
+      <c r="M88" s="218"/>
+      <c r="N88" s="218"/>
+      <c r="O88" s="218"/>
+      <c r="P88" s="218"/>
     </row>
     <row r="89" spans="2:18" ht="67.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E89" s="210"/>
-      <c r="F89" s="210"/>
-      <c r="G89" s="210"/>
-      <c r="H89" s="210"/>
-      <c r="I89" s="210"/>
-      <c r="J89" s="210"/>
-      <c r="K89" s="210"/>
-      <c r="L89" s="210"/>
-      <c r="M89" s="210"/>
-      <c r="N89" s="210"/>
-      <c r="O89" s="210"/>
-      <c r="P89" s="210"/>
+      <c r="E89" s="218"/>
+      <c r="F89" s="218"/>
+      <c r="G89" s="218"/>
+      <c r="H89" s="218"/>
+      <c r="I89" s="218"/>
+      <c r="J89" s="218"/>
+      <c r="K89" s="218"/>
+      <c r="L89" s="218"/>
+      <c r="M89" s="218"/>
+      <c r="N89" s="218"/>
+      <c r="O89" s="218"/>
+      <c r="P89" s="218"/>
     </row>
   </sheetData>
   <mergeCells count="20">
